--- a/MapLab3D_ProjectParameters_1_2_0_0_Reference.xlsx
+++ b/MapLab3D_ProjectParameters_1_2_0_0_Reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Daten\Projekte\MapLab3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884DF197-4D27-460B-8BCD-23DCFD76E8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601CC033-07FC-473D-97E2-65AECBB2B525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="0" windowWidth="19230" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PP ref" sheetId="1" r:id="rId1"/>
@@ -4237,38 +4237,6 @@
 ---+  elevation level  +----------</t>
   </si>
   <si>
-    <t>Continuously changing line width:
-par{1} = minimum line width / mm
-par{2} = maximum line width / mm
-         The maximum line width must be greater than or equal to
-         the minimum line width.
-par{3} = sampling
-         The ends of the polygon consists of semicircles, the center is equal
-         to the first and last point of x and y. The number of edges of a
-         semicircle is defined by sampling. Examples:
-         sampling=1: only one edge, no circle
-                  6: should be the standard value for lines:
-                     - The lines are longer:
-                       Line segements will be connected automatically
-                     - Higher values increase the execution time.
-par{4} = lifting dz (background) / mm
-par{5} = direction reversal (0/1)
-         0: The beginning of the line has the minimum line width.
-            Note: In OpenStreetMap the direction of rivers is downstream
-                  (the direction that the river flows).
-         1: The end of the line has the minimum line width.
-par{6} = increase in line width / per thousand (&gt;=0)
-         Example:
-         5: With a total line length of 100 mm, the line width at the end 
-            is 0.5 mm greater than the line width at the beginning.
-         0: The line width is constantly equal to the minimum line width.
-         If par{7}=0 and par{8}=0:
-         Long line:  The maximum line width is reached before the end
-                     of the line, the line width then remains constant.
-         Short line: The maximum line width is not reached at the end
-                     of the line.</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
@@ -4617,6 +4585,39 @@
   </si>
   <si>
     <t>Symbols: Minimum distance between two vertices of the source plots</t>
+  </si>
+  <si>
+    <t>Continuously changing line width:
+Lines with this line style have only one start and end point, so they do have no branches!
+par{1} = minimum line width / mm
+par{2} = maximum line width / mm
+         The maximum line width must be greater than or equal to
+         the minimum line width.
+par{3} = sampling
+         The ends of the polygon consists of semicircles, the center is equal
+         to the first and last point of x and y. The number of edges of a
+         semicircle is defined by sampling. Examples:
+         sampling=1: only one edge, no circle
+                  6: should be the standard value for lines:
+                     - The lines are longer:
+                       Line segements will be connected automatically
+                     - Higher values increase the execution time.
+par{4} = lifting dz (background) / mm
+par{5} = direction reversal (0/1)
+         0: The beginning of the line has the minimum line width.
+            Note: In OpenStreetMap the direction of rivers is downstream
+                  (the direction that the river flows).
+         1: The end of the line has the minimum line width.
+par{6} = increase in line width / per thousand (&gt;=0)
+         Example:
+         5: With a total line length of 100 mm, the line width at the end 
+            is 0.5 mm greater than the line width at the beginning.
+         0: The line width is constantly equal to the minimum line width.
+         If par{7}=0 and par{8}=0:
+         Long line:  The maximum line width is reached before the end
+                     of the line, the line width then remains constant.
+         Short line: The maximum line width is not reached at the end
+                     of the line.</t>
   </si>
 </sst>
 </file>
@@ -5847,28 +5848,40 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5883,20 +5896,8 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7559,29 +7560,29 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="18.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="229" t="s">
+      <c r="A2" s="216" t="s">
         <v>1090</v>
       </c>
-      <c r="B2" s="230"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="230"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="230"/>
-      <c r="L2" s="230"/>
-      <c r="M2" s="230"/>
-      <c r="N2" s="230"/>
-      <c r="O2" s="230"/>
-      <c r="P2" s="230"/>
-      <c r="Q2" s="230"/>
-      <c r="R2" s="230"/>
-      <c r="S2" s="230"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="231"/>
+      <c r="B2" s="217"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="217"/>
+      <c r="J2" s="217"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="217"/>
+      <c r="M2" s="217"/>
+      <c r="N2" s="217"/>
+      <c r="O2" s="217"/>
+      <c r="P2" s="217"/>
+      <c r="Q2" s="217"/>
+      <c r="R2" s="217"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="218"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="110"/>
@@ -7700,15 +7701,15 @@
       <c r="O6" s="22"/>
       <c r="P6" s="23"/>
       <c r="Q6" s="202" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="R6" s="36"/>
       <c r="S6" s="19"/>
       <c r="T6" s="143" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="U6" s="143" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
@@ -7785,7 +7786,7 @@
       <c r="R8" s="36"/>
       <c r="S8" s="24"/>
       <c r="T8" s="54" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="U8" s="54" t="s">
         <v>124</v>
@@ -7983,7 +7984,7 @@
       <c r="T14" s="54" t="s">
         <v>838</v>
       </c>
-      <c r="U14" s="217"/>
+      <c r="U14" s="215"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="37"/>
@@ -8006,7 +8007,7 @@
       <c r="R15" s="25"/>
       <c r="S15" s="42"/>
       <c r="T15" s="190"/>
-      <c r="U15" s="217"/>
+      <c r="U15" s="215"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="37"/>
@@ -8029,7 +8030,7 @@
       <c r="R16" s="25"/>
       <c r="S16" s="42"/>
       <c r="T16" s="190"/>
-      <c r="U16" s="217"/>
+      <c r="U16" s="215"/>
     </row>
     <row r="17" spans="1:21" ht="39" x14ac:dyDescent="0.35">
       <c r="A17" s="37" t="s">
@@ -8252,7 +8253,7 @@
       </c>
       <c r="S21" s="42"/>
       <c r="T21" s="54" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="U21" s="43"/>
     </row>
@@ -8618,7 +8619,7 @@
       <c r="T29" s="54" t="s">
         <v>783</v>
       </c>
-      <c r="U29" s="217" t="s">
+      <c r="U29" s="215" t="s">
         <v>1079</v>
       </c>
     </row>
@@ -8661,7 +8662,7 @@
       <c r="T30" s="54" t="s">
         <v>782</v>
       </c>
-      <c r="U30" s="217"/>
+      <c r="U30" s="215"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" s="37"/>
@@ -8684,7 +8685,7 @@
       <c r="R31" s="25"/>
       <c r="S31" s="42"/>
       <c r="T31" s="54"/>
-      <c r="U31" s="217"/>
+      <c r="U31" s="215"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" s="37"/>
@@ -8707,7 +8708,7 @@
       <c r="R32" s="25"/>
       <c r="S32" s="42"/>
       <c r="T32" s="54"/>
-      <c r="U32" s="217"/>
+      <c r="U32" s="215"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" s="37" t="s">
@@ -8756,7 +8757,7 @@
       <c r="T33" s="54" t="s">
         <v>778</v>
       </c>
-      <c r="U33" s="217" t="s">
+      <c r="U33" s="215" t="s">
         <v>777</v>
       </c>
     </row>
@@ -8807,7 +8808,7 @@
       <c r="T34" s="54" t="s">
         <v>779</v>
       </c>
-      <c r="U34" s="217"/>
+      <c r="U34" s="215"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" s="37" t="s">
@@ -8856,7 +8857,7 @@
       <c r="T35" s="54" t="s">
         <v>780</v>
       </c>
-      <c r="U35" s="217"/>
+      <c r="U35" s="215"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" s="37" t="s">
@@ -8905,7 +8906,7 @@
       <c r="T36" s="54" t="s">
         <v>781</v>
       </c>
-      <c r="U36" s="217"/>
+      <c r="U36" s="215"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" s="37"/>
@@ -8928,7 +8929,7 @@
       <c r="R37" s="25"/>
       <c r="S37" s="42"/>
       <c r="T37" s="54"/>
-      <c r="U37" s="217"/>
+      <c r="U37" s="215"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" s="37"/>
@@ -8951,7 +8952,7 @@
       <c r="R38" s="25"/>
       <c r="S38" s="42"/>
       <c r="T38" s="54"/>
-      <c r="U38" s="217"/>
+      <c r="U38" s="215"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" s="37" t="s">
@@ -9000,7 +9001,7 @@
       <c r="T39" s="54" t="s">
         <v>454</v>
       </c>
-      <c r="U39" s="216" t="s">
+      <c r="U39" s="220" t="s">
         <v>458</v>
       </c>
     </row>
@@ -9051,7 +9052,7 @@
       <c r="T40" s="54" t="s">
         <v>455</v>
       </c>
-      <c r="U40" s="216"/>
+      <c r="U40" s="220"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" s="37" t="s">
@@ -9100,7 +9101,7 @@
       <c r="T41" s="54" t="s">
         <v>456</v>
       </c>
-      <c r="U41" s="216"/>
+      <c r="U41" s="220"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" s="37" t="s">
@@ -9149,7 +9150,7 @@
       <c r="T42" s="54" t="s">
         <v>457</v>
       </c>
-      <c r="U42" s="216"/>
+      <c r="U42" s="220"/>
     </row>
     <row r="43" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="37" t="s">
@@ -9190,7 +9191,7 @@
       <c r="T43" s="54" t="s">
         <v>965</v>
       </c>
-      <c r="U43" s="217" t="s">
+      <c r="U43" s="215" t="s">
         <v>512</v>
       </c>
     </row>
@@ -9208,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>2</v>
@@ -9233,7 +9234,7 @@
       <c r="T44" s="54" t="s">
         <v>966</v>
       </c>
-      <c r="U44" s="217"/>
+      <c r="U44" s="215"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" s="37"/>
@@ -9256,7 +9257,7 @@
       <c r="R45" s="25"/>
       <c r="S45" s="42"/>
       <c r="T45" s="54"/>
-      <c r="U45" s="217"/>
+      <c r="U45" s="215"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" s="37" t="s">
@@ -9297,7 +9298,7 @@
       <c r="T46" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="U46" s="217" t="s">
+      <c r="U46" s="215" t="s">
         <v>683</v>
       </c>
     </row>
@@ -9340,7 +9341,7 @@
       <c r="T47" s="54" t="s">
         <v>175</v>
       </c>
-      <c r="U47" s="217"/>
+      <c r="U47" s="215"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" s="37" t="s">
@@ -9381,7 +9382,7 @@
       <c r="T48" s="54" t="s">
         <v>776</v>
       </c>
-      <c r="U48" s="217" t="s">
+      <c r="U48" s="215" t="s">
         <v>785</v>
       </c>
     </row>
@@ -9406,7 +9407,7 @@
       <c r="R49" s="25"/>
       <c r="S49" s="42"/>
       <c r="T49" s="54"/>
-      <c r="U49" s="217"/>
+      <c r="U49" s="215"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" s="37"/>
@@ -9429,7 +9430,7 @@
       <c r="R50" s="25"/>
       <c r="S50" s="42"/>
       <c r="T50" s="54"/>
-      <c r="U50" s="217"/>
+      <c r="U50" s="215"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" s="37"/>
@@ -9452,7 +9453,7 @@
       <c r="R51" s="25"/>
       <c r="S51" s="42"/>
       <c r="T51" s="54"/>
-      <c r="U51" s="217"/>
+      <c r="U51" s="215"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="37"/>
@@ -9475,7 +9476,7 @@
       <c r="R52" s="25"/>
       <c r="S52" s="42"/>
       <c r="T52" s="54"/>
-      <c r="U52" s="217"/>
+      <c r="U52" s="215"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="37"/>
@@ -9498,7 +9499,7 @@
       <c r="R53" s="25"/>
       <c r="S53" s="42"/>
       <c r="T53" s="54"/>
-      <c r="U53" s="217"/>
+      <c r="U53" s="215"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="37"/>
@@ -9521,7 +9522,7 @@
       <c r="R54" s="25"/>
       <c r="S54" s="42"/>
       <c r="T54" s="54"/>
-      <c r="U54" s="217"/>
+      <c r="U54" s="215"/>
     </row>
     <row r="55" spans="1:21" ht="104" x14ac:dyDescent="0.35">
       <c r="A55" s="37" t="s">
@@ -9633,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="J57" s="38" t="s">
         <v>2</v>
@@ -9650,7 +9651,7 @@
       </c>
       <c r="S57" s="42"/>
       <c r="T57" s="211" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="U57" s="211"/>
     </row>
@@ -9680,7 +9681,7 @@
         <v>1</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="J58" s="38" t="s">
         <v>2</v>
@@ -9842,7 +9843,7 @@
       <c r="T61" s="54" t="s">
         <v>790</v>
       </c>
-      <c r="U61" s="217" t="s">
+      <c r="U61" s="215" t="s">
         <v>792</v>
       </c>
     </row>
@@ -9891,7 +9892,7 @@
       <c r="T62" s="54" t="s">
         <v>791</v>
       </c>
-      <c r="U62" s="217"/>
+      <c r="U62" s="215"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="37"/>
@@ -9914,7 +9915,7 @@
       <c r="R63" s="25"/>
       <c r="S63" s="42"/>
       <c r="T63" s="54"/>
-      <c r="U63" s="217"/>
+      <c r="U63" s="215"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="37"/>
@@ -9937,7 +9938,7 @@
       <c r="R64" s="25"/>
       <c r="S64" s="42"/>
       <c r="T64" s="54"/>
-      <c r="U64" s="217"/>
+      <c r="U64" s="215"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" s="37" t="s">
@@ -10189,7 +10190,7 @@
       <c r="T70" s="54" t="s">
         <v>552</v>
       </c>
-      <c r="U70" s="217" t="s">
+      <c r="U70" s="215" t="s">
         <v>1085</v>
       </c>
     </row>
@@ -10231,7 +10232,7 @@
       <c r="O71" s="39"/>
       <c r="P71" s="40"/>
       <c r="Q71" s="53" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="R71" s="25" t="s">
         <v>548</v>
@@ -10240,7 +10241,7 @@
       <c r="T71" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="U71" s="217"/>
+      <c r="U71" s="215"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="37" t="s">
@@ -10289,7 +10290,7 @@
       <c r="T72" s="54" t="s">
         <v>551</v>
       </c>
-      <c r="U72" s="217"/>
+      <c r="U72" s="215"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" s="37" t="s">
@@ -10334,7 +10335,7 @@
       <c r="T73" s="54" t="s">
         <v>552</v>
       </c>
-      <c r="U73" s="217"/>
+      <c r="U73" s="215"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" s="37" t="s">
@@ -10381,7 +10382,7 @@
       <c r="T74" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="U74" s="217"/>
+      <c r="U74" s="215"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" s="37" t="s">
@@ -10430,7 +10431,7 @@
       <c r="T75" s="54" t="s">
         <v>551</v>
       </c>
-      <c r="U75" s="217"/>
+      <c r="U75" s="215"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" s="37" t="s">
@@ -10477,7 +10478,7 @@
       <c r="T76" s="54" t="s">
         <v>556</v>
       </c>
-      <c r="U76" s="217"/>
+      <c r="U76" s="215"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" s="37" t="s">
@@ -10524,7 +10525,7 @@
       <c r="T77" s="54" t="s">
         <v>557</v>
       </c>
-      <c r="U77" s="217"/>
+      <c r="U77" s="215"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" s="37" t="s">
@@ -10573,7 +10574,7 @@
       <c r="T78" s="54" t="s">
         <v>558</v>
       </c>
-      <c r="U78" s="217"/>
+      <c r="U78" s="215"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" s="37" t="s">
@@ -10618,7 +10619,7 @@
       <c r="T79" s="54" t="s">
         <v>556</v>
       </c>
-      <c r="U79" s="217"/>
+      <c r="U79" s="215"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" s="37" t="s">
@@ -10665,7 +10666,7 @@
       <c r="T80" s="54" t="s">
         <v>557</v>
       </c>
-      <c r="U80" s="217"/>
+      <c r="U80" s="215"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" s="37" t="s">
@@ -10714,7 +10715,7 @@
       <c r="T81" s="54" t="s">
         <v>558</v>
       </c>
-      <c r="U81" s="217"/>
+      <c r="U81" s="215"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A82" s="37" t="s">
@@ -10761,7 +10762,7 @@
       <c r="T82" s="54" t="s">
         <v>564</v>
       </c>
-      <c r="U82" s="217"/>
+      <c r="U82" s="215"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" s="37" t="s">
@@ -10808,7 +10809,7 @@
       <c r="T83" s="54" t="s">
         <v>559</v>
       </c>
-      <c r="U83" s="217"/>
+      <c r="U83" s="215"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" s="37" t="s">
@@ -10857,7 +10858,7 @@
       <c r="T84" s="54" t="s">
         <v>560</v>
       </c>
-      <c r="U84" s="217"/>
+      <c r="U84" s="215"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" s="37" t="s">
@@ -10902,7 +10903,7 @@
       <c r="T85" s="54" t="s">
         <v>564</v>
       </c>
-      <c r="U85" s="217"/>
+      <c r="U85" s="215"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A86" s="37" t="s">
@@ -10949,7 +10950,7 @@
       <c r="T86" s="54" t="s">
         <v>559</v>
       </c>
-      <c r="U86" s="217"/>
+      <c r="U86" s="215"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" s="37" t="s">
@@ -10998,7 +10999,7 @@
       <c r="T87" s="54" t="s">
         <v>560</v>
       </c>
-      <c r="U87" s="217"/>
+      <c r="U87" s="215"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" s="37" t="s">
@@ -11045,7 +11046,7 @@
       <c r="T88" s="54" t="s">
         <v>561</v>
       </c>
-      <c r="U88" s="217"/>
+      <c r="U88" s="215"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" s="37" t="s">
@@ -11092,7 +11093,7 @@
       <c r="T89" s="54" t="s">
         <v>562</v>
       </c>
-      <c r="U89" s="217"/>
+      <c r="U89" s="215"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" s="37" t="s">
@@ -11141,7 +11142,7 @@
       <c r="T90" s="54" t="s">
         <v>563</v>
       </c>
-      <c r="U90" s="217"/>
+      <c r="U90" s="215"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" s="37" t="s">
@@ -11186,7 +11187,7 @@
       <c r="T91" s="54" t="s">
         <v>561</v>
       </c>
-      <c r="U91" s="217"/>
+      <c r="U91" s="215"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" s="37" t="s">
@@ -11233,7 +11234,7 @@
       <c r="T92" s="54" t="s">
         <v>562</v>
       </c>
-      <c r="U92" s="217"/>
+      <c r="U92" s="215"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A93" s="37" t="s">
@@ -11282,7 +11283,7 @@
       <c r="T93" s="54" t="s">
         <v>563</v>
       </c>
-      <c r="U93" s="217"/>
+      <c r="U93" s="215"/>
     </row>
     <row r="94" spans="1:21" ht="104" x14ac:dyDescent="0.35">
       <c r="A94" s="37" t="s">
@@ -11324,7 +11325,7 @@
         <v>182</v>
       </c>
       <c r="U94" s="143" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.35">
@@ -11374,7 +11375,7 @@
       <c r="T95" s="54" t="s">
         <v>695</v>
       </c>
-      <c r="U95" s="217" t="s">
+      <c r="U95" s="215" t="s">
         <v>899</v>
       </c>
     </row>
@@ -11425,7 +11426,7 @@
       <c r="T96" s="54" t="s">
         <v>696</v>
       </c>
-      <c r="U96" s="217"/>
+      <c r="U96" s="215"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97" s="37" t="s">
@@ -11474,7 +11475,7 @@
       <c r="T97" s="54" t="s">
         <v>697</v>
       </c>
-      <c r="U97" s="217"/>
+      <c r="U97" s="215"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" s="37"/>
@@ -11497,7 +11498,7 @@
       <c r="R98" s="25"/>
       <c r="S98" s="42"/>
       <c r="T98" s="54"/>
-      <c r="U98" s="217"/>
+      <c r="U98" s="215"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" s="37"/>
@@ -11520,7 +11521,7 @@
       <c r="R99" s="25"/>
       <c r="S99" s="42"/>
       <c r="T99" s="54"/>
-      <c r="U99" s="217"/>
+      <c r="U99" s="215"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100" s="37"/>
@@ -11543,7 +11544,7 @@
       <c r="R100" s="25"/>
       <c r="S100" s="42"/>
       <c r="T100" s="54"/>
-      <c r="U100" s="217"/>
+      <c r="U100" s="215"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="37"/>
@@ -11566,7 +11567,7 @@
       <c r="R101" s="25"/>
       <c r="S101" s="42"/>
       <c r="T101" s="54"/>
-      <c r="U101" s="217"/>
+      <c r="U101" s="215"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" s="37"/>
@@ -11589,7 +11590,7 @@
       <c r="R102" s="25"/>
       <c r="S102" s="42"/>
       <c r="T102" s="54"/>
-      <c r="U102" s="217"/>
+      <c r="U102" s="215"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" s="37"/>
@@ -11612,7 +11613,7 @@
       <c r="R103" s="25"/>
       <c r="S103" s="42"/>
       <c r="T103" s="54"/>
-      <c r="U103" s="217"/>
+      <c r="U103" s="215"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="37"/>
@@ -11635,7 +11636,7 @@
       <c r="R104" s="25"/>
       <c r="S104" s="42"/>
       <c r="T104" s="54"/>
-      <c r="U104" s="217"/>
+      <c r="U104" s="215"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" s="37"/>
@@ -11658,7 +11659,7 @@
       <c r="R105" s="25"/>
       <c r="S105" s="42"/>
       <c r="T105" s="54"/>
-      <c r="U105" s="217"/>
+      <c r="U105" s="215"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" s="37"/>
@@ -11681,7 +11682,7 @@
       <c r="R106" s="25"/>
       <c r="S106" s="42"/>
       <c r="T106" s="54"/>
-      <c r="U106" s="217"/>
+      <c r="U106" s="215"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="37"/>
@@ -11704,7 +11705,7 @@
       <c r="R107" s="25"/>
       <c r="S107" s="42"/>
       <c r="T107" s="54"/>
-      <c r="U107" s="217"/>
+      <c r="U107" s="215"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="37"/>
@@ -11727,7 +11728,7 @@
       <c r="R108" s="25"/>
       <c r="S108" s="42"/>
       <c r="T108" s="54"/>
-      <c r="U108" s="217"/>
+      <c r="U108" s="215"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="37"/>
@@ -11750,7 +11751,7 @@
       <c r="R109" s="25"/>
       <c r="S109" s="42"/>
       <c r="T109" s="54"/>
-      <c r="U109" s="217"/>
+      <c r="U109" s="215"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" s="37"/>
@@ -11773,7 +11774,7 @@
       <c r="R110" s="25"/>
       <c r="S110" s="42"/>
       <c r="T110" s="54"/>
-      <c r="U110" s="217"/>
+      <c r="U110" s="215"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" s="37"/>
@@ -11796,7 +11797,7 @@
       <c r="R111" s="25"/>
       <c r="S111" s="42"/>
       <c r="T111" s="54"/>
-      <c r="U111" s="217"/>
+      <c r="U111" s="215"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" s="37"/>
@@ -11819,7 +11820,7 @@
       <c r="R112" s="25"/>
       <c r="S112" s="42"/>
       <c r="T112" s="54"/>
-      <c r="U112" s="217"/>
+      <c r="U112" s="215"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" s="37"/>
@@ -11842,7 +11843,7 @@
       <c r="R113" s="25"/>
       <c r="S113" s="42"/>
       <c r="T113" s="54"/>
-      <c r="U113" s="217"/>
+      <c r="U113" s="215"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" s="37"/>
@@ -11865,7 +11866,7 @@
       <c r="R114" s="25"/>
       <c r="S114" s="42"/>
       <c r="T114" s="54"/>
-      <c r="U114" s="217"/>
+      <c r="U114" s="215"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" s="37"/>
@@ -11888,7 +11889,7 @@
       <c r="R115" s="25"/>
       <c r="S115" s="42"/>
       <c r="T115" s="54"/>
-      <c r="U115" s="217"/>
+      <c r="U115" s="215"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" s="37"/>
@@ -11911,7 +11912,7 @@
       <c r="R116" s="25"/>
       <c r="S116" s="42"/>
       <c r="T116" s="54"/>
-      <c r="U116" s="217"/>
+      <c r="U116" s="215"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" s="37"/>
@@ -11934,7 +11935,7 @@
       <c r="R117" s="25"/>
       <c r="S117" s="42"/>
       <c r="T117" s="54"/>
-      <c r="U117" s="217"/>
+      <c r="U117" s="215"/>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" s="37"/>
@@ -12200,7 +12201,7 @@
       <c r="T127" s="54" t="s">
         <v>845</v>
       </c>
-      <c r="U127" s="217" t="s">
+      <c r="U127" s="215" t="s">
         <v>847</v>
       </c>
     </row>
@@ -12251,7 +12252,7 @@
       <c r="T128" s="54" t="s">
         <v>844</v>
       </c>
-      <c r="U128" s="217"/>
+      <c r="U128" s="215"/>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" s="37"/>
@@ -12274,7 +12275,7 @@
       <c r="R129" s="25"/>
       <c r="S129" s="42"/>
       <c r="T129" s="54"/>
-      <c r="U129" s="217"/>
+      <c r="U129" s="215"/>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" s="37"/>
@@ -12297,7 +12298,7 @@
       <c r="R130" s="25"/>
       <c r="S130" s="42"/>
       <c r="T130" s="54"/>
-      <c r="U130" s="217"/>
+      <c r="U130" s="215"/>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" s="37"/>
@@ -12320,7 +12321,7 @@
       <c r="R131" s="25"/>
       <c r="S131" s="42"/>
       <c r="T131" s="54"/>
-      <c r="U131" s="217"/>
+      <c r="U131" s="215"/>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A132" s="37" t="s">
@@ -12336,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="E132" s="37" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F132" s="38" t="s">
         <v>2</v>
@@ -12367,10 +12368,10 @@
         <v>9</v>
       </c>
       <c r="T132" s="201" t="s">
-        <v>1135</v>
-      </c>
-      <c r="U132" s="217" t="s">
-        <v>1137</v>
+        <v>1134</v>
+      </c>
+      <c r="U132" s="215" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.35">
@@ -12387,7 +12388,7 @@
         <v>1</v>
       </c>
       <c r="E133" s="37" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F133" s="38" t="s">
         <v>2</v>
@@ -12418,9 +12419,9 @@
         <v>50</v>
       </c>
       <c r="T133" s="201" t="s">
-        <v>1136</v>
-      </c>
-      <c r="U133" s="217"/>
+        <v>1135</v>
+      </c>
+      <c r="U133" s="215"/>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" s="37" t="s">
@@ -12469,7 +12470,7 @@
       <c r="T134" s="54" t="s">
         <v>843</v>
       </c>
-      <c r="U134" s="217" t="s">
+      <c r="U134" s="215" t="s">
         <v>848</v>
       </c>
     </row>
@@ -12494,7 +12495,7 @@
       <c r="R135" s="25"/>
       <c r="S135" s="42"/>
       <c r="T135" s="54"/>
-      <c r="U135" s="217"/>
+      <c r="U135" s="215"/>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" s="37"/>
@@ -12517,7 +12518,7 @@
       <c r="R136" s="25"/>
       <c r="S136" s="42"/>
       <c r="T136" s="54"/>
-      <c r="U136" s="217"/>
+      <c r="U136" s="215"/>
     </row>
     <row r="137" spans="1:21" ht="39" x14ac:dyDescent="0.35">
       <c r="A137" s="37" t="s">
@@ -12740,7 +12741,7 @@
       <c r="T141" s="54" t="s">
         <v>1063</v>
       </c>
-      <c r="U141" s="217" t="s">
+      <c r="U141" s="215" t="s">
         <v>1065</v>
       </c>
     </row>
@@ -12789,7 +12790,7 @@
       <c r="T142" s="191" t="s">
         <v>1064</v>
       </c>
-      <c r="U142" s="217"/>
+      <c r="U142" s="215"/>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" s="37" t="s">
@@ -12838,7 +12839,7 @@
       <c r="T143" s="54" t="s">
         <v>1060</v>
       </c>
-      <c r="U143" s="217" t="s">
+      <c r="U143" s="215" t="s">
         <v>1059</v>
       </c>
     </row>
@@ -12889,7 +12890,7 @@
       <c r="T144" s="191" t="s">
         <v>1061</v>
       </c>
-      <c r="U144" s="217"/>
+      <c r="U144" s="215"/>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" s="37" t="s">
@@ -12938,7 +12939,7 @@
       <c r="T145" s="191" t="s">
         <v>1062</v>
       </c>
-      <c r="U145" s="217"/>
+      <c r="U145" s="215"/>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" s="37"/>
@@ -13301,7 +13302,7 @@
       <c r="T156" s="173" t="s">
         <v>930</v>
       </c>
-      <c r="U156" s="222" t="s">
+      <c r="U156" s="225" t="s">
         <v>928</v>
       </c>
     </row>
@@ -13344,7 +13345,7 @@
       <c r="T157" s="143" t="s">
         <v>632</v>
       </c>
-      <c r="U157" s="222"/>
+      <c r="U157" s="225"/>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A158" s="37" t="s">
@@ -13383,9 +13384,9 @@
         <v>9</v>
       </c>
       <c r="T158" s="143" t="s">
-        <v>1139</v>
-      </c>
-      <c r="U158" s="222"/>
+        <v>1138</v>
+      </c>
+      <c r="U158" s="225"/>
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A159" s="37" t="s">
@@ -13426,7 +13427,7 @@
       <c r="T159" s="143" t="s">
         <v>633</v>
       </c>
-      <c r="U159" s="222"/>
+      <c r="U159" s="225"/>
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A160" s="37" t="s">
@@ -13467,7 +13468,7 @@
       <c r="T160" s="143" t="s">
         <v>634</v>
       </c>
-      <c r="U160" s="222"/>
+      <c r="U160" s="225"/>
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A161" s="37" t="s">
@@ -13508,7 +13509,7 @@
       <c r="T161" s="143" t="s">
         <v>635</v>
       </c>
-      <c r="U161" s="222"/>
+      <c r="U161" s="225"/>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A162" s="37" t="s">
@@ -13549,7 +13550,7 @@
       <c r="T162" s="143" t="s">
         <v>636</v>
       </c>
-      <c r="U162" s="222"/>
+      <c r="U162" s="225"/>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A163" s="37" t="s">
@@ -13590,7 +13591,7 @@
       <c r="T163" s="143" t="s">
         <v>637</v>
       </c>
-      <c r="U163" s="222"/>
+      <c r="U163" s="225"/>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A164" s="37" t="s">
@@ -13631,7 +13632,7 @@
       <c r="T164" s="143" t="s">
         <v>638</v>
       </c>
-      <c r="U164" s="222"/>
+      <c r="U164" s="225"/>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A165" s="37"/>
@@ -13654,7 +13655,7 @@
       <c r="R165" s="25"/>
       <c r="S165" s="24"/>
       <c r="T165" s="143"/>
-      <c r="U165" s="222"/>
+      <c r="U165" s="225"/>
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A166" s="37"/>
@@ -13677,7 +13678,7 @@
       <c r="R166" s="25"/>
       <c r="S166" s="24"/>
       <c r="T166" s="143"/>
-      <c r="U166" s="222"/>
+      <c r="U166" s="225"/>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A167" s="37"/>
@@ -13700,7 +13701,7 @@
       <c r="R167" s="25"/>
       <c r="S167" s="24"/>
       <c r="T167" s="143"/>
-      <c r="U167" s="222"/>
+      <c r="U167" s="225"/>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A168" s="37"/>
@@ -13723,7 +13724,7 @@
       <c r="R168" s="25"/>
       <c r="S168" s="24"/>
       <c r="T168" s="143"/>
-      <c r="U168" s="222"/>
+      <c r="U168" s="225"/>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A169" s="37"/>
@@ -13746,7 +13747,7 @@
       <c r="R169" s="25"/>
       <c r="S169" s="24"/>
       <c r="T169" s="143"/>
-      <c r="U169" s="222"/>
+      <c r="U169" s="225"/>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A170" s="37"/>
@@ -13769,7 +13770,7 @@
       <c r="R170" s="25"/>
       <c r="S170" s="24"/>
       <c r="T170" s="143"/>
-      <c r="U170" s="222"/>
+      <c r="U170" s="225"/>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A171" s="37"/>
@@ -13792,7 +13793,7 @@
       <c r="R171" s="25"/>
       <c r="S171" s="24"/>
       <c r="T171" s="143"/>
-      <c r="U171" s="222"/>
+      <c r="U171" s="225"/>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A172" s="37"/>
@@ -13815,7 +13816,7 @@
       <c r="R172" s="25"/>
       <c r="S172" s="24"/>
       <c r="T172" s="143"/>
-      <c r="U172" s="222"/>
+      <c r="U172" s="225"/>
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A173" s="37"/>
@@ -13838,7 +13839,7 @@
       <c r="R173" s="25"/>
       <c r="S173" s="24"/>
       <c r="T173" s="143"/>
-      <c r="U173" s="222"/>
+      <c r="U173" s="225"/>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A174" s="37"/>
@@ -13861,7 +13862,7 @@
       <c r="R174" s="25"/>
       <c r="S174" s="24"/>
       <c r="T174" s="143"/>
-      <c r="U174" s="222"/>
+      <c r="U174" s="225"/>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A175" s="37"/>
@@ -13884,7 +13885,7 @@
       <c r="R175" s="25"/>
       <c r="S175" s="24"/>
       <c r="T175" s="143"/>
-      <c r="U175" s="222"/>
+      <c r="U175" s="225"/>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A176" s="37"/>
@@ -13907,7 +13908,7 @@
       <c r="R176" s="25"/>
       <c r="S176" s="24"/>
       <c r="T176" s="143"/>
-      <c r="U176" s="222"/>
+      <c r="U176" s="225"/>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" s="37"/>
@@ -13930,7 +13931,7 @@
       <c r="R177" s="25"/>
       <c r="S177" s="24"/>
       <c r="T177" s="143"/>
-      <c r="U177" s="222"/>
+      <c r="U177" s="225"/>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A178" s="37"/>
@@ -13953,7 +13954,7 @@
       <c r="R178" s="25"/>
       <c r="S178" s="24"/>
       <c r="T178" s="143"/>
-      <c r="U178" s="222"/>
+      <c r="U178" s="225"/>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A179" s="37"/>
@@ -13976,7 +13977,7 @@
       <c r="R179" s="25"/>
       <c r="S179" s="24"/>
       <c r="T179" s="143"/>
-      <c r="U179" s="222"/>
+      <c r="U179" s="225"/>
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A180" s="37"/>
@@ -13999,7 +14000,7 @@
       <c r="R180" s="25"/>
       <c r="S180" s="24"/>
       <c r="T180" s="143"/>
-      <c r="U180" s="222"/>
+      <c r="U180" s="225"/>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A181" s="37"/>
@@ -14022,7 +14023,7 @@
       <c r="R181" s="25"/>
       <c r="S181" s="24"/>
       <c r="T181" s="143"/>
-      <c r="U181" s="222"/>
+      <c r="U181" s="225"/>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A182" s="37"/>
@@ -14045,7 +14046,7 @@
       <c r="R182" s="25"/>
       <c r="S182" s="24"/>
       <c r="T182" s="143"/>
-      <c r="U182" s="222"/>
+      <c r="U182" s="225"/>
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A183" s="37"/>
@@ -14068,7 +14069,7 @@
       <c r="R183" s="25"/>
       <c r="S183" s="24"/>
       <c r="T183" s="143"/>
-      <c r="U183" s="222"/>
+      <c r="U183" s="225"/>
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A184" s="37"/>
@@ -14091,7 +14092,7 @@
       <c r="R184" s="25"/>
       <c r="S184" s="24"/>
       <c r="T184" s="143"/>
-      <c r="U184" s="222"/>
+      <c r="U184" s="225"/>
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A185" s="37"/>
@@ -14114,7 +14115,7 @@
       <c r="R185" s="25"/>
       <c r="S185" s="24"/>
       <c r="T185" s="143"/>
-      <c r="U185" s="222"/>
+      <c r="U185" s="225"/>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A186" s="37"/>
@@ -14137,7 +14138,7 @@
       <c r="R186" s="25"/>
       <c r="S186" s="24"/>
       <c r="T186" s="143"/>
-      <c r="U186" s="222"/>
+      <c r="U186" s="225"/>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A187" s="37"/>
@@ -14160,7 +14161,7 @@
       <c r="R187" s="25"/>
       <c r="S187" s="24"/>
       <c r="T187" s="143"/>
-      <c r="U187" s="222"/>
+      <c r="U187" s="225"/>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A188" s="37"/>
@@ -14183,7 +14184,7 @@
       <c r="R188" s="25"/>
       <c r="S188" s="24"/>
       <c r="T188" s="143"/>
-      <c r="U188" s="222"/>
+      <c r="U188" s="225"/>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A189" s="37"/>
@@ -14206,7 +14207,7 @@
       <c r="R189" s="25"/>
       <c r="S189" s="24"/>
       <c r="T189" s="143"/>
-      <c r="U189" s="222"/>
+      <c r="U189" s="225"/>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A190" s="37"/>
@@ -14229,7 +14230,7 @@
       <c r="R190" s="25"/>
       <c r="S190" s="24"/>
       <c r="T190" s="143"/>
-      <c r="U190" s="222"/>
+      <c r="U190" s="225"/>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A191" s="37"/>
@@ -14252,7 +14253,7 @@
       <c r="R191" s="25"/>
       <c r="S191" s="24"/>
       <c r="T191" s="143"/>
-      <c r="U191" s="222"/>
+      <c r="U191" s="225"/>
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A192" s="37"/>
@@ -14275,7 +14276,7 @@
       <c r="R192" s="25"/>
       <c r="S192" s="24"/>
       <c r="T192" s="143"/>
-      <c r="U192" s="222"/>
+      <c r="U192" s="225"/>
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A193" s="37"/>
@@ -14298,7 +14299,7 @@
       <c r="R193" s="25"/>
       <c r="S193" s="24"/>
       <c r="T193" s="143"/>
-      <c r="U193" s="222"/>
+      <c r="U193" s="225"/>
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A194" s="37"/>
@@ -14321,7 +14322,7 @@
       <c r="R194" s="25"/>
       <c r="S194" s="24"/>
       <c r="T194" s="143"/>
-      <c r="U194" s="222"/>
+      <c r="U194" s="225"/>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A195" s="37"/>
@@ -14344,7 +14345,7 @@
       <c r="R195" s="25"/>
       <c r="S195" s="24"/>
       <c r="T195" s="143"/>
-      <c r="U195" s="222"/>
+      <c r="U195" s="225"/>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A196" s="37"/>
@@ -14367,7 +14368,7 @@
       <c r="R196" s="25"/>
       <c r="S196" s="24"/>
       <c r="T196" s="143"/>
-      <c r="U196" s="222"/>
+      <c r="U196" s="225"/>
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A197" s="37" t="s">
@@ -14549,7 +14550,7 @@
         <v>1</v>
       </c>
       <c r="E201" s="37" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="F201" s="38" t="s">
         <v>2</v>
@@ -14572,7 +14573,7 @@
         <v>9</v>
       </c>
       <c r="T201" s="143" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="U201" s="63"/>
     </row>
@@ -14885,8 +14886,8 @@
       <c r="T208" s="143" t="s">
         <v>932</v>
       </c>
-      <c r="U208" s="215" t="s">
-        <v>1141</v>
+      <c r="U208" s="221" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.35">
@@ -14936,7 +14937,7 @@
       <c r="T209" s="143" t="s">
         <v>922</v>
       </c>
-      <c r="U209" s="215"/>
+      <c r="U209" s="221"/>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A210" s="37" t="s">
@@ -14964,7 +14965,7 @@
         <v>1</v>
       </c>
       <c r="I210" s="37" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="J210" s="38" t="s">
         <v>2</v>
@@ -14983,9 +14984,9 @@
         <v>9</v>
       </c>
       <c r="T210" s="143" t="s">
-        <v>1143</v>
-      </c>
-      <c r="U210" s="215"/>
+        <v>1142</v>
+      </c>
+      <c r="U210" s="221"/>
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A211" s="37"/>
@@ -15008,7 +15009,7 @@
       <c r="R211" s="25"/>
       <c r="S211" s="24"/>
       <c r="T211" s="143"/>
-      <c r="U211" s="215"/>
+      <c r="U211" s="221"/>
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A212" s="37"/>
@@ -15031,7 +15032,7 @@
       <c r="R212" s="25"/>
       <c r="S212" s="24"/>
       <c r="T212" s="143"/>
-      <c r="U212" s="215"/>
+      <c r="U212" s="221"/>
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A213" s="37"/>
@@ -15054,7 +15055,7 @@
       <c r="R213" s="25"/>
       <c r="S213" s="24"/>
       <c r="T213" s="143"/>
-      <c r="U213" s="215"/>
+      <c r="U213" s="221"/>
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A214" s="37"/>
@@ -15077,7 +15078,7 @@
       <c r="R214" s="25"/>
       <c r="S214" s="24"/>
       <c r="T214" s="143"/>
-      <c r="U214" s="215"/>
+      <c r="U214" s="221"/>
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A215" s="37"/>
@@ -15100,7 +15101,7 @@
       <c r="R215" s="25"/>
       <c r="S215" s="24"/>
       <c r="T215" s="143"/>
-      <c r="U215" s="215"/>
+      <c r="U215" s="221"/>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A216" s="37"/>
@@ -15123,7 +15124,7 @@
       <c r="R216" s="25"/>
       <c r="S216" s="24"/>
       <c r="T216" s="143"/>
-      <c r="U216" s="215"/>
+      <c r="U216" s="221"/>
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A217" s="37"/>
@@ -15146,7 +15147,7 @@
       <c r="R217" s="25"/>
       <c r="S217" s="24"/>
       <c r="T217" s="143"/>
-      <c r="U217" s="215"/>
+      <c r="U217" s="221"/>
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A218" s="37"/>
@@ -15169,7 +15170,7 @@
       <c r="R218" s="25"/>
       <c r="S218" s="24"/>
       <c r="T218" s="143"/>
-      <c r="U218" s="215"/>
+      <c r="U218" s="221"/>
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A219" s="37"/>
@@ -15192,7 +15193,7 @@
       <c r="R219" s="25"/>
       <c r="S219" s="24"/>
       <c r="T219" s="143"/>
-      <c r="U219" s="215"/>
+      <c r="U219" s="221"/>
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A220" s="37" t="s">
@@ -15239,7 +15240,7 @@
       <c r="T220" s="173" t="s">
         <v>925</v>
       </c>
-      <c r="U220" s="215" t="s">
+      <c r="U220" s="221" t="s">
         <v>927</v>
       </c>
     </row>
@@ -15288,7 +15289,7 @@
       <c r="T221" s="173" t="s">
         <v>926</v>
       </c>
-      <c r="U221" s="215"/>
+      <c r="U221" s="221"/>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A222" s="37"/>
@@ -15311,7 +15312,7 @@
       <c r="R222" s="25"/>
       <c r="S222" s="24"/>
       <c r="T222" s="173"/>
-      <c r="U222" s="215"/>
+      <c r="U222" s="221"/>
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A223" s="37"/>
@@ -15334,7 +15335,7 @@
       <c r="R223" s="25"/>
       <c r="S223" s="24"/>
       <c r="T223" s="173"/>
-      <c r="U223" s="215"/>
+      <c r="U223" s="221"/>
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A224" s="37"/>
@@ -15357,7 +15358,7 @@
       <c r="R224" s="25"/>
       <c r="S224" s="24"/>
       <c r="T224" s="173"/>
-      <c r="U224" s="215"/>
+      <c r="U224" s="221"/>
     </row>
     <row r="225" spans="1:21" ht="39" x14ac:dyDescent="0.35">
       <c r="A225" s="37" t="s">
@@ -15502,7 +15503,7 @@
       <c r="T227" s="143" t="s">
         <v>647</v>
       </c>
-      <c r="U227" s="215" t="s">
+      <c r="U227" s="221" t="s">
         <v>674</v>
       </c>
     </row>
@@ -15549,7 +15550,7 @@
       <c r="T228" s="143" t="s">
         <v>648</v>
       </c>
-      <c r="U228" s="215"/>
+      <c r="U228" s="221"/>
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A229" s="37" t="s">
@@ -15843,7 +15844,7 @@
       <c r="T234" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U234" s="215" t="s">
+      <c r="U234" s="221" t="s">
         <v>676</v>
       </c>
     </row>
@@ -15894,7 +15895,7 @@
       <c r="T235" s="143" t="s">
         <v>654</v>
       </c>
-      <c r="U235" s="215"/>
+      <c r="U235" s="221"/>
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A236" s="37" t="s">
@@ -15943,7 +15944,7 @@
       <c r="T236" s="143" t="s">
         <v>655</v>
       </c>
-      <c r="U236" s="215"/>
+      <c r="U236" s="221"/>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A237" s="37" t="s">
@@ -15992,7 +15993,7 @@
       <c r="T237" s="143" t="s">
         <v>656</v>
       </c>
-      <c r="U237" s="215"/>
+      <c r="U237" s="221"/>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A238" s="37" t="s">
@@ -16041,7 +16042,7 @@
       <c r="T238" s="143" t="s">
         <v>657</v>
       </c>
-      <c r="U238" s="215"/>
+      <c r="U238" s="221"/>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A239" s="37" t="s">
@@ -16090,7 +16091,7 @@
       <c r="T239" s="143" t="s">
         <v>658</v>
       </c>
-      <c r="U239" s="215"/>
+      <c r="U239" s="221"/>
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A240" s="37" t="s">
@@ -16602,7 +16603,7 @@
       <c r="T251" s="77" t="s">
         <v>643</v>
       </c>
-      <c r="U251" s="223" t="s">
+      <c r="U251" s="227" t="s">
         <v>680</v>
       </c>
     </row>
@@ -16655,7 +16656,7 @@
       <c r="T252" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U252" s="215"/>
+      <c r="U252" s="221"/>
     </row>
     <row r="253" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A253" s="37" t="s">
@@ -16702,7 +16703,7 @@
       <c r="T253" s="143" t="s">
         <v>659</v>
       </c>
-      <c r="U253" s="215"/>
+      <c r="U253" s="221"/>
     </row>
     <row r="254" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A254" s="37" t="s">
@@ -16749,7 +16750,7 @@
       <c r="T254" s="143" t="s">
         <v>662</v>
       </c>
-      <c r="U254" s="215"/>
+      <c r="U254" s="221"/>
     </row>
     <row r="255" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A255" s="78"/>
@@ -16772,7 +16773,7 @@
       <c r="R255" s="83"/>
       <c r="S255" s="84"/>
       <c r="T255" s="85"/>
-      <c r="U255" s="215"/>
+      <c r="U255" s="221"/>
     </row>
     <row r="256" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A256" s="37" t="s">
@@ -16819,7 +16820,7 @@
       <c r="T256" s="143" t="s">
         <v>643</v>
       </c>
-      <c r="U256" s="215"/>
+      <c r="U256" s="221"/>
     </row>
     <row r="257" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A257" s="37" t="s">
@@ -16870,7 +16871,7 @@
       <c r="T257" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U257" s="215"/>
+      <c r="U257" s="221"/>
     </row>
     <row r="258" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A258" s="37" t="s">
@@ -16917,7 +16918,7 @@
       <c r="T258" s="143" t="s">
         <v>646</v>
       </c>
-      <c r="U258" s="215"/>
+      <c r="U258" s="221"/>
     </row>
     <row r="259" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A259" s="37" t="s">
@@ -16966,7 +16967,7 @@
       <c r="T259" s="143" t="s">
         <v>661</v>
       </c>
-      <c r="U259" s="215"/>
+      <c r="U259" s="221"/>
     </row>
     <row r="260" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A260" s="78"/>
@@ -16989,7 +16990,7 @@
       <c r="R260" s="83"/>
       <c r="S260" s="84"/>
       <c r="T260" s="85"/>
-      <c r="U260" s="215"/>
+      <c r="U260" s="221"/>
     </row>
     <row r="261" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A261" s="37" t="s">
@@ -17036,7 +17037,7 @@
       <c r="T261" s="143" t="s">
         <v>643</v>
       </c>
-      <c r="U261" s="215"/>
+      <c r="U261" s="221"/>
     </row>
     <row r="262" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A262" s="37" t="s">
@@ -17087,7 +17088,7 @@
       <c r="T262" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U262" s="215"/>
+      <c r="U262" s="221"/>
     </row>
     <row r="263" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A263" s="37" t="s">
@@ -17134,7 +17135,7 @@
       <c r="T263" s="143" t="s">
         <v>646</v>
       </c>
-      <c r="U263" s="215"/>
+      <c r="U263" s="221"/>
     </row>
     <row r="264" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A264" s="78"/>
@@ -17157,7 +17158,7 @@
       <c r="R264" s="83"/>
       <c r="S264" s="84"/>
       <c r="T264" s="85"/>
-      <c r="U264" s="215"/>
+      <c r="U264" s="221"/>
     </row>
     <row r="265" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A265" s="70" t="s">
@@ -17204,7 +17205,7 @@
       <c r="T265" s="77" t="s">
         <v>643</v>
       </c>
-      <c r="U265" s="215"/>
+      <c r="U265" s="221"/>
     </row>
     <row r="266" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A266" s="37" t="s">
@@ -17255,7 +17256,7 @@
       <c r="T266" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U266" s="215"/>
+      <c r="U266" s="221"/>
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A267" s="37" t="s">
@@ -17302,7 +17303,7 @@
       <c r="T267" s="143" t="s">
         <v>646</v>
       </c>
-      <c r="U267" s="215"/>
+      <c r="U267" s="221"/>
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A268" s="78"/>
@@ -17325,7 +17326,7 @@
       <c r="R268" s="83"/>
       <c r="S268" s="84"/>
       <c r="T268" s="85"/>
-      <c r="U268" s="215"/>
+      <c r="U268" s="221"/>
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A269" s="70" t="s">
@@ -17372,7 +17373,7 @@
       <c r="T269" s="77" t="s">
         <v>643</v>
       </c>
-      <c r="U269" s="215"/>
+      <c r="U269" s="221"/>
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A270" s="37" t="s">
@@ -17423,7 +17424,7 @@
       <c r="T270" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U270" s="215"/>
+      <c r="U270" s="221"/>
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A271" s="37" t="s">
@@ -17470,7 +17471,7 @@
       <c r="T271" s="143" t="s">
         <v>646</v>
       </c>
-      <c r="U271" s="215"/>
+      <c r="U271" s="221"/>
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A272" s="78"/>
@@ -17493,7 +17494,7 @@
       <c r="R272" s="83"/>
       <c r="S272" s="84"/>
       <c r="T272" s="85"/>
-      <c r="U272" s="215"/>
+      <c r="U272" s="221"/>
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A273" s="70" t="s">
@@ -17540,7 +17541,7 @@
       <c r="T273" s="77" t="s">
         <v>643</v>
       </c>
-      <c r="U273" s="215"/>
+      <c r="U273" s="221"/>
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A274" s="37" t="s">
@@ -17592,7 +17593,7 @@
       <c r="T274" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U274" s="215"/>
+      <c r="U274" s="221"/>
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A275" s="37" t="s">
@@ -17644,7 +17645,7 @@
       <c r="T275" s="143" t="s">
         <v>666</v>
       </c>
-      <c r="U275" s="215"/>
+      <c r="U275" s="221"/>
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A276" s="37" t="s">
@@ -17691,7 +17692,7 @@
       <c r="T276" s="143" t="s">
         <v>662</v>
       </c>
-      <c r="U276" s="215"/>
+      <c r="U276" s="221"/>
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A277" s="78"/>
@@ -17714,7 +17715,7 @@
       <c r="R277" s="83"/>
       <c r="S277" s="84"/>
       <c r="T277" s="85"/>
-      <c r="U277" s="215"/>
+      <c r="U277" s="221"/>
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A278" s="70" t="s">
@@ -17761,7 +17762,7 @@
       <c r="T278" s="77" t="s">
         <v>643</v>
       </c>
-      <c r="U278" s="215"/>
+      <c r="U278" s="221"/>
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A279" s="37" t="s">
@@ -17808,7 +17809,7 @@
       <c r="T279" s="143" t="s">
         <v>643</v>
       </c>
-      <c r="U279" s="215"/>
+      <c r="U279" s="221"/>
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A280" s="37" t="s">
@@ -17855,7 +17856,7 @@
       <c r="T280" s="143" t="s">
         <v>662</v>
       </c>
-      <c r="U280" s="215"/>
+      <c r="U280" s="221"/>
     </row>
     <row r="281" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A281" s="78"/>
@@ -17878,7 +17879,7 @@
       <c r="R281" s="83"/>
       <c r="S281" s="84"/>
       <c r="T281" s="85"/>
-      <c r="U281" s="215"/>
+      <c r="U281" s="221"/>
     </row>
     <row r="282" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A282" s="70" t="s">
@@ -17925,7 +17926,7 @@
       <c r="T282" s="77" t="s">
         <v>643</v>
       </c>
-      <c r="U282" s="215"/>
+      <c r="U282" s="221"/>
     </row>
     <row r="283" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A283" s="37" t="s">
@@ -17974,7 +17975,7 @@
       <c r="T283" s="143" t="s">
         <v>667</v>
       </c>
-      <c r="U283" s="215"/>
+      <c r="U283" s="221"/>
     </row>
     <row r="284" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A284" s="37" t="s">
@@ -18002,7 +18003,7 @@
         <v>1</v>
       </c>
       <c r="I284" s="37" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="J284" s="38" t="s">
         <v>2</v>
@@ -18021,9 +18022,9 @@
         <v>9</v>
       </c>
       <c r="T284" s="143" t="s">
-        <v>1144</v>
-      </c>
-      <c r="U284" s="215"/>
+        <v>1143</v>
+      </c>
+      <c r="U284" s="221"/>
     </row>
     <row r="285" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A285" s="37" t="s">
@@ -18072,7 +18073,7 @@
       <c r="T285" s="143" t="s">
         <v>645</v>
       </c>
-      <c r="U285" s="215"/>
+      <c r="U285" s="221"/>
     </row>
     <row r="286" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A286" s="37" t="s">
@@ -18119,7 +18120,7 @@
       <c r="T286" s="143" t="s">
         <v>647</v>
       </c>
-      <c r="U286" s="215"/>
+      <c r="U286" s="221"/>
     </row>
     <row r="287" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A287" s="37" t="s">
@@ -18166,7 +18167,7 @@
       <c r="T287" s="143" t="s">
         <v>648</v>
       </c>
-      <c r="U287" s="215"/>
+      <c r="U287" s="221"/>
     </row>
     <row r="288" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A288" s="37" t="s">
@@ -18213,7 +18214,7 @@
       <c r="T288" s="143" t="s">
         <v>649</v>
       </c>
-      <c r="U288" s="215"/>
+      <c r="U288" s="221"/>
     </row>
     <row r="289" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A289" s="37" t="s">
@@ -18264,7 +18265,7 @@
       <c r="T289" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U289" s="215"/>
+      <c r="U289" s="221"/>
     </row>
     <row r="290" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A290" s="37" t="s">
@@ -18315,7 +18316,7 @@
       <c r="T290" s="143" t="s">
         <v>666</v>
       </c>
-      <c r="U290" s="215"/>
+      <c r="U290" s="221"/>
     </row>
     <row r="291" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A291" s="37" t="s">
@@ -18364,7 +18365,7 @@
       <c r="T291" s="143" t="s">
         <v>661</v>
       </c>
-      <c r="U291" s="215"/>
+      <c r="U291" s="221"/>
     </row>
     <row r="292" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A292" s="78"/>
@@ -18387,7 +18388,7 @@
       <c r="R292" s="83"/>
       <c r="S292" s="84"/>
       <c r="T292" s="85"/>
-      <c r="U292" s="215"/>
+      <c r="U292" s="221"/>
     </row>
     <row r="293" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A293" s="70" t="s">
@@ -18434,7 +18435,7 @@
       <c r="T293" s="77" t="s">
         <v>643</v>
       </c>
-      <c r="U293" s="215"/>
+      <c r="U293" s="221"/>
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A294" s="37" t="s">
@@ -18483,7 +18484,7 @@
       <c r="T294" s="143" t="s">
         <v>667</v>
       </c>
-      <c r="U294" s="215"/>
+      <c r="U294" s="221"/>
     </row>
     <row r="295" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A295" s="37" t="s">
@@ -18511,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="I295" s="37" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="J295" s="38" t="s">
         <v>2</v>
@@ -18530,9 +18531,9 @@
         <v>9</v>
       </c>
       <c r="T295" s="143" t="s">
-        <v>1144</v>
-      </c>
-      <c r="U295" s="215"/>
+        <v>1143</v>
+      </c>
+      <c r="U295" s="221"/>
     </row>
     <row r="296" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A296" s="37" t="s">
@@ -18581,7 +18582,7 @@
       <c r="T296" s="143" t="s">
         <v>645</v>
       </c>
-      <c r="U296" s="215"/>
+      <c r="U296" s="221"/>
     </row>
     <row r="297" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A297" s="37" t="s">
@@ -18628,7 +18629,7 @@
       <c r="T297" s="143" t="s">
         <v>647</v>
       </c>
-      <c r="U297" s="215"/>
+      <c r="U297" s="221"/>
     </row>
     <row r="298" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A298" s="37" t="s">
@@ -18675,7 +18676,7 @@
       <c r="T298" s="143" t="s">
         <v>648</v>
       </c>
-      <c r="U298" s="215"/>
+      <c r="U298" s="221"/>
     </row>
     <row r="299" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A299" s="37" t="s">
@@ -18722,7 +18723,7 @@
       <c r="T299" s="143" t="s">
         <v>649</v>
       </c>
-      <c r="U299" s="215"/>
+      <c r="U299" s="221"/>
     </row>
     <row r="300" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A300" s="37" t="s">
@@ -18773,7 +18774,7 @@
       <c r="T300" s="143" t="s">
         <v>653</v>
       </c>
-      <c r="U300" s="215"/>
+      <c r="U300" s="221"/>
     </row>
     <row r="301" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A301" s="37" t="s">
@@ -18824,7 +18825,7 @@
       <c r="T301" s="143" t="s">
         <v>666</v>
       </c>
-      <c r="U301" s="215"/>
+      <c r="U301" s="221"/>
     </row>
     <row r="302" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A302" s="37" t="s">
@@ -18873,7 +18874,7 @@
       <c r="T302" s="143" t="s">
         <v>661</v>
       </c>
-      <c r="U302" s="215"/>
+      <c r="U302" s="221"/>
     </row>
     <row r="303" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A303" s="37"/>
@@ -18896,7 +18897,7 @@
       <c r="R303" s="25"/>
       <c r="S303" s="24"/>
       <c r="T303" s="143"/>
-      <c r="U303" s="215"/>
+      <c r="U303" s="221"/>
     </row>
     <row r="304" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A304" s="37"/>
@@ -19496,9 +19497,9 @@
         <v>9</v>
       </c>
       <c r="T323" s="143" t="s">
-        <v>1165</v>
-      </c>
-      <c r="U323" s="217"/>
+        <v>1164</v>
+      </c>
+      <c r="U323" s="215"/>
     </row>
     <row r="324" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A324" s="37" t="s">
@@ -19537,9 +19538,9 @@
         <v>9</v>
       </c>
       <c r="T324" s="54" t="s">
-        <v>1166</v>
-      </c>
-      <c r="U324" s="217"/>
+        <v>1165</v>
+      </c>
+      <c r="U324" s="215"/>
     </row>
     <row r="325" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A325" s="37" t="s">
@@ -19578,9 +19579,9 @@
         <v>9</v>
       </c>
       <c r="T325" s="54" t="s">
-        <v>1167</v>
-      </c>
-      <c r="U325" s="217"/>
+        <v>1166</v>
+      </c>
+      <c r="U325" s="215"/>
     </row>
     <row r="326" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A326" s="37" t="s">
@@ -19621,7 +19622,7 @@
       <c r="T326" s="54" t="s">
         <v>1124</v>
       </c>
-      <c r="U326" s="217"/>
+      <c r="U326" s="215"/>
     </row>
     <row r="327" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A327" s="37" t="s">
@@ -19662,7 +19663,7 @@
       <c r="T327" s="54" t="s">
         <v>451</v>
       </c>
-      <c r="U327" s="217"/>
+      <c r="U327" s="215"/>
     </row>
     <row r="328" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A328" s="37" t="s">
@@ -19703,7 +19704,7 @@
       <c r="T328" s="54" t="s">
         <v>449</v>
       </c>
-      <c r="U328" s="217"/>
+      <c r="U328" s="215"/>
     </row>
     <row r="329" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A329" s="37" t="s">
@@ -19744,7 +19745,7 @@
       <c r="T329" s="54" t="s">
         <v>452</v>
       </c>
-      <c r="U329" s="217"/>
+      <c r="U329" s="215"/>
     </row>
     <row r="330" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A330" s="37" t="s">
@@ -19785,7 +19786,7 @@
       <c r="T330" s="54" t="s">
         <v>450</v>
       </c>
-      <c r="U330" s="217"/>
+      <c r="U330" s="215"/>
     </row>
     <row r="331" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A331" s="37" t="s">
@@ -19826,7 +19827,7 @@
       <c r="T331" s="54" t="s">
         <v>441</v>
       </c>
-      <c r="U331" s="217"/>
+      <c r="U331" s="215"/>
     </row>
     <row r="332" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A332" s="37" t="s">
@@ -19867,7 +19868,7 @@
       <c r="T332" s="54" t="s">
         <v>442</v>
       </c>
-      <c r="U332" s="217"/>
+      <c r="U332" s="215"/>
     </row>
     <row r="333" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A333" s="37" t="s">
@@ -19906,9 +19907,9 @@
         <v>9</v>
       </c>
       <c r="T333" s="54" t="s">
-        <v>1168</v>
-      </c>
-      <c r="U333" s="217"/>
+        <v>1167</v>
+      </c>
+      <c r="U333" s="215"/>
     </row>
     <row r="334" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A334" s="37" t="s">
@@ -19947,7 +19948,7 @@
       <c r="T334" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="U334" s="217"/>
+      <c r="U334" s="215"/>
     </row>
     <row r="335" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A335" s="37"/>
@@ -19970,7 +19971,7 @@
       <c r="R335" s="25"/>
       <c r="S335" s="42"/>
       <c r="T335" s="54"/>
-      <c r="U335" s="217"/>
+      <c r="U335" s="215"/>
     </row>
     <row r="336" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A336" s="37"/>
@@ -19993,7 +19994,7 @@
       <c r="R336" s="25"/>
       <c r="S336" s="42"/>
       <c r="T336" s="54"/>
-      <c r="U336" s="217"/>
+      <c r="U336" s="215"/>
     </row>
     <row r="337" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A337" s="37"/>
@@ -20016,7 +20017,7 @@
       <c r="R337" s="25"/>
       <c r="S337" s="42"/>
       <c r="T337" s="54"/>
-      <c r="U337" s="217"/>
+      <c r="U337" s="215"/>
     </row>
     <row r="338" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A338" s="37"/>
@@ -20039,7 +20040,7 @@
       <c r="R338" s="25"/>
       <c r="S338" s="42"/>
       <c r="T338" s="54"/>
-      <c r="U338" s="217"/>
+      <c r="U338" s="215"/>
     </row>
     <row r="339" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A339" s="37"/>
@@ -20062,7 +20063,7 @@
       <c r="R339" s="25"/>
       <c r="S339" s="42"/>
       <c r="T339" s="54"/>
-      <c r="U339" s="217"/>
+      <c r="U339" s="215"/>
     </row>
     <row r="340" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A340" s="37"/>
@@ -20085,7 +20086,7 @@
       <c r="R340" s="25"/>
       <c r="S340" s="42"/>
       <c r="T340" s="54"/>
-      <c r="U340" s="217"/>
+      <c r="U340" s="215"/>
     </row>
     <row r="341" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A341" s="37"/>
@@ -20108,7 +20109,7 @@
       <c r="R341" s="25"/>
       <c r="S341" s="42"/>
       <c r="T341" s="54"/>
-      <c r="U341" s="217"/>
+      <c r="U341" s="215"/>
     </row>
     <row r="342" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A342" s="37"/>
@@ -20131,7 +20132,7 @@
       <c r="R342" s="25"/>
       <c r="S342" s="42"/>
       <c r="T342" s="54"/>
-      <c r="U342" s="217"/>
+      <c r="U342" s="215"/>
     </row>
     <row r="343" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A343" s="37"/>
@@ -20154,7 +20155,7 @@
       <c r="R343" s="25"/>
       <c r="S343" s="42"/>
       <c r="T343" s="54"/>
-      <c r="U343" s="217"/>
+      <c r="U343" s="215"/>
     </row>
     <row r="344" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A344" s="37"/>
@@ -20177,7 +20178,7 @@
       <c r="R344" s="25"/>
       <c r="S344" s="42"/>
       <c r="T344" s="54"/>
-      <c r="U344" s="217"/>
+      <c r="U344" s="215"/>
     </row>
     <row r="345" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A345" s="37"/>
@@ -20200,7 +20201,7 @@
       <c r="R345" s="25"/>
       <c r="S345" s="42"/>
       <c r="T345" s="54"/>
-      <c r="U345" s="217"/>
+      <c r="U345" s="215"/>
     </row>
     <row r="346" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A346" s="37"/>
@@ -20223,7 +20224,7 @@
       <c r="R346" s="25"/>
       <c r="S346" s="42"/>
       <c r="T346" s="54"/>
-      <c r="U346" s="217"/>
+      <c r="U346" s="215"/>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A347" s="37"/>
@@ -20246,7 +20247,7 @@
       <c r="R347" s="25"/>
       <c r="S347" s="42"/>
       <c r="T347" s="54"/>
-      <c r="U347" s="217"/>
+      <c r="U347" s="215"/>
     </row>
     <row r="348" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A348" s="37"/>
@@ -20269,7 +20270,7 @@
       <c r="R348" s="25"/>
       <c r="S348" s="42"/>
       <c r="T348" s="54"/>
-      <c r="U348" s="217"/>
+      <c r="U348" s="215"/>
     </row>
     <row r="349" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A349" s="37"/>
@@ -20292,7 +20293,7 @@
       <c r="R349" s="25"/>
       <c r="S349" s="42"/>
       <c r="T349" s="54"/>
-      <c r="U349" s="217"/>
+      <c r="U349" s="215"/>
     </row>
     <row r="350" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="44"/>
@@ -20315,7 +20316,7 @@
       <c r="R350" s="66"/>
       <c r="S350" s="90"/>
       <c r="T350" s="50"/>
-      <c r="U350" s="225"/>
+      <c r="U350" s="229"/>
     </row>
     <row r="351" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A351" s="37"/>
@@ -20575,7 +20576,7 @@
       <c r="T358" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="U358" s="216" t="s">
+      <c r="U358" s="220" t="s">
         <v>257</v>
       </c>
     </row>
@@ -20626,7 +20627,7 @@
       <c r="T359" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="U359" s="216"/>
+      <c r="U359" s="220"/>
     </row>
     <row r="360" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A360" s="37" t="s">
@@ -20675,7 +20676,7 @@
       <c r="T360" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="U360" s="216"/>
+      <c r="U360" s="220"/>
     </row>
     <row r="361" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A361" s="37" t="s">
@@ -20724,7 +20725,7 @@
       <c r="T361" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="U361" s="216"/>
+      <c r="U361" s="220"/>
     </row>
     <row r="362" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A362" s="37" t="s">
@@ -20773,7 +20774,7 @@
       <c r="T362" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="U362" s="216"/>
+      <c r="U362" s="220"/>
     </row>
     <row r="363" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A363" s="37" t="s">
@@ -20822,7 +20823,7 @@
       <c r="T363" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="U363" s="216"/>
+      <c r="U363" s="220"/>
     </row>
     <row r="364" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A364" s="37" t="s">
@@ -20871,7 +20872,7 @@
       <c r="T364" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="U364" s="216"/>
+      <c r="U364" s="220"/>
     </row>
     <row r="365" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A365" s="37" t="s">
@@ -20918,7 +20919,7 @@
       <c r="T365" s="54" t="s">
         <v>271</v>
       </c>
-      <c r="U365" s="216"/>
+      <c r="U365" s="220"/>
     </row>
     <row r="366" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A366" s="37" t="s">
@@ -20967,7 +20968,7 @@
       <c r="T366" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="U366" s="216"/>
+      <c r="U366" s="220"/>
     </row>
     <row r="367" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A367" s="37" t="s">
@@ -21014,7 +21015,7 @@
       <c r="T367" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="U367" s="216"/>
+      <c r="U367" s="220"/>
     </row>
     <row r="368" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A368" s="37" t="s">
@@ -21063,7 +21064,7 @@
       <c r="T368" s="54" t="s">
         <v>274</v>
       </c>
-      <c r="U368" s="216"/>
+      <c r="U368" s="220"/>
     </row>
     <row r="369" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A369" s="37" t="s">
@@ -21112,7 +21113,7 @@
       <c r="T369" s="54" t="s">
         <v>489</v>
       </c>
-      <c r="U369" s="216"/>
+      <c r="U369" s="220"/>
     </row>
     <row r="370" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A370" s="37" t="s">
@@ -21159,7 +21160,7 @@
       <c r="T370" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="U370" s="216"/>
+      <c r="U370" s="220"/>
     </row>
     <row r="371" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A371" s="37" t="s">
@@ -21206,7 +21207,7 @@
       <c r="T371" s="54" t="s">
         <v>278</v>
       </c>
-      <c r="U371" s="216"/>
+      <c r="U371" s="220"/>
     </row>
     <row r="372" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A372" s="37" t="s">
@@ -21253,7 +21254,7 @@
       <c r="T372" s="54" t="s">
         <v>280</v>
       </c>
-      <c r="U372" s="216"/>
+      <c r="U372" s="220"/>
     </row>
     <row r="373" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A373" s="37" t="s">
@@ -21300,7 +21301,7 @@
       <c r="T373" s="54" t="s">
         <v>282</v>
       </c>
-      <c r="U373" s="216"/>
+      <c r="U373" s="220"/>
     </row>
     <row r="374" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A374" s="37" t="s">
@@ -21347,7 +21348,7 @@
       <c r="T374" s="54" t="s">
         <v>284</v>
       </c>
-      <c r="U374" s="216"/>
+      <c r="U374" s="220"/>
     </row>
     <row r="375" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A375" s="37" t="s">
@@ -21394,7 +21395,7 @@
       <c r="T375" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="U375" s="216"/>
+      <c r="U375" s="220"/>
     </row>
     <row r="376" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A376" s="78" t="s">
@@ -21441,7 +21442,7 @@
       <c r="T376" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="U376" s="218"/>
+      <c r="U376" s="226"/>
     </row>
     <row r="377" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A377" s="37" t="s">
@@ -21490,7 +21491,7 @@
       <c r="T377" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="U377" s="224" t="s">
+      <c r="U377" s="228" t="s">
         <v>390</v>
       </c>
     </row>
@@ -21541,7 +21542,7 @@
       <c r="T378" s="54" t="s">
         <v>374</v>
       </c>
-      <c r="U378" s="216"/>
+      <c r="U378" s="220"/>
     </row>
     <row r="379" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A379" s="37" t="s">
@@ -21590,7 +21591,7 @@
       <c r="T379" s="54" t="s">
         <v>375</v>
       </c>
-      <c r="U379" s="216"/>
+      <c r="U379" s="220"/>
     </row>
     <row r="380" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A380" s="37" t="s">
@@ -21639,7 +21640,7 @@
       <c r="T380" s="54" t="s">
         <v>376</v>
       </c>
-      <c r="U380" s="216"/>
+      <c r="U380" s="220"/>
     </row>
     <row r="381" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A381" s="37" t="s">
@@ -21686,7 +21687,7 @@
       <c r="T381" s="54" t="s">
         <v>377</v>
       </c>
-      <c r="U381" s="216"/>
+      <c r="U381" s="220"/>
     </row>
     <row r="382" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A382" s="37" t="s">
@@ -21733,7 +21734,7 @@
       <c r="T382" s="54" t="s">
         <v>378</v>
       </c>
-      <c r="U382" s="216"/>
+      <c r="U382" s="220"/>
     </row>
     <row r="383" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A383" s="37" t="s">
@@ -21780,7 +21781,7 @@
       <c r="T383" s="54" t="s">
         <v>379</v>
       </c>
-      <c r="U383" s="216"/>
+      <c r="U383" s="220"/>
     </row>
     <row r="384" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A384" s="37" t="s">
@@ -21829,7 +21830,7 @@
       <c r="T384" s="54" t="s">
         <v>380</v>
       </c>
-      <c r="U384" s="216"/>
+      <c r="U384" s="220"/>
     </row>
     <row r="385" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A385" s="37" t="s">
@@ -21876,7 +21877,7 @@
       <c r="T385" s="54" t="s">
         <v>381</v>
       </c>
-      <c r="U385" s="216"/>
+      <c r="U385" s="220"/>
     </row>
     <row r="386" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A386" s="37" t="s">
@@ -21925,7 +21926,7 @@
       <c r="T386" s="54" t="s">
         <v>382</v>
       </c>
-      <c r="U386" s="216"/>
+      <c r="U386" s="220"/>
     </row>
     <row r="387" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A387" s="37" t="s">
@@ -21972,7 +21973,7 @@
       <c r="T387" s="54" t="s">
         <v>420</v>
       </c>
-      <c r="U387" s="216"/>
+      <c r="U387" s="220"/>
     </row>
     <row r="388" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A388" s="37" t="s">
@@ -22021,7 +22022,7 @@
       <c r="T388" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="U388" s="216"/>
+      <c r="U388" s="220"/>
     </row>
     <row r="389" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A389" s="37" t="s">
@@ -22068,7 +22069,7 @@
       <c r="T389" s="54" t="s">
         <v>383</v>
       </c>
-      <c r="U389" s="216"/>
+      <c r="U389" s="220"/>
     </row>
     <row r="390" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A390" s="37" t="s">
@@ -22117,7 +22118,7 @@
       <c r="T390" s="54" t="s">
         <v>421</v>
       </c>
-      <c r="U390" s="216"/>
+      <c r="U390" s="220"/>
     </row>
     <row r="391" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A391" s="37" t="s">
@@ -22164,7 +22165,7 @@
       <c r="T391" s="54" t="s">
         <v>422</v>
       </c>
-      <c r="U391" s="216"/>
+      <c r="U391" s="220"/>
     </row>
     <row r="392" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A392" s="37" t="s">
@@ -22213,7 +22214,7 @@
       <c r="T392" s="54" t="s">
         <v>384</v>
       </c>
-      <c r="U392" s="216"/>
+      <c r="U392" s="220"/>
     </row>
     <row r="393" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A393" s="37" t="s">
@@ -22262,7 +22263,7 @@
       <c r="T393" s="54" t="s">
         <v>385</v>
       </c>
-      <c r="U393" s="216"/>
+      <c r="U393" s="220"/>
     </row>
     <row r="394" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A394" s="37" t="s">
@@ -22311,7 +22312,7 @@
       <c r="T394" s="54" t="s">
         <v>386</v>
       </c>
-      <c r="U394" s="216"/>
+      <c r="U394" s="220"/>
     </row>
     <row r="395" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A395" s="37" t="s">
@@ -22360,7 +22361,7 @@
       <c r="T395" s="54" t="s">
         <v>387</v>
       </c>
-      <c r="U395" s="216"/>
+      <c r="U395" s="220"/>
     </row>
     <row r="396" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A396" s="37" t="s">
@@ -22409,7 +22410,7 @@
       <c r="T396" s="54" t="s">
         <v>388</v>
       </c>
-      <c r="U396" s="216"/>
+      <c r="U396" s="220"/>
     </row>
     <row r="397" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A397" s="37" t="s">
@@ -22458,7 +22459,7 @@
       <c r="T397" s="54" t="s">
         <v>389</v>
       </c>
-      <c r="U397" s="216"/>
+      <c r="U397" s="220"/>
     </row>
     <row r="398" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A398" s="78" t="s">
@@ -22507,7 +22508,7 @@
       <c r="T398" s="103" t="s">
         <v>834</v>
       </c>
-      <c r="U398" s="218"/>
+      <c r="U398" s="226"/>
     </row>
     <row r="399" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A399" s="70" t="s">
@@ -22605,7 +22606,7 @@
       <c r="T400" s="195" t="s">
         <v>715</v>
       </c>
-      <c r="U400" s="217"/>
+      <c r="U400" s="215"/>
     </row>
     <row r="401" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A401" s="37" t="s">
@@ -22654,7 +22655,7 @@
       <c r="T401" s="195" t="s">
         <v>717</v>
       </c>
-      <c r="U401" s="217"/>
+      <c r="U401" s="215"/>
     </row>
     <row r="402" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A402" s="37" t="s">
@@ -22703,7 +22704,7 @@
       <c r="T402" s="195" t="s">
         <v>718</v>
       </c>
-      <c r="U402" s="217"/>
+      <c r="U402" s="215"/>
     </row>
     <row r="403" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A403" s="37" t="s">
@@ -22752,7 +22753,7 @@
       <c r="T403" s="195" t="s">
         <v>716</v>
       </c>
-      <c r="U403" s="217"/>
+      <c r="U403" s="215"/>
     </row>
     <row r="404" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A404" s="37" t="s">
@@ -22780,7 +22781,7 @@
         <v>1</v>
       </c>
       <c r="I404" s="37" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="J404" s="38" t="s">
         <v>2</v>
@@ -22799,9 +22800,9 @@
         <v>9</v>
       </c>
       <c r="T404" s="195" t="s">
-        <v>1182</v>
-      </c>
-      <c r="U404" s="217"/>
+        <v>1181</v>
+      </c>
+      <c r="U404" s="215"/>
     </row>
     <row r="405" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A405" s="37" t="s">
@@ -22846,9 +22847,9 @@
       </c>
       <c r="S405" s="24"/>
       <c r="T405" s="195" t="s">
-        <v>1183</v>
-      </c>
-      <c r="U405" s="217"/>
+        <v>1182</v>
+      </c>
+      <c r="U405" s="215"/>
     </row>
     <row r="406" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A406" s="37" t="s">
@@ -22895,9 +22896,9 @@
         <v>9</v>
       </c>
       <c r="T406" s="195" t="s">
-        <v>1184</v>
-      </c>
-      <c r="U406" s="217"/>
+        <v>1183</v>
+      </c>
+      <c r="U406" s="215"/>
     </row>
     <row r="407" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A407" s="37" t="s">
@@ -22942,9 +22943,9 @@
       </c>
       <c r="S407" s="42"/>
       <c r="T407" s="195" t="s">
-        <v>1185</v>
-      </c>
-      <c r="U407" s="217"/>
+        <v>1184</v>
+      </c>
+      <c r="U407" s="215"/>
     </row>
     <row r="408" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A408" s="37" t="s">
@@ -22991,9 +22992,9 @@
         <v>9</v>
       </c>
       <c r="T408" s="195" t="s">
-        <v>1186</v>
-      </c>
-      <c r="U408" s="217"/>
+        <v>1185</v>
+      </c>
+      <c r="U408" s="215"/>
     </row>
     <row r="409" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A409" s="78" t="s">
@@ -23042,7 +23043,7 @@
       <c r="T409" s="196" t="s">
         <v>1076</v>
       </c>
-      <c r="U409" s="226"/>
+      <c r="U409" s="230"/>
     </row>
     <row r="410" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A410" s="70" t="s">
@@ -23058,7 +23059,7 @@
         <v>1</v>
       </c>
       <c r="E410" s="70" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F410" s="71" t="s">
         <v>2</v>
@@ -23087,10 +23088,10 @@
       </c>
       <c r="S410" s="76"/>
       <c r="T410" s="213" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="U410" s="219" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="411" spans="1:21" x14ac:dyDescent="0.35">
@@ -23107,7 +23108,7 @@
         <v>1</v>
       </c>
       <c r="E411" s="37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F411" s="38" t="s">
         <v>2</v>
@@ -23138,9 +23139,9 @@
         <v>9</v>
       </c>
       <c r="T411" s="211" t="s">
-        <v>1192</v>
-      </c>
-      <c r="U411" s="217"/>
+        <v>1191</v>
+      </c>
+      <c r="U411" s="215"/>
     </row>
     <row r="412" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A412" s="37" t="s">
@@ -23156,19 +23157,19 @@
         <v>1</v>
       </c>
       <c r="E412" s="34" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F412" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="G412" s="39">
+        <v>1</v>
+      </c>
+      <c r="H412" s="40">
+        <v>1</v>
+      </c>
+      <c r="I412" s="37" t="s">
         <v>1188</v>
-      </c>
-      <c r="F412" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="G412" s="39">
-        <v>1</v>
-      </c>
-      <c r="H412" s="40">
-        <v>1</v>
-      </c>
-      <c r="I412" s="37" t="s">
-        <v>1189</v>
       </c>
       <c r="J412" s="38" t="s">
         <v>2</v>
@@ -23187,9 +23188,9 @@
         <v>9</v>
       </c>
       <c r="T412" s="211" t="s">
-        <v>1193</v>
-      </c>
-      <c r="U412" s="217"/>
+        <v>1192</v>
+      </c>
+      <c r="U412" s="215"/>
     </row>
     <row r="413" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A413" s="37" t="s">
@@ -23205,7 +23206,7 @@
         <v>1</v>
       </c>
       <c r="E413" s="34" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F413" s="38" t="s">
         <v>2</v>
@@ -23236,9 +23237,9 @@
         <v>9</v>
       </c>
       <c r="T413" s="211" t="s">
-        <v>1194</v>
-      </c>
-      <c r="U413" s="217"/>
+        <v>1193</v>
+      </c>
+      <c r="U413" s="215"/>
     </row>
     <row r="414" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A414" s="37" t="s">
@@ -23254,7 +23255,7 @@
         <v>1</v>
       </c>
       <c r="E414" s="37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F414" s="38" t="s">
         <v>2</v>
@@ -23266,7 +23267,7 @@
         <v>1</v>
       </c>
       <c r="I414" s="37" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="J414" s="38" t="s">
         <v>2</v>
@@ -23285,9 +23286,9 @@
         <v>9</v>
       </c>
       <c r="T414" s="211" t="s">
-        <v>1195</v>
-      </c>
-      <c r="U414" s="217"/>
+        <v>1194</v>
+      </c>
+      <c r="U414" s="215"/>
     </row>
     <row r="415" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A415" s="37" t="s">
@@ -23303,7 +23304,7 @@
         <v>1</v>
       </c>
       <c r="E415" s="37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F415" s="38" t="s">
         <v>2</v>
@@ -23315,7 +23316,7 @@
         <v>1</v>
       </c>
       <c r="I415" s="37" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="J415" s="38" t="s">
         <v>2</v>
@@ -23334,9 +23335,9 @@
         <v>9</v>
       </c>
       <c r="T415" s="211" t="s">
-        <v>1196</v>
-      </c>
-      <c r="U415" s="217"/>
+        <v>1195</v>
+      </c>
+      <c r="U415" s="215"/>
     </row>
     <row r="416" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A416" s="37" t="s">
@@ -23352,7 +23353,7 @@
         <v>1</v>
       </c>
       <c r="E416" s="37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F416" s="38" t="s">
         <v>2</v>
@@ -23381,9 +23382,9 @@
       </c>
       <c r="S416" s="24"/>
       <c r="T416" s="211" t="s">
-        <v>1197</v>
-      </c>
-      <c r="U416" s="217"/>
+        <v>1196</v>
+      </c>
+      <c r="U416" s="215"/>
     </row>
     <row r="417" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A417" s="37" t="s">
@@ -23399,7 +23400,7 @@
         <v>1</v>
       </c>
       <c r="E417" s="37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F417" s="38" t="s">
         <v>2</v>
@@ -23430,9 +23431,9 @@
         <v>9</v>
       </c>
       <c r="T417" s="211" t="s">
-        <v>1198</v>
-      </c>
-      <c r="U417" s="217"/>
+        <v>1197</v>
+      </c>
+      <c r="U417" s="215"/>
     </row>
     <row r="418" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A418" s="37" t="s">
@@ -23448,7 +23449,7 @@
         <v>1</v>
       </c>
       <c r="E418" s="37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F418" s="38" t="s">
         <v>2</v>
@@ -23477,9 +23478,9 @@
       </c>
       <c r="S418" s="42"/>
       <c r="T418" s="211" t="s">
-        <v>1199</v>
-      </c>
-      <c r="U418" s="217"/>
+        <v>1198</v>
+      </c>
+      <c r="U418" s="215"/>
     </row>
     <row r="419" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A419" s="37" t="s">
@@ -23495,7 +23496,7 @@
         <v>1</v>
       </c>
       <c r="E419" s="37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F419" s="38" t="s">
         <v>2</v>
@@ -23526,9 +23527,9 @@
         <v>9</v>
       </c>
       <c r="T419" s="211" t="s">
-        <v>1200</v>
-      </c>
-      <c r="U419" s="217"/>
+        <v>1199</v>
+      </c>
+      <c r="U419" s="215"/>
     </row>
     <row r="420" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A420" s="78" t="s">
@@ -23544,7 +23545,7 @@
         <v>1</v>
       </c>
       <c r="E420" s="78" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="F420" s="79" t="s">
         <v>2</v>
@@ -23575,9 +23576,9 @@
         <v>134</v>
       </c>
       <c r="T420" s="212" t="s">
-        <v>1201</v>
-      </c>
-      <c r="U420" s="226"/>
+        <v>1200</v>
+      </c>
+      <c r="U420" s="230"/>
     </row>
     <row r="421" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A421" s="37"/>
@@ -23753,7 +23754,7 @@
         <v>217</v>
       </c>
       <c r="U426" s="143" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="427" spans="1:21" x14ac:dyDescent="0.35">
@@ -23882,7 +23883,7 @@
       <c r="T429" s="143" t="s">
         <v>135</v>
       </c>
-      <c r="U429" s="216" t="s">
+      <c r="U429" s="220" t="s">
         <v>824</v>
       </c>
     </row>
@@ -23928,7 +23929,7 @@
       <c r="T430" s="143" t="s">
         <v>136</v>
       </c>
-      <c r="U430" s="216"/>
+      <c r="U430" s="220"/>
     </row>
     <row r="431" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A431" s="34" t="s">
@@ -23972,7 +23973,7 @@
       <c r="T431" s="143" t="s">
         <v>137</v>
       </c>
-      <c r="U431" s="216"/>
+      <c r="U431" s="220"/>
     </row>
     <row r="432" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A432" s="34" t="s">
@@ -24485,7 +24486,7 @@
       <c r="T443" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="U443" s="216"/>
+      <c r="U443" s="220"/>
     </row>
     <row r="444" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A444" s="34" t="s">
@@ -24529,7 +24530,7 @@
       <c r="T444" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="U444" s="216"/>
+      <c r="U444" s="220"/>
     </row>
     <row r="445" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A445" s="34" t="s">
@@ -24573,7 +24574,7 @@
       <c r="T445" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="U445" s="216"/>
+      <c r="U445" s="220"/>
     </row>
     <row r="446" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A446" s="34" t="s">
@@ -25065,7 +25066,7 @@
         <v>1</v>
       </c>
       <c r="E460" s="37" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F460" s="38" t="s">
         <v>2</v>
@@ -25077,7 +25078,7 @@
         <v>1</v>
       </c>
       <c r="I460" s="34" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="J460" s="35" t="s">
         <v>2</v>
@@ -25098,10 +25099,10 @@
       </c>
       <c r="S460" s="19"/>
       <c r="T460" s="206" t="s">
-        <v>1156</v>
-      </c>
-      <c r="U460" s="217" t="s">
-        <v>1161</v>
+        <v>1155</v>
+      </c>
+      <c r="U460" s="215" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="461" spans="1:21" x14ac:dyDescent="0.35">
@@ -25119,19 +25120,19 @@
         <v>1</v>
       </c>
       <c r="E461" s="37" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F461" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="G461" s="22">
+        <v>1</v>
+      </c>
+      <c r="H461" s="23">
+        <v>1</v>
+      </c>
+      <c r="I461" s="34" t="s">
         <v>1152</v>
-      </c>
-      <c r="F461" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="G461" s="22">
-        <v>1</v>
-      </c>
-      <c r="H461" s="23">
-        <v>1</v>
-      </c>
-      <c r="I461" s="34" t="s">
-        <v>1153</v>
       </c>
       <c r="J461" s="35" t="s">
         <v>2</v>
@@ -25152,9 +25153,9 @@
       </c>
       <c r="S461" s="19"/>
       <c r="T461" s="206" t="s">
-        <v>1154</v>
-      </c>
-      <c r="U461" s="217"/>
+        <v>1153</v>
+      </c>
+      <c r="U461" s="215"/>
     </row>
     <row r="462" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A462" s="34"/>
@@ -25177,7 +25178,7 @@
       <c r="R462" s="105"/>
       <c r="S462" s="19"/>
       <c r="T462" s="206"/>
-      <c r="U462" s="217"/>
+      <c r="U462" s="215"/>
     </row>
     <row r="463" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A463" s="34"/>
@@ -25200,7 +25201,7 @@
       <c r="R463" s="105"/>
       <c r="S463" s="19"/>
       <c r="T463" s="206"/>
-      <c r="U463" s="217"/>
+      <c r="U463" s="215"/>
     </row>
     <row r="464" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A464" s="34"/>
@@ -25223,7 +25224,7 @@
       <c r="R464" s="105"/>
       <c r="S464" s="19"/>
       <c r="T464" s="206"/>
-      <c r="U464" s="217"/>
+      <c r="U464" s="215"/>
     </row>
     <row r="465" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A465" s="34"/>
@@ -25246,7 +25247,7 @@
       <c r="R465" s="105"/>
       <c r="S465" s="19"/>
       <c r="T465" s="206"/>
-      <c r="U465" s="217"/>
+      <c r="U465" s="215"/>
     </row>
     <row r="466" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A466" s="34"/>
@@ -25269,7 +25270,7 @@
       <c r="R466" s="105"/>
       <c r="S466" s="19"/>
       <c r="T466" s="206"/>
-      <c r="U466" s="217"/>
+      <c r="U466" s="215"/>
     </row>
     <row r="467" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A467" s="34"/>
@@ -25292,7 +25293,7 @@
       <c r="R467" s="105"/>
       <c r="S467" s="19"/>
       <c r="T467" s="206"/>
-      <c r="U467" s="217"/>
+      <c r="U467" s="215"/>
     </row>
     <row r="468" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A468" s="34"/>
@@ -25315,7 +25316,7 @@
       <c r="R468" s="105"/>
       <c r="S468" s="19"/>
       <c r="T468" s="206"/>
-      <c r="U468" s="217"/>
+      <c r="U468" s="215"/>
     </row>
     <row r="469" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A469" s="34"/>
@@ -25338,7 +25339,7 @@
       <c r="R469" s="105"/>
       <c r="S469" s="19"/>
       <c r="T469" s="206"/>
-      <c r="U469" s="217"/>
+      <c r="U469" s="215"/>
     </row>
     <row r="470" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A470" s="34"/>
@@ -25361,7 +25362,7 @@
       <c r="R470" s="105"/>
       <c r="S470" s="19"/>
       <c r="T470" s="206"/>
-      <c r="U470" s="217"/>
+      <c r="U470" s="215"/>
     </row>
     <row r="471" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A471" s="34"/>
@@ -25384,7 +25385,7 @@
       <c r="R471" s="105"/>
       <c r="S471" s="19"/>
       <c r="T471" s="206"/>
-      <c r="U471" s="217"/>
+      <c r="U471" s="215"/>
     </row>
     <row r="472" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A472" s="34"/>
@@ -25407,7 +25408,7 @@
       <c r="R472" s="105"/>
       <c r="S472" s="19"/>
       <c r="T472" s="206"/>
-      <c r="U472" s="217"/>
+      <c r="U472" s="215"/>
     </row>
     <row r="473" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A473" s="34"/>
@@ -25430,7 +25431,7 @@
       <c r="R473" s="105"/>
       <c r="S473" s="19"/>
       <c r="T473" s="206"/>
-      <c r="U473" s="217"/>
+      <c r="U473" s="215"/>
     </row>
     <row r="474" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A474" s="34"/>
@@ -25453,7 +25454,7 @@
       <c r="R474" s="105"/>
       <c r="S474" s="19"/>
       <c r="T474" s="206"/>
-      <c r="U474" s="217"/>
+      <c r="U474" s="215"/>
     </row>
     <row r="475" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A475" s="34"/>
@@ -25476,7 +25477,7 @@
       <c r="R475" s="105"/>
       <c r="S475" s="19"/>
       <c r="T475" s="206"/>
-      <c r="U475" s="217"/>
+      <c r="U475" s="215"/>
     </row>
     <row r="476" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A476" s="34"/>
@@ -25499,7 +25500,7 @@
       <c r="R476" s="105"/>
       <c r="S476" s="19"/>
       <c r="T476" s="206"/>
-      <c r="U476" s="217"/>
+      <c r="U476" s="215"/>
     </row>
     <row r="477" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A477" s="34"/>
@@ -25522,7 +25523,7 @@
       <c r="R477" s="105"/>
       <c r="S477" s="19"/>
       <c r="T477" s="206"/>
-      <c r="U477" s="217"/>
+      <c r="U477" s="215"/>
     </row>
     <row r="478" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A478" s="34"/>
@@ -25545,7 +25546,7 @@
       <c r="R478" s="105"/>
       <c r="S478" s="19"/>
       <c r="T478" s="206"/>
-      <c r="U478" s="217"/>
+      <c r="U478" s="215"/>
     </row>
     <row r="479" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A479" s="34"/>
@@ -25568,7 +25569,7 @@
       <c r="R479" s="105"/>
       <c r="S479" s="19"/>
       <c r="T479" s="206"/>
-      <c r="U479" s="217"/>
+      <c r="U479" s="215"/>
     </row>
     <row r="480" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A480" s="34"/>
@@ -25591,7 +25592,7 @@
       <c r="R480" s="105"/>
       <c r="S480" s="19"/>
       <c r="T480" s="206"/>
-      <c r="U480" s="217"/>
+      <c r="U480" s="215"/>
     </row>
     <row r="481" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A481" s="34"/>
@@ -25614,7 +25615,7 @@
       <c r="R481" s="105"/>
       <c r="S481" s="19"/>
       <c r="T481" s="206"/>
-      <c r="U481" s="217"/>
+      <c r="U481" s="215"/>
     </row>
     <row r="482" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A482" s="34"/>
@@ -25637,7 +25638,7 @@
       <c r="R482" s="105"/>
       <c r="S482" s="19"/>
       <c r="T482" s="206"/>
-      <c r="U482" s="217"/>
+      <c r="U482" s="215"/>
     </row>
     <row r="483" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A483" s="34"/>
@@ -25660,7 +25661,7 @@
       <c r="R483" s="105"/>
       <c r="S483" s="19"/>
       <c r="T483" s="206"/>
-      <c r="U483" s="217"/>
+      <c r="U483" s="215"/>
     </row>
     <row r="484" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A484" s="34"/>
@@ -25683,7 +25684,7 @@
       <c r="R484" s="105"/>
       <c r="S484" s="19"/>
       <c r="T484" s="206"/>
-      <c r="U484" s="217"/>
+      <c r="U484" s="215"/>
     </row>
     <row r="485" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A485" s="34"/>
@@ -25706,7 +25707,7 @@
       <c r="R485" s="105"/>
       <c r="S485" s="19"/>
       <c r="T485" s="206"/>
-      <c r="U485" s="217"/>
+      <c r="U485" s="215"/>
     </row>
     <row r="486" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A486" s="34"/>
@@ -25729,7 +25730,7 @@
       <c r="R486" s="105"/>
       <c r="S486" s="19"/>
       <c r="T486" s="206"/>
-      <c r="U486" s="217"/>
+      <c r="U486" s="215"/>
     </row>
     <row r="487" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A487" s="34"/>
@@ -25752,7 +25753,7 @@
       <c r="R487" s="105"/>
       <c r="S487" s="19"/>
       <c r="T487" s="206"/>
-      <c r="U487" s="217"/>
+      <c r="U487" s="215"/>
     </row>
     <row r="488" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A488" s="34"/>
@@ -25775,7 +25776,7 @@
       <c r="R488" s="105"/>
       <c r="S488" s="19"/>
       <c r="T488" s="206"/>
-      <c r="U488" s="217"/>
+      <c r="U488" s="215"/>
     </row>
     <row r="489" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A489" s="34"/>
@@ -25798,7 +25799,7 @@
       <c r="R489" s="105"/>
       <c r="S489" s="19"/>
       <c r="T489" s="206"/>
-      <c r="U489" s="217"/>
+      <c r="U489" s="215"/>
     </row>
     <row r="490" spans="1:21" ht="39" x14ac:dyDescent="0.35">
       <c r="A490" s="34"/>
@@ -25822,7 +25823,7 @@
       <c r="S490" s="19"/>
       <c r="T490" s="206"/>
       <c r="U490" s="203" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="491" spans="1:21" ht="26" x14ac:dyDescent="0.35">
@@ -25847,7 +25848,7 @@
       <c r="S491" s="19"/>
       <c r="T491" s="206"/>
       <c r="U491" s="203" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="492" spans="1:21" x14ac:dyDescent="0.35">
@@ -26033,7 +26034,7 @@
       <c r="S499" s="19"/>
       <c r="T499" s="206"/>
       <c r="U499" s="203" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="500" spans="1:21" x14ac:dyDescent="0.35">
@@ -26219,7 +26220,7 @@
       <c r="S507" s="19"/>
       <c r="T507" s="206"/>
       <c r="U507" s="203" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="508" spans="1:21" x14ac:dyDescent="0.35">
@@ -26662,7 +26663,7 @@
       <c r="T521" s="178" t="s">
         <v>162</v>
       </c>
-      <c r="U521" s="217" t="s">
+      <c r="U521" s="215" t="s">
         <v>691</v>
       </c>
     </row>
@@ -26706,7 +26707,7 @@
       <c r="T522" s="178" t="s">
         <v>163</v>
       </c>
-      <c r="U522" s="217"/>
+      <c r="U522" s="215"/>
     </row>
     <row r="523" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A523" s="34" t="s">
@@ -26748,7 +26749,7 @@
       <c r="T523" s="178" t="s">
         <v>164</v>
       </c>
-      <c r="U523" s="217"/>
+      <c r="U523" s="215"/>
     </row>
     <row r="524" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A524" s="34"/>
@@ -26771,7 +26772,7 @@
       <c r="R524" s="180"/>
       <c r="S524" s="19"/>
       <c r="T524" s="178"/>
-      <c r="U524" s="217"/>
+      <c r="U524" s="215"/>
     </row>
     <row r="525" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A525" s="34"/>
@@ -26794,7 +26795,7 @@
       <c r="R525" s="180"/>
       <c r="S525" s="19"/>
       <c r="T525" s="178"/>
-      <c r="U525" s="217"/>
+      <c r="U525" s="215"/>
     </row>
     <row r="526" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A526" s="34"/>
@@ -26817,7 +26818,7 @@
       <c r="R526" s="180"/>
       <c r="S526" s="19"/>
       <c r="T526" s="178"/>
-      <c r="U526" s="217"/>
+      <c r="U526" s="215"/>
     </row>
     <row r="527" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A527" s="34"/>
@@ -26840,7 +26841,7 @@
       <c r="R527" s="180"/>
       <c r="S527" s="19"/>
       <c r="T527" s="178"/>
-      <c r="U527" s="217"/>
+      <c r="U527" s="215"/>
     </row>
     <row r="528" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A528" s="34"/>
@@ -26863,7 +26864,7 @@
       <c r="R528" s="180"/>
       <c r="S528" s="19"/>
       <c r="T528" s="178"/>
-      <c r="U528" s="217"/>
+      <c r="U528" s="215"/>
     </row>
     <row r="529" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A529" s="34"/>
@@ -26886,7 +26887,7 @@
       <c r="R529" s="180"/>
       <c r="S529" s="19"/>
       <c r="T529" s="178"/>
-      <c r="U529" s="217"/>
+      <c r="U529" s="215"/>
     </row>
     <row r="530" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A530" s="34"/>
@@ -26909,7 +26910,7 @@
       <c r="R530" s="180"/>
       <c r="S530" s="19"/>
       <c r="T530" s="178"/>
-      <c r="U530" s="217"/>
+      <c r="U530" s="215"/>
     </row>
     <row r="531" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A531" s="34"/>
@@ -26932,7 +26933,7 @@
       <c r="R531" s="180"/>
       <c r="S531" s="19"/>
       <c r="T531" s="178"/>
-      <c r="U531" s="217"/>
+      <c r="U531" s="215"/>
     </row>
     <row r="532" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A532" s="34"/>
@@ -26955,7 +26956,7 @@
       <c r="R532" s="180"/>
       <c r="S532" s="19"/>
       <c r="T532" s="178"/>
-      <c r="U532" s="217"/>
+      <c r="U532" s="215"/>
     </row>
     <row r="533" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A533" s="34"/>
@@ -26978,7 +26979,7 @@
       <c r="R533" s="180"/>
       <c r="S533" s="19"/>
       <c r="T533" s="178"/>
-      <c r="U533" s="217"/>
+      <c r="U533" s="215"/>
     </row>
     <row r="534" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A534" s="34"/>
@@ -27001,7 +27002,7 @@
       <c r="R534" s="180"/>
       <c r="S534" s="19"/>
       <c r="T534" s="178"/>
-      <c r="U534" s="217"/>
+      <c r="U534" s="215"/>
     </row>
     <row r="535" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A535" s="34"/>
@@ -27024,7 +27025,7 @@
       <c r="R535" s="180"/>
       <c r="S535" s="19"/>
       <c r="T535" s="178"/>
-      <c r="U535" s="217"/>
+      <c r="U535" s="215"/>
     </row>
     <row r="536" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A536" s="34"/>
@@ -27047,7 +27048,7 @@
       <c r="R536" s="180"/>
       <c r="S536" s="19"/>
       <c r="T536" s="178"/>
-      <c r="U536" s="217"/>
+      <c r="U536" s="215"/>
     </row>
     <row r="537" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A537" s="34"/>
@@ -27070,7 +27071,7 @@
       <c r="R537" s="180"/>
       <c r="S537" s="19"/>
       <c r="T537" s="178"/>
-      <c r="U537" s="217"/>
+      <c r="U537" s="215"/>
     </row>
     <row r="538" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A538" s="34"/>
@@ -27093,7 +27094,7 @@
       <c r="R538" s="180"/>
       <c r="S538" s="19"/>
       <c r="T538" s="178"/>
-      <c r="U538" s="217"/>
+      <c r="U538" s="215"/>
     </row>
     <row r="539" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A539" s="34"/>
@@ -27116,7 +27117,7 @@
       <c r="R539" s="180"/>
       <c r="S539" s="19"/>
       <c r="T539" s="178"/>
-      <c r="U539" s="217"/>
+      <c r="U539" s="215"/>
     </row>
     <row r="540" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A540" s="34"/>
@@ -27139,7 +27140,7 @@
       <c r="R540" s="180"/>
       <c r="S540" s="19"/>
       <c r="T540" s="178"/>
-      <c r="U540" s="217"/>
+      <c r="U540" s="215"/>
     </row>
     <row r="541" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A541" s="34"/>
@@ -27162,7 +27163,7 @@
       <c r="R541" s="180"/>
       <c r="S541" s="19"/>
       <c r="T541" s="178"/>
-      <c r="U541" s="217"/>
+      <c r="U541" s="215"/>
     </row>
     <row r="542" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A542" s="34"/>
@@ -27185,7 +27186,7 @@
       <c r="R542" s="180"/>
       <c r="S542" s="19"/>
       <c r="T542" s="178"/>
-      <c r="U542" s="217"/>
+      <c r="U542" s="215"/>
     </row>
     <row r="543" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A543" s="34"/>
@@ -27208,7 +27209,7 @@
       <c r="R543" s="180"/>
       <c r="S543" s="19"/>
       <c r="T543" s="178"/>
-      <c r="U543" s="217"/>
+      <c r="U543" s="215"/>
     </row>
     <row r="544" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A544" s="34"/>
@@ -27231,7 +27232,7 @@
       <c r="R544" s="180"/>
       <c r="S544" s="19"/>
       <c r="T544" s="178"/>
-      <c r="U544" s="217"/>
+      <c r="U544" s="215"/>
     </row>
     <row r="545" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A545" s="34"/>
@@ -27254,7 +27255,7 @@
       <c r="R545" s="180"/>
       <c r="S545" s="19"/>
       <c r="T545" s="178"/>
-      <c r="U545" s="217"/>
+      <c r="U545" s="215"/>
     </row>
     <row r="546" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A546" s="34"/>
@@ -27277,7 +27278,7 @@
       <c r="R546" s="180"/>
       <c r="S546" s="19"/>
       <c r="T546" s="178"/>
-      <c r="U546" s="217"/>
+      <c r="U546" s="215"/>
     </row>
     <row r="547" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A547" s="34"/>
@@ -27300,7 +27301,7 @@
       <c r="R547" s="180"/>
       <c r="S547" s="19"/>
       <c r="T547" s="178"/>
-      <c r="U547" s="217"/>
+      <c r="U547" s="215"/>
     </row>
     <row r="548" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A548" s="34"/>
@@ -27323,7 +27324,7 @@
       <c r="R548" s="180"/>
       <c r="S548" s="19"/>
       <c r="T548" s="178"/>
-      <c r="U548" s="217"/>
+      <c r="U548" s="215"/>
     </row>
     <row r="549" spans="1:21" ht="52" x14ac:dyDescent="0.35">
       <c r="A549" s="34" t="s">
@@ -27477,7 +27478,7 @@
       <c r="T551" s="54" t="s">
         <v>444</v>
       </c>
-      <c r="U551" s="216" t="s">
+      <c r="U551" s="220" t="s">
         <v>1073</v>
       </c>
     </row>
@@ -27502,7 +27503,7 @@
       <c r="R552" s="25"/>
       <c r="S552" s="42"/>
       <c r="T552" s="54"/>
-      <c r="U552" s="216"/>
+      <c r="U552" s="220"/>
     </row>
     <row r="553" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A553" s="37"/>
@@ -27525,7 +27526,7 @@
       <c r="R553" s="25"/>
       <c r="S553" s="42"/>
       <c r="T553" s="54"/>
-      <c r="U553" s="216"/>
+      <c r="U553" s="220"/>
     </row>
     <row r="554" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A554" s="37"/>
@@ -27548,7 +27549,7 @@
       <c r="R554" s="25"/>
       <c r="S554" s="42"/>
       <c r="T554" s="54"/>
-      <c r="U554" s="216"/>
+      <c r="U554" s="220"/>
     </row>
     <row r="555" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A555" s="37"/>
@@ -27571,7 +27572,7 @@
       <c r="R555" s="25"/>
       <c r="S555" s="42"/>
       <c r="T555" s="54"/>
-      <c r="U555" s="216"/>
+      <c r="U555" s="220"/>
     </row>
     <row r="556" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A556" s="37"/>
@@ -27594,7 +27595,7 @@
       <c r="R556" s="25"/>
       <c r="S556" s="42"/>
       <c r="T556" s="54"/>
-      <c r="U556" s="216"/>
+      <c r="U556" s="220"/>
     </row>
     <row r="557" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A557" s="37"/>
@@ -27617,7 +27618,7 @@
       <c r="R557" s="25"/>
       <c r="S557" s="42"/>
       <c r="T557" s="54"/>
-      <c r="U557" s="216"/>
+      <c r="U557" s="220"/>
     </row>
     <row r="558" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A558" s="37"/>
@@ -27640,7 +27641,7 @@
       <c r="R558" s="25"/>
       <c r="S558" s="42"/>
       <c r="T558" s="193"/>
-      <c r="U558" s="217" t="s">
+      <c r="U558" s="215" t="s">
         <v>1074</v>
       </c>
     </row>
@@ -27665,7 +27666,7 @@
       <c r="R559" s="25"/>
       <c r="S559" s="42"/>
       <c r="T559" s="193"/>
-      <c r="U559" s="217"/>
+      <c r="U559" s="215"/>
     </row>
     <row r="560" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A560" s="37"/>
@@ -27688,7 +27689,7 @@
       <c r="R560" s="25"/>
       <c r="S560" s="42"/>
       <c r="T560" s="193"/>
-      <c r="U560" s="217"/>
+      <c r="U560" s="215"/>
     </row>
     <row r="561" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A561" s="37"/>
@@ -27711,7 +27712,7 @@
       <c r="R561" s="25"/>
       <c r="S561" s="42"/>
       <c r="T561" s="193"/>
-      <c r="U561" s="217"/>
+      <c r="U561" s="215"/>
     </row>
     <row r="562" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A562" s="37"/>
@@ -27734,7 +27735,7 @@
       <c r="R562" s="25"/>
       <c r="S562" s="42"/>
       <c r="T562" s="193"/>
-      <c r="U562" s="217"/>
+      <c r="U562" s="215"/>
     </row>
     <row r="563" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A563" s="37"/>
@@ -27757,7 +27758,7 @@
       <c r="R563" s="25"/>
       <c r="S563" s="42"/>
       <c r="T563" s="193"/>
-      <c r="U563" s="217"/>
+      <c r="U563" s="215"/>
     </row>
     <row r="564" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A564" s="37"/>
@@ -27780,7 +27781,7 @@
       <c r="R564" s="25"/>
       <c r="S564" s="42"/>
       <c r="T564" s="193"/>
-      <c r="U564" s="217"/>
+      <c r="U564" s="215"/>
     </row>
     <row r="565" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A565" s="37"/>
@@ -28240,7 +28241,7 @@
       <c r="R584" s="25"/>
       <c r="S584" s="42"/>
       <c r="T584" s="177"/>
-      <c r="U584" s="217" t="s">
+      <c r="U584" s="215" t="s">
         <v>1075</v>
       </c>
     </row>
@@ -28265,7 +28266,7 @@
       <c r="R585" s="25"/>
       <c r="S585" s="42"/>
       <c r="T585" s="177"/>
-      <c r="U585" s="217"/>
+      <c r="U585" s="215"/>
     </row>
     <row r="586" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A586" s="37"/>
@@ -28288,7 +28289,7 @@
       <c r="R586" s="25"/>
       <c r="S586" s="42"/>
       <c r="T586" s="177"/>
-      <c r="U586" s="217"/>
+      <c r="U586" s="215"/>
     </row>
     <row r="587" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A587" s="37"/>
@@ -28311,7 +28312,7 @@
       <c r="R587" s="25"/>
       <c r="S587" s="42"/>
       <c r="T587" s="177"/>
-      <c r="U587" s="217"/>
+      <c r="U587" s="215"/>
     </row>
     <row r="588" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A588" s="37"/>
@@ -28334,7 +28335,7 @@
       <c r="R588" s="25"/>
       <c r="S588" s="42"/>
       <c r="T588" s="177"/>
-      <c r="U588" s="217"/>
+      <c r="U588" s="215"/>
     </row>
     <row r="589" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A589" s="37"/>
@@ -28357,7 +28358,7 @@
       <c r="R589" s="25"/>
       <c r="S589" s="42"/>
       <c r="T589" s="193"/>
-      <c r="U589" s="217"/>
+      <c r="U589" s="215"/>
     </row>
     <row r="590" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A590" s="37"/>
@@ -28380,7 +28381,7 @@
       <c r="R590" s="25"/>
       <c r="S590" s="42"/>
       <c r="T590" s="177"/>
-      <c r="U590" s="217"/>
+      <c r="U590" s="215"/>
     </row>
     <row r="591" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A591" s="37"/>
@@ -28403,7 +28404,7 @@
       <c r="R591" s="25"/>
       <c r="S591" s="42"/>
       <c r="T591" s="177"/>
-      <c r="U591" s="217"/>
+      <c r="U591" s="215"/>
     </row>
     <row r="592" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A592" s="37"/>
@@ -28426,7 +28427,7 @@
       <c r="R592" s="25"/>
       <c r="S592" s="42"/>
       <c r="T592" s="177"/>
-      <c r="U592" s="217"/>
+      <c r="U592" s="215"/>
     </row>
     <row r="593" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A593" s="37"/>
@@ -28867,7 +28868,7 @@
       <c r="T610" s="54" t="s">
         <v>316</v>
       </c>
-      <c r="U610" s="216" t="s">
+      <c r="U610" s="220" t="s">
         <v>944</v>
       </c>
     </row>
@@ -28919,7 +28920,7 @@
       <c r="T611" s="54" t="s">
         <v>317</v>
       </c>
-      <c r="U611" s="216"/>
+      <c r="U611" s="220"/>
     </row>
     <row r="612" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A612" s="34" t="s">
@@ -28969,7 +28970,7 @@
       <c r="T612" s="54" t="s">
         <v>318</v>
       </c>
-      <c r="U612" s="216"/>
+      <c r="U612" s="220"/>
     </row>
     <row r="613" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A613" s="37"/>
@@ -28992,7 +28993,7 @@
       <c r="R613" s="25"/>
       <c r="S613" s="42"/>
       <c r="T613" s="54"/>
-      <c r="U613" s="216"/>
+      <c r="U613" s="220"/>
     </row>
     <row r="614" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A614" s="37"/>
@@ -29015,7 +29016,7 @@
       <c r="R614" s="25"/>
       <c r="S614" s="42"/>
       <c r="T614" s="54"/>
-      <c r="U614" s="216"/>
+      <c r="U614" s="220"/>
     </row>
     <row r="615" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A615" s="37"/>
@@ -29038,7 +29039,7 @@
       <c r="R615" s="25"/>
       <c r="S615" s="42"/>
       <c r="T615" s="54"/>
-      <c r="U615" s="216"/>
+      <c r="U615" s="220"/>
     </row>
     <row r="616" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A616" s="37"/>
@@ -29061,7 +29062,7 @@
       <c r="R616" s="25"/>
       <c r="S616" s="42"/>
       <c r="T616" s="54"/>
-      <c r="U616" s="216"/>
+      <c r="U616" s="220"/>
     </row>
     <row r="617" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A617" s="37"/>
@@ -29084,7 +29085,7 @@
       <c r="R617" s="25"/>
       <c r="S617" s="42"/>
       <c r="T617" s="54"/>
-      <c r="U617" s="216"/>
+      <c r="U617" s="220"/>
     </row>
     <row r="618" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A618" s="37"/>
@@ -29107,7 +29108,7 @@
       <c r="R618" s="25"/>
       <c r="S618" s="42"/>
       <c r="T618" s="54"/>
-      <c r="U618" s="216"/>
+      <c r="U618" s="220"/>
     </row>
     <row r="619" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A619" s="37"/>
@@ -29130,7 +29131,7 @@
       <c r="R619" s="25"/>
       <c r="S619" s="42"/>
       <c r="T619" s="54"/>
-      <c r="U619" s="216"/>
+      <c r="U619" s="220"/>
     </row>
     <row r="620" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A620" s="37"/>
@@ -29153,7 +29154,7 @@
       <c r="R620" s="25"/>
       <c r="S620" s="42"/>
       <c r="T620" s="54"/>
-      <c r="U620" s="216"/>
+      <c r="U620" s="220"/>
     </row>
     <row r="621" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A621" s="37"/>
@@ -29176,7 +29177,7 @@
       <c r="R621" s="25"/>
       <c r="S621" s="42"/>
       <c r="T621" s="54"/>
-      <c r="U621" s="216"/>
+      <c r="U621" s="220"/>
     </row>
     <row r="622" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A622" s="37"/>
@@ -29199,7 +29200,7 @@
       <c r="R622" s="25"/>
       <c r="S622" s="42"/>
       <c r="T622" s="54"/>
-      <c r="U622" s="216"/>
+      <c r="U622" s="220"/>
     </row>
     <row r="623" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A623" s="37"/>
@@ -29222,7 +29223,7 @@
       <c r="R623" s="25"/>
       <c r="S623" s="42"/>
       <c r="T623" s="54"/>
-      <c r="U623" s="216"/>
+      <c r="U623" s="220"/>
     </row>
     <row r="624" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A624" s="37"/>
@@ -29245,7 +29246,7 @@
       <c r="R624" s="25"/>
       <c r="S624" s="42"/>
       <c r="T624" s="54"/>
-      <c r="U624" s="216"/>
+      <c r="U624" s="220"/>
     </row>
     <row r="625" spans="1:21" ht="377" x14ac:dyDescent="0.35">
       <c r="A625" s="34" t="s">
@@ -29466,7 +29467,7 @@
         <v>1</v>
       </c>
       <c r="I629" s="34" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="J629" s="38" t="s">
         <v>2</v>
@@ -29485,10 +29486,10 @@
         <v>9</v>
       </c>
       <c r="T629" s="143" t="s">
+        <v>1147</v>
+      </c>
+      <c r="U629" s="64" t="s">
         <v>1148</v>
-      </c>
-      <c r="U629" s="64" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="630" spans="1:21" ht="39" x14ac:dyDescent="0.35">
@@ -29518,7 +29519,7 @@
         <v>1</v>
       </c>
       <c r="I630" s="34" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="J630" s="38" t="s">
         <v>2</v>
@@ -29537,10 +29538,10 @@
         <v>9</v>
       </c>
       <c r="T630" s="143" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="U630" s="64" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="631" spans="1:21" x14ac:dyDescent="0.35">
@@ -29693,7 +29694,7 @@
       <c r="T633" s="143" t="s">
         <v>539</v>
       </c>
-      <c r="U633" s="215" t="s">
+      <c r="U633" s="221" t="s">
         <v>542</v>
       </c>
     </row>
@@ -29745,7 +29746,7 @@
       <c r="T634" s="143" t="s">
         <v>540</v>
       </c>
-      <c r="U634" s="215"/>
+      <c r="U634" s="221"/>
     </row>
     <row r="635" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A635" s="34" t="s">
@@ -29795,7 +29796,7 @@
       <c r="T635" s="143" t="s">
         <v>541</v>
       </c>
-      <c r="U635" s="215"/>
+      <c r="U635" s="221"/>
     </row>
     <row r="636" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A636" s="34" t="s">
@@ -29845,7 +29846,7 @@
       <c r="T636" s="179" t="s">
         <v>536</v>
       </c>
-      <c r="U636" s="215" t="s">
+      <c r="U636" s="221" t="s">
         <v>543</v>
       </c>
     </row>
@@ -29897,7 +29898,7 @@
       <c r="T637" s="179" t="s">
         <v>537</v>
       </c>
-      <c r="U637" s="215"/>
+      <c r="U637" s="221"/>
     </row>
     <row r="638" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A638" s="97" t="s">
@@ -29947,7 +29948,7 @@
       <c r="T638" s="85" t="s">
         <v>538</v>
       </c>
-      <c r="U638" s="227"/>
+      <c r="U638" s="222"/>
     </row>
     <row r="639" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A639" s="34" t="s">
@@ -30006,7 +30007,7 @@
         <v>1</v>
       </c>
       <c r="E640" s="37" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F640" s="38" t="s">
         <v>2</v>
@@ -30018,7 +30019,7 @@
         <v>1</v>
       </c>
       <c r="I640" s="34" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="J640" s="35" t="s">
         <v>2</v>
@@ -30039,7 +30040,7 @@
       </c>
       <c r="S640" s="19"/>
       <c r="T640" s="206" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="U640" s="206"/>
     </row>
@@ -30058,19 +30059,19 @@
         <v>1</v>
       </c>
       <c r="E641" s="37" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F641" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="G641" s="22">
+        <v>1</v>
+      </c>
+      <c r="H641" s="23">
+        <v>1</v>
+      </c>
+      <c r="I641" s="34" t="s">
         <v>1152</v>
-      </c>
-      <c r="F641" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="G641" s="22">
-        <v>1</v>
-      </c>
-      <c r="H641" s="23">
-        <v>1</v>
-      </c>
-      <c r="I641" s="34" t="s">
-        <v>1153</v>
       </c>
       <c r="J641" s="35" t="s">
         <v>2</v>
@@ -30091,7 +30092,7 @@
       </c>
       <c r="S641" s="19"/>
       <c r="T641" s="206" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="U641" s="206"/>
     </row>
@@ -30938,7 +30939,7 @@
         <v>1</v>
       </c>
       <c r="I660" s="34" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="J660" s="38" t="s">
         <v>2</v>
@@ -30957,7 +30958,7 @@
         <v>9</v>
       </c>
       <c r="T660" s="143" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="U660" s="64"/>
     </row>
@@ -30988,7 +30989,7 @@
         <v>1</v>
       </c>
       <c r="I661" s="34" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="J661" s="38" t="s">
         <v>2</v>
@@ -31007,7 +31008,7 @@
         <v>9</v>
       </c>
       <c r="T661" s="143" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="U661" s="64"/>
     </row>
@@ -32052,7 +32053,7 @@
       <c r="T687" s="54" t="s">
         <v>481</v>
       </c>
-      <c r="U687" s="216" t="s">
+      <c r="U687" s="220" t="s">
         <v>172</v>
       </c>
     </row>
@@ -32096,7 +32097,7 @@
       </c>
       <c r="S688" s="24"/>
       <c r="T688" s="54"/>
-      <c r="U688" s="216"/>
+      <c r="U688" s="220"/>
     </row>
     <row r="689" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A689" s="34" t="s">
@@ -32138,7 +32139,7 @@
       </c>
       <c r="S689" s="24"/>
       <c r="T689" s="54"/>
-      <c r="U689" s="216"/>
+      <c r="U689" s="220"/>
     </row>
     <row r="690" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A690" s="34" t="s">
@@ -32180,7 +32181,7 @@
       </c>
       <c r="S690" s="24"/>
       <c r="T690" s="54"/>
-      <c r="U690" s="216"/>
+      <c r="U690" s="220"/>
     </row>
     <row r="691" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A691" s="34" t="s">
@@ -32264,7 +32265,7 @@
       <c r="T692" s="54" t="s">
         <v>483</v>
       </c>
-      <c r="U692" s="216" t="s">
+      <c r="U692" s="220" t="s">
         <v>173</v>
       </c>
     </row>
@@ -32308,7 +32309,7 @@
       </c>
       <c r="S693" s="24"/>
       <c r="T693" s="54"/>
-      <c r="U693" s="216"/>
+      <c r="U693" s="220"/>
     </row>
     <row r="694" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A694" s="34" t="s">
@@ -32350,7 +32351,7 @@
       </c>
       <c r="S694" s="24"/>
       <c r="T694" s="54"/>
-      <c r="U694" s="216"/>
+      <c r="U694" s="220"/>
     </row>
     <row r="695" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A695" s="34" t="s">
@@ -32392,7 +32393,7 @@
       </c>
       <c r="S695" s="24"/>
       <c r="T695" s="54"/>
-      <c r="U695" s="216"/>
+      <c r="U695" s="220"/>
     </row>
     <row r="696" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A696" s="34" t="s">
@@ -32434,7 +32435,7 @@
       </c>
       <c r="S696" s="24"/>
       <c r="T696" s="54"/>
-      <c r="U696" s="216"/>
+      <c r="U696" s="220"/>
     </row>
     <row r="697" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A697" s="97" t="s">
@@ -32476,7 +32477,7 @@
       </c>
       <c r="S697" s="84"/>
       <c r="T697" s="103"/>
-      <c r="U697" s="218"/>
+      <c r="U697" s="226"/>
     </row>
     <row r="698" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A698" s="34" t="s">
@@ -32972,7 +32973,7 @@
       <c r="T709" s="54" t="s">
         <v>481</v>
       </c>
-      <c r="U709" s="216"/>
+      <c r="U709" s="220"/>
     </row>
     <row r="710" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A710" s="34" t="s">
@@ -33014,7 +33015,7 @@
       </c>
       <c r="S710" s="24"/>
       <c r="T710" s="54"/>
-      <c r="U710" s="216"/>
+      <c r="U710" s="220"/>
     </row>
     <row r="711" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A711" s="34" t="s">
@@ -33056,7 +33057,7 @@
       </c>
       <c r="S711" s="24"/>
       <c r="T711" s="54"/>
-      <c r="U711" s="216"/>
+      <c r="U711" s="220"/>
     </row>
     <row r="712" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A712" s="34" t="s">
@@ -33098,7 +33099,7 @@
       </c>
       <c r="S712" s="24"/>
       <c r="T712" s="54"/>
-      <c r="U712" s="216"/>
+      <c r="U712" s="220"/>
     </row>
     <row r="713" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A713" s="34" t="s">
@@ -33182,7 +33183,7 @@
       <c r="T714" s="54" t="s">
         <v>483</v>
       </c>
-      <c r="U714" s="216"/>
+      <c r="U714" s="220"/>
     </row>
     <row r="715" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A715" s="34" t="s">
@@ -33224,7 +33225,7 @@
       </c>
       <c r="S715" s="24"/>
       <c r="T715" s="54"/>
-      <c r="U715" s="216"/>
+      <c r="U715" s="220"/>
     </row>
     <row r="716" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A716" s="34" t="s">
@@ -33266,7 +33267,7 @@
       </c>
       <c r="S716" s="24"/>
       <c r="T716" s="54"/>
-      <c r="U716" s="216"/>
+      <c r="U716" s="220"/>
     </row>
     <row r="717" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A717" s="34" t="s">
@@ -33308,7 +33309,7 @@
       </c>
       <c r="S717" s="24"/>
       <c r="T717" s="54"/>
-      <c r="U717" s="216"/>
+      <c r="U717" s="220"/>
     </row>
     <row r="718" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A718" s="34" t="s">
@@ -33350,7 +33351,7 @@
       </c>
       <c r="S718" s="24"/>
       <c r="T718" s="54"/>
-      <c r="U718" s="216"/>
+      <c r="U718" s="220"/>
     </row>
     <row r="719" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A719" s="97" t="s">
@@ -33392,7 +33393,7 @@
       </c>
       <c r="S719" s="84"/>
       <c r="T719" s="103"/>
-      <c r="U719" s="218"/>
+      <c r="U719" s="226"/>
     </row>
     <row r="720" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A720" s="37"/>
@@ -33616,7 +33617,7 @@
       <c r="T727" s="54" t="s">
         <v>886</v>
       </c>
-      <c r="U727" s="217"/>
+      <c r="U727" s="215"/>
     </row>
     <row r="728" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A728" s="37" t="s">
@@ -33655,7 +33656,7 @@
       <c r="T728" s="54" t="s">
         <v>887</v>
       </c>
-      <c r="U728" s="217"/>
+      <c r="U728" s="215"/>
     </row>
     <row r="729" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A729" s="37" t="s">
@@ -33776,7 +33777,7 @@
       <c r="T731" s="54" t="s">
         <v>811</v>
       </c>
-      <c r="U731" s="217" t="s">
+      <c r="U731" s="215" t="s">
         <v>804</v>
       </c>
     </row>
@@ -33817,7 +33818,7 @@
       <c r="T732" s="54" t="s">
         <v>812</v>
       </c>
-      <c r="U732" s="217"/>
+      <c r="U732" s="215"/>
     </row>
     <row r="733" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A733" s="37"/>
@@ -33840,7 +33841,7 @@
       <c r="R733" s="86"/>
       <c r="S733" s="24"/>
       <c r="T733" s="54"/>
-      <c r="U733" s="217"/>
+      <c r="U733" s="215"/>
     </row>
     <row r="734" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A734" s="37"/>
@@ -33863,7 +33864,7 @@
       <c r="R734" s="86"/>
       <c r="S734" s="24"/>
       <c r="T734" s="54"/>
-      <c r="U734" s="217"/>
+      <c r="U734" s="215"/>
     </row>
     <row r="735" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A735" s="37"/>
@@ -33886,7 +33887,7 @@
       <c r="R735" s="86"/>
       <c r="S735" s="24"/>
       <c r="T735" s="54"/>
-      <c r="U735" s="217"/>
+      <c r="U735" s="215"/>
     </row>
     <row r="736" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A736" s="37"/>
@@ -33909,7 +33910,7 @@
       <c r="R736" s="86"/>
       <c r="S736" s="24"/>
       <c r="T736" s="54"/>
-      <c r="U736" s="217"/>
+      <c r="U736" s="215"/>
     </row>
     <row r="737" spans="1:21" ht="65" x14ac:dyDescent="0.35">
       <c r="A737" s="37" t="s">
@@ -33995,7 +33996,7 @@
       <c r="T738" s="54" t="s">
         <v>424</v>
       </c>
-      <c r="U738" s="215" t="s">
+      <c r="U738" s="221" t="s">
         <v>1070</v>
       </c>
     </row>
@@ -34042,7 +34043,7 @@
       <c r="T739" s="54" t="s">
         <v>430</v>
       </c>
-      <c r="U739" s="215"/>
+      <c r="U739" s="221"/>
     </row>
     <row r="740" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A740" s="37" t="s">
@@ -34087,7 +34088,7 @@
       <c r="T740" s="54" t="s">
         <v>423</v>
       </c>
-      <c r="U740" s="215"/>
+      <c r="U740" s="221"/>
     </row>
     <row r="741" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A741" s="37" t="s">
@@ -34132,7 +34133,7 @@
       <c r="T741" s="54" t="s">
         <v>424</v>
       </c>
-      <c r="U741" s="215"/>
+      <c r="U741" s="221"/>
     </row>
     <row r="742" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A742" s="37" t="s">
@@ -34177,7 +34178,7 @@
       <c r="T742" s="54" t="s">
         <v>430</v>
       </c>
-      <c r="U742" s="215"/>
+      <c r="U742" s="221"/>
     </row>
     <row r="743" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A743" s="37" t="s">
@@ -34222,7 +34223,7 @@
       <c r="T743" s="54" t="s">
         <v>423</v>
       </c>
-      <c r="U743" s="215"/>
+      <c r="U743" s="221"/>
     </row>
     <row r="744" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A744" s="37" t="s">
@@ -34267,7 +34268,7 @@
       <c r="T744" s="54" t="s">
         <v>424</v>
       </c>
-      <c r="U744" s="215"/>
+      <c r="U744" s="221"/>
     </row>
     <row r="745" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A745" s="37" t="s">
@@ -34312,7 +34313,7 @@
       <c r="T745" s="54" t="s">
         <v>430</v>
       </c>
-      <c r="U745" s="215"/>
+      <c r="U745" s="221"/>
     </row>
     <row r="746" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A746" s="37" t="s">
@@ -34357,7 +34358,7 @@
       <c r="T746" s="54" t="s">
         <v>423</v>
       </c>
-      <c r="U746" s="215"/>
+      <c r="U746" s="221"/>
     </row>
     <row r="747" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A747" s="37" t="s">
@@ -34402,7 +34403,7 @@
       <c r="T747" s="54" t="s">
         <v>424</v>
       </c>
-      <c r="U747" s="215"/>
+      <c r="U747" s="221"/>
     </row>
     <row r="748" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A748" s="37" t="s">
@@ -34447,7 +34448,7 @@
       <c r="T748" s="54" t="s">
         <v>430</v>
       </c>
-      <c r="U748" s="215"/>
+      <c r="U748" s="221"/>
     </row>
     <row r="749" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A749" s="37" t="s">
@@ -34492,7 +34493,7 @@
       <c r="T749" s="54" t="s">
         <v>423</v>
       </c>
-      <c r="U749" s="215"/>
+      <c r="U749" s="221"/>
     </row>
     <row r="750" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A750" s="37"/>
@@ -34515,7 +34516,7 @@
       <c r="R750" s="86"/>
       <c r="S750" s="24"/>
       <c r="T750" s="54"/>
-      <c r="U750" s="215"/>
+      <c r="U750" s="221"/>
     </row>
     <row r="751" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A751" s="37"/>
@@ -34538,7 +34539,7 @@
       <c r="R751" s="86"/>
       <c r="S751" s="24"/>
       <c r="T751" s="172"/>
-      <c r="U751" s="215"/>
+      <c r="U751" s="221"/>
     </row>
     <row r="752" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A752" s="37"/>
@@ -34561,7 +34562,7 @@
       <c r="R752" s="86"/>
       <c r="S752" s="24"/>
       <c r="T752" s="172"/>
-      <c r="U752" s="215"/>
+      <c r="U752" s="221"/>
     </row>
     <row r="753" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A753" s="37"/>
@@ -34584,7 +34585,7 @@
       <c r="R753" s="86"/>
       <c r="S753" s="24"/>
       <c r="T753" s="172"/>
-      <c r="U753" s="215"/>
+      <c r="U753" s="221"/>
     </row>
     <row r="754" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A754" s="37"/>
@@ -34607,7 +34608,7 @@
       <c r="R754" s="86"/>
       <c r="S754" s="24"/>
       <c r="T754" s="172"/>
-      <c r="U754" s="215"/>
+      <c r="U754" s="221"/>
     </row>
     <row r="755" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A755" s="37"/>
@@ -34630,7 +34631,7 @@
       <c r="R755" s="86"/>
       <c r="S755" s="24"/>
       <c r="T755" s="172"/>
-      <c r="U755" s="215"/>
+      <c r="U755" s="221"/>
     </row>
     <row r="756" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A756" s="37"/>
@@ -34653,7 +34654,7 @@
       <c r="R756" s="86"/>
       <c r="S756" s="24"/>
       <c r="T756" s="172"/>
-      <c r="U756" s="215"/>
+      <c r="U756" s="221"/>
     </row>
     <row r="757" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A757" s="37"/>
@@ -34676,7 +34677,7 @@
       <c r="R757" s="86"/>
       <c r="S757" s="24"/>
       <c r="T757" s="172"/>
-      <c r="U757" s="215"/>
+      <c r="U757" s="221"/>
     </row>
     <row r="758" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A758" s="37"/>
@@ -34699,7 +34700,7 @@
       <c r="R758" s="86"/>
       <c r="S758" s="24"/>
       <c r="T758" s="172"/>
-      <c r="U758" s="215"/>
+      <c r="U758" s="221"/>
     </row>
     <row r="759" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A759" s="37"/>
@@ -34722,7 +34723,7 @@
       <c r="R759" s="86"/>
       <c r="S759" s="24"/>
       <c r="T759" s="172"/>
-      <c r="U759" s="215"/>
+      <c r="U759" s="221"/>
     </row>
     <row r="760" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A760" s="37"/>
@@ -34745,7 +34746,7 @@
       <c r="R760" s="86"/>
       <c r="S760" s="24"/>
       <c r="T760" s="172"/>
-      <c r="U760" s="215"/>
+      <c r="U760" s="221"/>
     </row>
     <row r="761" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A761" s="37"/>
@@ -34768,7 +34769,7 @@
       <c r="R761" s="86"/>
       <c r="S761" s="24"/>
       <c r="T761" s="172"/>
-      <c r="U761" s="215"/>
+      <c r="U761" s="221"/>
     </row>
     <row r="762" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A762" s="37"/>
@@ -34791,7 +34792,7 @@
       <c r="R762" s="86"/>
       <c r="S762" s="24"/>
       <c r="T762" s="172"/>
-      <c r="U762" s="215"/>
+      <c r="U762" s="221"/>
     </row>
     <row r="763" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A763" s="37"/>
@@ -34814,7 +34815,7 @@
       <c r="R763" s="86"/>
       <c r="S763" s="24"/>
       <c r="T763" s="172"/>
-      <c r="U763" s="215"/>
+      <c r="U763" s="221"/>
     </row>
     <row r="764" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A764" s="37"/>
@@ -34837,7 +34838,7 @@
       <c r="R764" s="86"/>
       <c r="S764" s="24"/>
       <c r="T764" s="172"/>
-      <c r="U764" s="215"/>
+      <c r="U764" s="221"/>
     </row>
     <row r="765" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A765" s="37"/>
@@ -34860,7 +34861,7 @@
       <c r="R765" s="86"/>
       <c r="S765" s="24"/>
       <c r="T765" s="191"/>
-      <c r="U765" s="215"/>
+      <c r="U765" s="221"/>
     </row>
     <row r="766" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A766" s="37"/>
@@ -34883,7 +34884,7 @@
       <c r="R766" s="86"/>
       <c r="S766" s="24"/>
       <c r="T766" s="172"/>
-      <c r="U766" s="215"/>
+      <c r="U766" s="221"/>
     </row>
     <row r="767" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A767" s="37"/>
@@ -34906,7 +34907,7 @@
       <c r="R767" s="86"/>
       <c r="S767" s="24"/>
       <c r="T767" s="172"/>
-      <c r="U767" s="215"/>
+      <c r="U767" s="221"/>
     </row>
     <row r="768" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A768" s="37"/>
@@ -34929,7 +34930,7 @@
       <c r="R768" s="86"/>
       <c r="S768" s="24"/>
       <c r="T768" s="172"/>
-      <c r="U768" s="215"/>
+      <c r="U768" s="221"/>
     </row>
     <row r="769" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A769" s="37"/>
@@ -34952,7 +34953,7 @@
       <c r="R769" s="86"/>
       <c r="S769" s="24"/>
       <c r="T769" s="54"/>
-      <c r="U769" s="215"/>
+      <c r="U769" s="221"/>
     </row>
     <row r="770" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A770" s="37"/>
@@ -34975,7 +34976,7 @@
       <c r="R770" s="86"/>
       <c r="S770" s="24"/>
       <c r="T770" s="54"/>
-      <c r="U770" s="215"/>
+      <c r="U770" s="221"/>
     </row>
     <row r="771" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A771" s="37"/>
@@ -34998,7 +34999,7 @@
       <c r="R771" s="86"/>
       <c r="S771" s="24"/>
       <c r="T771" s="54"/>
-      <c r="U771" s="215"/>
+      <c r="U771" s="221"/>
     </row>
     <row r="772" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A772" s="37"/>
@@ -35021,7 +35022,7 @@
       <c r="R772" s="86"/>
       <c r="S772" s="24"/>
       <c r="T772" s="54"/>
-      <c r="U772" s="215"/>
+      <c r="U772" s="221"/>
     </row>
     <row r="773" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A773" s="37" t="s">
@@ -35066,7 +35067,7 @@
       <c r="T773" s="54" t="s">
         <v>425</v>
       </c>
-      <c r="U773" s="215" t="s">
+      <c r="U773" s="221" t="s">
         <v>921</v>
       </c>
     </row>
@@ -35113,7 +35114,7 @@
       <c r="T774" s="54" t="s">
         <v>431</v>
       </c>
-      <c r="U774" s="215"/>
+      <c r="U774" s="221"/>
     </row>
     <row r="775" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A775" s="37" t="s">
@@ -35158,7 +35159,7 @@
       <c r="T775" s="54" t="s">
         <v>426</v>
       </c>
-      <c r="U775" s="215"/>
+      <c r="U775" s="221"/>
     </row>
     <row r="776" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A776" s="37" t="s">
@@ -35203,7 +35204,7 @@
       <c r="T776" s="54" t="s">
         <v>425</v>
       </c>
-      <c r="U776" s="215"/>
+      <c r="U776" s="221"/>
     </row>
     <row r="777" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A777" s="37" t="s">
@@ -35248,7 +35249,7 @@
       <c r="T777" s="54" t="s">
         <v>431</v>
       </c>
-      <c r="U777" s="215"/>
+      <c r="U777" s="221"/>
     </row>
     <row r="778" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A778" s="37" t="s">
@@ -35293,7 +35294,7 @@
       <c r="T778" s="54" t="s">
         <v>426</v>
       </c>
-      <c r="U778" s="215"/>
+      <c r="U778" s="221"/>
     </row>
     <row r="779" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A779" s="37" t="s">
@@ -35338,7 +35339,7 @@
       <c r="T779" s="54" t="s">
         <v>425</v>
       </c>
-      <c r="U779" s="215"/>
+      <c r="U779" s="221"/>
     </row>
     <row r="780" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A780" s="37" t="s">
@@ -35383,7 +35384,7 @@
       <c r="T780" s="54" t="s">
         <v>431</v>
       </c>
-      <c r="U780" s="215"/>
+      <c r="U780" s="221"/>
     </row>
     <row r="781" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A781" s="37" t="s">
@@ -35428,7 +35429,7 @@
       <c r="T781" s="54" t="s">
         <v>426</v>
       </c>
-      <c r="U781" s="215"/>
+      <c r="U781" s="221"/>
     </row>
     <row r="782" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A782" s="37" t="s">
@@ -35473,7 +35474,7 @@
       <c r="T782" s="54" t="s">
         <v>425</v>
       </c>
-      <c r="U782" s="215"/>
+      <c r="U782" s="221"/>
     </row>
     <row r="783" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A783" s="37" t="s">
@@ -35518,7 +35519,7 @@
       <c r="T783" s="54" t="s">
         <v>431</v>
       </c>
-      <c r="U783" s="215"/>
+      <c r="U783" s="221"/>
     </row>
     <row r="784" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A784" s="37" t="s">
@@ -35563,7 +35564,7 @@
       <c r="T784" s="54" t="s">
         <v>426</v>
       </c>
-      <c r="U784" s="215"/>
+      <c r="U784" s="221"/>
     </row>
     <row r="785" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A785" s="37"/>
@@ -35586,7 +35587,7 @@
       <c r="R785" s="25"/>
       <c r="S785" s="24"/>
       <c r="T785" s="54"/>
-      <c r="U785" s="215"/>
+      <c r="U785" s="221"/>
     </row>
     <row r="786" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A786" s="37"/>
@@ -35609,7 +35610,7 @@
       <c r="R786" s="25"/>
       <c r="S786" s="24"/>
       <c r="T786" s="54"/>
-      <c r="U786" s="215"/>
+      <c r="U786" s="221"/>
     </row>
     <row r="787" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A787" s="37"/>
@@ -35632,7 +35633,7 @@
       <c r="R787" s="25"/>
       <c r="S787" s="24"/>
       <c r="T787" s="54"/>
-      <c r="U787" s="215"/>
+      <c r="U787" s="221"/>
     </row>
     <row r="788" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A788" s="37" t="s">
@@ -35677,7 +35678,7 @@
       <c r="T788" s="54" t="s">
         <v>427</v>
       </c>
-      <c r="U788" s="216" t="s">
+      <c r="U788" s="220" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -35724,7 +35725,7 @@
       <c r="T789" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U789" s="216"/>
+      <c r="U789" s="220"/>
     </row>
     <row r="790" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A790" s="37" t="s">
@@ -35769,7 +35770,7 @@
       <c r="T790" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U790" s="216"/>
+      <c r="U790" s="220"/>
     </row>
     <row r="791" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A791" s="37" t="s">
@@ -35814,7 +35815,7 @@
       <c r="T791" s="54" t="s">
         <v>427</v>
       </c>
-      <c r="U791" s="216"/>
+      <c r="U791" s="220"/>
     </row>
     <row r="792" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A792" s="37" t="s">
@@ -35859,7 +35860,7 @@
       <c r="T792" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U792" s="216"/>
+      <c r="U792" s="220"/>
     </row>
     <row r="793" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A793" s="37" t="s">
@@ -35904,7 +35905,7 @@
       <c r="T793" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U793" s="216"/>
+      <c r="U793" s="220"/>
     </row>
     <row r="794" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A794" s="37" t="s">
@@ -35949,7 +35950,7 @@
       <c r="T794" s="54" t="s">
         <v>427</v>
       </c>
-      <c r="U794" s="216"/>
+      <c r="U794" s="220"/>
     </row>
     <row r="795" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A795" s="37" t="s">
@@ -35994,7 +35995,7 @@
       <c r="T795" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U795" s="216"/>
+      <c r="U795" s="220"/>
     </row>
     <row r="796" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A796" s="37" t="s">
@@ -36039,7 +36040,7 @@
       <c r="T796" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U796" s="216"/>
+      <c r="U796" s="220"/>
     </row>
     <row r="797" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A797" s="37" t="s">
@@ -36084,7 +36085,7 @@
       <c r="T797" s="54" t="s">
         <v>427</v>
       </c>
-      <c r="U797" s="216"/>
+      <c r="U797" s="220"/>
     </row>
     <row r="798" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A798" s="37" t="s">
@@ -36129,7 +36130,7 @@
       <c r="T798" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U798" s="216"/>
+      <c r="U798" s="220"/>
     </row>
     <row r="799" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A799" s="37" t="s">
@@ -36174,7 +36175,7 @@
       <c r="T799" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U799" s="216"/>
+      <c r="U799" s="220"/>
     </row>
     <row r="800" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A800" s="37" t="s">
@@ -36219,7 +36220,7 @@
       <c r="T800" s="54" t="s">
         <v>428</v>
       </c>
-      <c r="U800" s="216"/>
+      <c r="U800" s="220"/>
     </row>
     <row r="801" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A801" s="37" t="s">
@@ -36264,7 +36265,7 @@
       <c r="T801" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U801" s="216"/>
+      <c r="U801" s="220"/>
     </row>
     <row r="802" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A802" s="37" t="s">
@@ -36309,7 +36310,7 @@
       <c r="T802" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U802" s="216"/>
+      <c r="U802" s="220"/>
     </row>
     <row r="803" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A803" s="37" t="s">
@@ -36354,7 +36355,7 @@
       <c r="T803" s="54" t="s">
         <v>428</v>
       </c>
-      <c r="U803" s="216"/>
+      <c r="U803" s="220"/>
     </row>
     <row r="804" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A804" s="37" t="s">
@@ -36399,7 +36400,7 @@
       <c r="T804" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U804" s="216"/>
+      <c r="U804" s="220"/>
     </row>
     <row r="805" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A805" s="37" t="s">
@@ -36444,7 +36445,7 @@
       <c r="T805" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U805" s="216"/>
+      <c r="U805" s="220"/>
     </row>
     <row r="806" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A806" s="37" t="s">
@@ -36489,7 +36490,7 @@
       <c r="T806" s="54" t="s">
         <v>428</v>
       </c>
-      <c r="U806" s="216"/>
+      <c r="U806" s="220"/>
     </row>
     <row r="807" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A807" s="37" t="s">
@@ -36534,7 +36535,7 @@
       <c r="T807" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U807" s="216"/>
+      <c r="U807" s="220"/>
     </row>
     <row r="808" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A808" s="37" t="s">
@@ -36579,7 +36580,7 @@
       <c r="T808" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U808" s="216"/>
+      <c r="U808" s="220"/>
     </row>
     <row r="809" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A809" s="37" t="s">
@@ -36624,7 +36625,7 @@
       <c r="T809" s="54" t="s">
         <v>428</v>
       </c>
-      <c r="U809" s="216"/>
+      <c r="U809" s="220"/>
     </row>
     <row r="810" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A810" s="37" t="s">
@@ -36669,7 +36670,7 @@
       <c r="T810" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="U810" s="216"/>
+      <c r="U810" s="220"/>
     </row>
     <row r="811" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A811" s="37" t="s">
@@ -36714,7 +36715,7 @@
       <c r="T811" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="U811" s="216"/>
+      <c r="U811" s="220"/>
     </row>
     <row r="812" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A812" s="37" t="s">
@@ -36763,7 +36764,7 @@
       <c r="T812" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="U812" s="220" t="s">
+      <c r="U812" s="223" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -36812,7 +36813,7 @@
       <c r="R813" s="25"/>
       <c r="S813" s="24"/>
       <c r="T813" s="54"/>
-      <c r="U813" s="220"/>
+      <c r="U813" s="223"/>
     </row>
     <row r="814" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A814" s="37" t="s">
@@ -36859,7 +36860,7 @@
       <c r="R814" s="25"/>
       <c r="S814" s="24"/>
       <c r="T814" s="54"/>
-      <c r="U814" s="220"/>
+      <c r="U814" s="223"/>
     </row>
     <row r="815" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A815" s="37"/>
@@ -36882,7 +36883,7 @@
       <c r="R815" s="25"/>
       <c r="S815" s="24"/>
       <c r="T815" s="54"/>
-      <c r="U815" s="220"/>
+      <c r="U815" s="223"/>
     </row>
     <row r="816" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A816" s="37"/>
@@ -36905,7 +36906,7 @@
       <c r="R816" s="25"/>
       <c r="S816" s="24"/>
       <c r="T816" s="54"/>
-      <c r="U816" s="220"/>
+      <c r="U816" s="223"/>
     </row>
     <row r="817" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A817" s="37"/>
@@ -36928,7 +36929,7 @@
       <c r="R817" s="25"/>
       <c r="S817" s="24"/>
       <c r="T817" s="54"/>
-      <c r="U817" s="220"/>
+      <c r="U817" s="223"/>
     </row>
     <row r="818" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A818" s="37"/>
@@ -36951,7 +36952,7 @@
       <c r="R818" s="25"/>
       <c r="S818" s="24"/>
       <c r="T818" s="54"/>
-      <c r="U818" s="220"/>
+      <c r="U818" s="223"/>
     </row>
     <row r="819" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A819" s="37"/>
@@ -36974,7 +36975,7 @@
       <c r="R819" s="25"/>
       <c r="S819" s="24"/>
       <c r="T819" s="200"/>
-      <c r="U819" s="220"/>
+      <c r="U819" s="223"/>
     </row>
     <row r="820" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A820" s="37"/>
@@ -36997,7 +36998,7 @@
       <c r="R820" s="25"/>
       <c r="S820" s="24"/>
       <c r="T820" s="54"/>
-      <c r="U820" s="220"/>
+      <c r="U820" s="223"/>
     </row>
     <row r="821" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A821" s="37"/>
@@ -37020,7 +37021,7 @@
       <c r="R821" s="25"/>
       <c r="S821" s="24"/>
       <c r="T821" s="54"/>
-      <c r="U821" s="220"/>
+      <c r="U821" s="223"/>
     </row>
     <row r="822" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A822" s="37" t="s">
@@ -37069,7 +37070,7 @@
       <c r="T822" s="54" t="s">
         <v>404</v>
       </c>
-      <c r="U822" s="220" t="s">
+      <c r="U822" s="223" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -37118,7 +37119,7 @@
       <c r="R823" s="25"/>
       <c r="S823" s="24"/>
       <c r="T823" s="54"/>
-      <c r="U823" s="220"/>
+      <c r="U823" s="223"/>
     </row>
     <row r="824" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A824" s="37" t="s">
@@ -37165,7 +37166,7 @@
       <c r="R824" s="25"/>
       <c r="S824" s="24"/>
       <c r="T824" s="54"/>
-      <c r="U824" s="220"/>
+      <c r="U824" s="223"/>
     </row>
     <row r="825" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A825" s="37"/>
@@ -37188,7 +37189,7 @@
       <c r="R825" s="25"/>
       <c r="S825" s="24"/>
       <c r="T825" s="54"/>
-      <c r="U825" s="220"/>
+      <c r="U825" s="223"/>
     </row>
     <row r="826" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A826" s="37"/>
@@ -37211,7 +37212,7 @@
       <c r="R826" s="25"/>
       <c r="S826" s="24"/>
       <c r="T826" s="54"/>
-      <c r="U826" s="220"/>
+      <c r="U826" s="223"/>
     </row>
     <row r="827" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A827" s="37"/>
@@ -37234,7 +37235,7 @@
       <c r="R827" s="25"/>
       <c r="S827" s="24"/>
       <c r="T827" s="54"/>
-      <c r="U827" s="220"/>
+      <c r="U827" s="223"/>
     </row>
     <row r="828" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A828" s="37"/>
@@ -37257,7 +37258,7 @@
       <c r="R828" s="25"/>
       <c r="S828" s="24"/>
       <c r="T828" s="54"/>
-      <c r="U828" s="220"/>
+      <c r="U828" s="223"/>
     </row>
     <row r="829" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A829" s="37"/>
@@ -37280,7 +37281,7 @@
       <c r="R829" s="25"/>
       <c r="S829" s="24"/>
       <c r="T829" s="54"/>
-      <c r="U829" s="220"/>
+      <c r="U829" s="223"/>
     </row>
     <row r="830" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A830" s="37" t="s">
@@ -37327,7 +37328,7 @@
       <c r="T830" s="54" t="s">
         <v>406</v>
       </c>
-      <c r="U830" s="220" t="s">
+      <c r="U830" s="223" t="s">
         <v>913</v>
       </c>
     </row>
@@ -37352,7 +37353,7 @@
       <c r="R831" s="25"/>
       <c r="S831" s="24"/>
       <c r="T831" s="54"/>
-      <c r="U831" s="220"/>
+      <c r="U831" s="223"/>
     </row>
     <row r="832" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A832" s="37"/>
@@ -37375,7 +37376,7 @@
       <c r="R832" s="25"/>
       <c r="S832" s="24"/>
       <c r="T832" s="54"/>
-      <c r="U832" s="220"/>
+      <c r="U832" s="223"/>
     </row>
     <row r="833" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A833" s="37"/>
@@ -37398,7 +37399,7 @@
       <c r="R833" s="25"/>
       <c r="S833" s="24"/>
       <c r="T833" s="54"/>
-      <c r="U833" s="220"/>
+      <c r="U833" s="223"/>
     </row>
     <row r="834" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A834" s="37"/>
@@ -37421,7 +37422,7 @@
       <c r="R834" s="25"/>
       <c r="S834" s="24"/>
       <c r="T834" s="54"/>
-      <c r="U834" s="220"/>
+      <c r="U834" s="223"/>
     </row>
     <row r="835" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A835" s="37"/>
@@ -37444,7 +37445,7 @@
       <c r="R835" s="25"/>
       <c r="S835" s="24"/>
       <c r="T835" s="54"/>
-      <c r="U835" s="220"/>
+      <c r="U835" s="223"/>
     </row>
     <row r="836" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A836" s="37"/>
@@ -37467,7 +37468,7 @@
       <c r="R836" s="25"/>
       <c r="S836" s="24"/>
       <c r="T836" s="171"/>
-      <c r="U836" s="220"/>
+      <c r="U836" s="223"/>
     </row>
     <row r="837" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A837" s="37"/>
@@ -37490,7 +37491,7 @@
       <c r="R837" s="25"/>
       <c r="S837" s="24"/>
       <c r="T837" s="171"/>
-      <c r="U837" s="220"/>
+      <c r="U837" s="223"/>
     </row>
     <row r="838" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A838" s="37"/>
@@ -37513,7 +37514,7 @@
       <c r="R838" s="25"/>
       <c r="S838" s="24"/>
       <c r="T838" s="171"/>
-      <c r="U838" s="220"/>
+      <c r="U838" s="223"/>
     </row>
     <row r="839" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A839" s="37"/>
@@ -37536,7 +37537,7 @@
       <c r="R839" s="25"/>
       <c r="S839" s="24"/>
       <c r="T839" s="54"/>
-      <c r="U839" s="220"/>
+      <c r="U839" s="223"/>
     </row>
     <row r="840" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A840" s="37"/>
@@ -37559,7 +37560,7 @@
       <c r="R840" s="25"/>
       <c r="S840" s="24"/>
       <c r="T840" s="54"/>
-      <c r="U840" s="220"/>
+      <c r="U840" s="223"/>
     </row>
     <row r="841" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A841" s="37"/>
@@ -37582,7 +37583,7 @@
       <c r="R841" s="25"/>
       <c r="S841" s="24"/>
       <c r="T841" s="54"/>
-      <c r="U841" s="220"/>
+      <c r="U841" s="223"/>
     </row>
     <row r="842" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A842" s="37"/>
@@ -37605,7 +37606,7 @@
       <c r="R842" s="25"/>
       <c r="S842" s="24"/>
       <c r="T842" s="54"/>
-      <c r="U842" s="220"/>
+      <c r="U842" s="223"/>
     </row>
     <row r="843" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A843" s="37"/>
@@ -37628,7 +37629,7 @@
       <c r="R843" s="25"/>
       <c r="S843" s="24"/>
       <c r="T843" s="54"/>
-      <c r="U843" s="220"/>
+      <c r="U843" s="223"/>
     </row>
     <row r="844" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A844" s="37"/>
@@ -37651,7 +37652,7 @@
       <c r="R844" s="25"/>
       <c r="S844" s="24"/>
       <c r="T844" s="54"/>
-      <c r="U844" s="220"/>
+      <c r="U844" s="223"/>
     </row>
     <row r="845" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A845" s="37" t="s">
@@ -37698,7 +37699,7 @@
       <c r="T845" s="54" t="s">
         <v>750</v>
       </c>
-      <c r="U845" s="220" t="s">
+      <c r="U845" s="223" t="s">
         <v>912</v>
       </c>
     </row>
@@ -37723,7 +37724,7 @@
       <c r="R846" s="25"/>
       <c r="S846" s="24"/>
       <c r="T846" s="54"/>
-      <c r="U846" s="220"/>
+      <c r="U846" s="223"/>
     </row>
     <row r="847" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A847" s="37"/>
@@ -37746,7 +37747,7 @@
       <c r="R847" s="25"/>
       <c r="S847" s="24"/>
       <c r="T847" s="54"/>
-      <c r="U847" s="220"/>
+      <c r="U847" s="223"/>
     </row>
     <row r="848" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A848" s="37"/>
@@ -37769,7 +37770,7 @@
       <c r="R848" s="25"/>
       <c r="S848" s="24"/>
       <c r="T848" s="54"/>
-      <c r="U848" s="220"/>
+      <c r="U848" s="223"/>
     </row>
     <row r="849" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A849" s="37"/>
@@ -37792,7 +37793,7 @@
       <c r="R849" s="25"/>
       <c r="S849" s="24"/>
       <c r="T849" s="54"/>
-      <c r="U849" s="220"/>
+      <c r="U849" s="223"/>
     </row>
     <row r="850" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A850" s="37"/>
@@ -37815,7 +37816,7 @@
       <c r="R850" s="25"/>
       <c r="S850" s="24"/>
       <c r="T850" s="54"/>
-      <c r="U850" s="220"/>
+      <c r="U850" s="223"/>
     </row>
     <row r="851" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A851" s="37"/>
@@ -37838,7 +37839,7 @@
       <c r="R851" s="25"/>
       <c r="S851" s="24"/>
       <c r="T851" s="54"/>
-      <c r="U851" s="220"/>
+      <c r="U851" s="223"/>
     </row>
     <row r="852" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A852" s="37"/>
@@ -37861,7 +37862,7 @@
       <c r="R852" s="25"/>
       <c r="S852" s="24"/>
       <c r="T852" s="54"/>
-      <c r="U852" s="220"/>
+      <c r="U852" s="223"/>
     </row>
     <row r="853" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A853" s="37"/>
@@ -37884,7 +37885,7 @@
       <c r="R853" s="25"/>
       <c r="S853" s="24"/>
       <c r="T853" s="54"/>
-      <c r="U853" s="220"/>
+      <c r="U853" s="223"/>
     </row>
     <row r="854" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A854" s="37"/>
@@ -37907,7 +37908,7 @@
       <c r="R854" s="25"/>
       <c r="S854" s="24"/>
       <c r="T854" s="54"/>
-      <c r="U854" s="220"/>
+      <c r="U854" s="223"/>
     </row>
     <row r="855" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A855" s="37"/>
@@ -37930,7 +37931,7 @@
       <c r="R855" s="25"/>
       <c r="S855" s="24"/>
       <c r="T855" s="54"/>
-      <c r="U855" s="220"/>
+      <c r="U855" s="223"/>
     </row>
     <row r="856" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A856" s="37"/>
@@ -37953,7 +37954,7 @@
       <c r="R856" s="25"/>
       <c r="S856" s="24"/>
       <c r="T856" s="54"/>
-      <c r="U856" s="220"/>
+      <c r="U856" s="223"/>
     </row>
     <row r="857" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A857" s="37" t="s">
@@ -38002,8 +38003,8 @@
       <c r="T857" s="54" t="s">
         <v>392</v>
       </c>
-      <c r="U857" s="220" t="s">
-        <v>1170</v>
+      <c r="U857" s="223" t="s">
+        <v>1169</v>
       </c>
     </row>
     <row r="858" spans="1:21" x14ac:dyDescent="0.35">
@@ -38053,7 +38054,7 @@
       <c r="T858" s="54" t="s">
         <v>393</v>
       </c>
-      <c r="U858" s="220"/>
+      <c r="U858" s="223"/>
     </row>
     <row r="859" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A859" s="37" t="s">
@@ -38102,7 +38103,7 @@
       <c r="T859" s="54" t="s">
         <v>394</v>
       </c>
-      <c r="U859" s="220"/>
+      <c r="U859" s="223"/>
     </row>
     <row r="860" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A860" s="37" t="s">
@@ -38151,7 +38152,7 @@
       <c r="T860" s="54" t="s">
         <v>395</v>
       </c>
-      <c r="U860" s="220"/>
+      <c r="U860" s="223"/>
     </row>
     <row r="861" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A861" s="37" t="s">
@@ -38200,7 +38201,7 @@
       <c r="T861" s="54" t="s">
         <v>396</v>
       </c>
-      <c r="U861" s="220"/>
+      <c r="U861" s="223"/>
     </row>
     <row r="862" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A862" s="37"/>
@@ -38223,7 +38224,7 @@
       <c r="R862" s="25"/>
       <c r="S862" s="24"/>
       <c r="T862" s="171"/>
-      <c r="U862" s="220"/>
+      <c r="U862" s="223"/>
     </row>
     <row r="863" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A863" s="37"/>
@@ -38246,7 +38247,7 @@
       <c r="R863" s="25"/>
       <c r="S863" s="24"/>
       <c r="T863" s="171"/>
-      <c r="U863" s="220"/>
+      <c r="U863" s="223"/>
     </row>
     <row r="864" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A864" s="37"/>
@@ -38269,7 +38270,7 @@
       <c r="R864" s="25"/>
       <c r="S864" s="24"/>
       <c r="T864" s="171"/>
-      <c r="U864" s="220"/>
+      <c r="U864" s="223"/>
     </row>
     <row r="865" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A865" s="37"/>
@@ -38292,7 +38293,7 @@
       <c r="R865" s="25"/>
       <c r="S865" s="24"/>
       <c r="T865" s="176"/>
-      <c r="U865" s="220"/>
+      <c r="U865" s="223"/>
     </row>
     <row r="866" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A866" s="37"/>
@@ -38315,7 +38316,7 @@
       <c r="R866" s="25"/>
       <c r="S866" s="24"/>
       <c r="T866" s="176"/>
-      <c r="U866" s="220"/>
+      <c r="U866" s="223"/>
     </row>
     <row r="867" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A867" s="37"/>
@@ -38338,7 +38339,7 @@
       <c r="R867" s="25"/>
       <c r="S867" s="24"/>
       <c r="T867" s="176"/>
-      <c r="U867" s="220"/>
+      <c r="U867" s="223"/>
     </row>
     <row r="868" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A868" s="37"/>
@@ -38361,7 +38362,7 @@
       <c r="R868" s="25"/>
       <c r="S868" s="24"/>
       <c r="T868" s="176"/>
-      <c r="U868" s="220"/>
+      <c r="U868" s="223"/>
     </row>
     <row r="869" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A869" s="37"/>
@@ -38384,7 +38385,7 @@
       <c r="R869" s="25"/>
       <c r="S869" s="24"/>
       <c r="T869" s="176"/>
-      <c r="U869" s="220"/>
+      <c r="U869" s="223"/>
     </row>
     <row r="870" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A870" s="37"/>
@@ -38407,7 +38408,7 @@
       <c r="R870" s="25"/>
       <c r="S870" s="24"/>
       <c r="T870" s="171"/>
-      <c r="U870" s="220"/>
+      <c r="U870" s="223"/>
     </row>
     <row r="871" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A871" s="37"/>
@@ -38430,7 +38431,7 @@
       <c r="R871" s="25"/>
       <c r="S871" s="24"/>
       <c r="T871" s="171"/>
-      <c r="U871" s="220"/>
+      <c r="U871" s="223"/>
     </row>
     <row r="872" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A872" s="37"/>
@@ -38453,7 +38454,7 @@
       <c r="R872" s="25"/>
       <c r="S872" s="24"/>
       <c r="T872" s="171"/>
-      <c r="U872" s="220"/>
+      <c r="U872" s="223"/>
     </row>
     <row r="873" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A873" s="37"/>
@@ -38476,7 +38477,7 @@
       <c r="R873" s="25"/>
       <c r="S873" s="24"/>
       <c r="T873" s="208"/>
-      <c r="U873" s="220"/>
+      <c r="U873" s="223"/>
     </row>
     <row r="874" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A874" s="37"/>
@@ -38499,7 +38500,7 @@
       <c r="R874" s="25"/>
       <c r="S874" s="24"/>
       <c r="T874" s="208"/>
-      <c r="U874" s="220"/>
+      <c r="U874" s="223"/>
     </row>
     <row r="875" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A875" s="37"/>
@@ -38522,7 +38523,7 @@
       <c r="R875" s="25"/>
       <c r="S875" s="24"/>
       <c r="T875" s="208"/>
-      <c r="U875" s="220"/>
+      <c r="U875" s="223"/>
     </row>
     <row r="876" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A876" s="37"/>
@@ -38545,7 +38546,7 @@
       <c r="R876" s="25"/>
       <c r="S876" s="24"/>
       <c r="T876" s="208"/>
-      <c r="U876" s="220"/>
+      <c r="U876" s="223"/>
     </row>
     <row r="877" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A877" s="37"/>
@@ -38568,7 +38569,7 @@
       <c r="R877" s="25"/>
       <c r="S877" s="24"/>
       <c r="T877" s="208"/>
-      <c r="U877" s="220"/>
+      <c r="U877" s="223"/>
     </row>
     <row r="878" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A878" s="37"/>
@@ -38591,7 +38592,7 @@
       <c r="R878" s="25"/>
       <c r="S878" s="24"/>
       <c r="T878" s="208"/>
-      <c r="U878" s="220"/>
+      <c r="U878" s="223"/>
     </row>
     <row r="879" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A879" s="37"/>
@@ -38614,7 +38615,7 @@
       <c r="R879" s="25"/>
       <c r="S879" s="24"/>
       <c r="T879" s="208"/>
-      <c r="U879" s="220"/>
+      <c r="U879" s="223"/>
     </row>
     <row r="880" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A880" s="37" t="s">
@@ -38655,7 +38656,7 @@
       <c r="T880" s="54" t="s">
         <v>357</v>
       </c>
-      <c r="U880" s="228" t="s">
+      <c r="U880" s="224" t="s">
         <v>410</v>
       </c>
     </row>
@@ -38696,7 +38697,7 @@
       <c r="R881" s="25"/>
       <c r="S881" s="24"/>
       <c r="T881" s="54"/>
-      <c r="U881" s="228"/>
+      <c r="U881" s="224"/>
     </row>
     <row r="882" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A882" s="37" t="s">
@@ -38735,7 +38736,7 @@
       <c r="R882" s="25"/>
       <c r="S882" s="24"/>
       <c r="T882" s="54"/>
-      <c r="U882" s="228"/>
+      <c r="U882" s="224"/>
     </row>
     <row r="883" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A883" s="37"/>
@@ -38758,7 +38759,7 @@
       <c r="R883" s="25"/>
       <c r="S883" s="24"/>
       <c r="T883" s="54"/>
-      <c r="U883" s="228"/>
+      <c r="U883" s="224"/>
     </row>
     <row r="884" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A884" s="37"/>
@@ -38781,7 +38782,7 @@
       <c r="R884" s="25"/>
       <c r="S884" s="24"/>
       <c r="T884" s="54"/>
-      <c r="U884" s="228"/>
+      <c r="U884" s="224"/>
     </row>
     <row r="885" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A885" s="37" t="s">
@@ -38822,7 +38823,7 @@
       <c r="T885" s="143" t="s">
         <v>409</v>
       </c>
-      <c r="U885" s="228" t="s">
+      <c r="U885" s="224" t="s">
         <v>411</v>
       </c>
     </row>
@@ -38863,7 +38864,7 @@
       <c r="R886" s="25"/>
       <c r="S886" s="24"/>
       <c r="T886" s="54"/>
-      <c r="U886" s="228"/>
+      <c r="U886" s="224"/>
     </row>
     <row r="887" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A887" s="37" t="s">
@@ -38902,7 +38903,7 @@
       <c r="R887" s="25"/>
       <c r="S887" s="24"/>
       <c r="T887" s="54"/>
-      <c r="U887" s="228"/>
+      <c r="U887" s="224"/>
     </row>
     <row r="888" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A888" s="37"/>
@@ -38925,7 +38926,7 @@
       <c r="R888" s="25"/>
       <c r="S888" s="24"/>
       <c r="T888" s="54"/>
-      <c r="U888" s="228"/>
+      <c r="U888" s="224"/>
     </row>
     <row r="889" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A889" s="37"/>
@@ -38948,7 +38949,7 @@
       <c r="R889" s="25"/>
       <c r="S889" s="24"/>
       <c r="T889" s="54"/>
-      <c r="U889" s="228"/>
+      <c r="U889" s="224"/>
     </row>
     <row r="890" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A890" s="37" t="s">
@@ -38964,7 +38965,7 @@
         <v>1</v>
       </c>
       <c r="E890" s="34" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F890" s="38" t="s">
         <v>2</v>
@@ -38991,10 +38992,10 @@
         <v>9</v>
       </c>
       <c r="T890" s="209" t="s">
-        <v>1172</v>
-      </c>
-      <c r="U890" s="221" t="s">
         <v>1171</v>
+      </c>
+      <c r="U890" s="231" t="s">
+        <v>1170</v>
       </c>
     </row>
     <row r="891" spans="1:21" x14ac:dyDescent="0.35">
@@ -39018,7 +39019,7 @@
       <c r="R891" s="25"/>
       <c r="S891" s="24"/>
       <c r="T891" s="209"/>
-      <c r="U891" s="221"/>
+      <c r="U891" s="231"/>
     </row>
     <row r="892" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A892" s="37"/>
@@ -39041,7 +39042,7 @@
       <c r="R892" s="25"/>
       <c r="S892" s="24"/>
       <c r="T892" s="209"/>
-      <c r="U892" s="221"/>
+      <c r="U892" s="231"/>
     </row>
     <row r="893" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A893" s="37"/>
@@ -39064,7 +39065,7 @@
       <c r="R893" s="25"/>
       <c r="S893" s="24"/>
       <c r="T893" s="209"/>
-      <c r="U893" s="221"/>
+      <c r="U893" s="231"/>
     </row>
     <row r="894" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A894" s="37"/>
@@ -39087,7 +39088,7 @@
       <c r="R894" s="25"/>
       <c r="S894" s="24"/>
       <c r="T894" s="209"/>
-      <c r="U894" s="221"/>
+      <c r="U894" s="231"/>
     </row>
     <row r="895" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A895" s="37"/>
@@ -39110,7 +39111,7 @@
       <c r="R895" s="25"/>
       <c r="S895" s="24"/>
       <c r="T895" s="209"/>
-      <c r="U895" s="221"/>
+      <c r="U895" s="231"/>
     </row>
     <row r="896" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A896" s="37"/>
@@ -39133,7 +39134,7 @@
       <c r="R896" s="25"/>
       <c r="S896" s="24"/>
       <c r="T896" s="209"/>
-      <c r="U896" s="221"/>
+      <c r="U896" s="231"/>
     </row>
     <row r="897" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A897" s="37"/>
@@ -39156,7 +39157,7 @@
       <c r="R897" s="25"/>
       <c r="S897" s="24"/>
       <c r="T897" s="209"/>
-      <c r="U897" s="221"/>
+      <c r="U897" s="231"/>
     </row>
     <row r="898" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A898" s="37"/>
@@ -39179,7 +39180,7 @@
       <c r="R898" s="25"/>
       <c r="S898" s="24"/>
       <c r="T898" s="209"/>
-      <c r="U898" s="221"/>
+      <c r="U898" s="231"/>
     </row>
     <row r="899" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A899" s="37"/>
@@ -39202,7 +39203,7 @@
       <c r="R899" s="25"/>
       <c r="S899" s="24"/>
       <c r="T899" s="209"/>
-      <c r="U899" s="221"/>
+      <c r="U899" s="231"/>
     </row>
     <row r="900" spans="1:21" ht="52" x14ac:dyDescent="0.35">
       <c r="A900" s="37" t="s">
@@ -39218,7 +39219,7 @@
         <v>1</v>
       </c>
       <c r="E900" s="34" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="F900" s="38" t="s">
         <v>2</v>
@@ -39243,10 +39244,10 @@
       </c>
       <c r="S900" s="24"/>
       <c r="T900" s="209" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U900" s="210" t="s">
         <v>1174</v>
-      </c>
-      <c r="U900" s="210" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="901" spans="1:21" x14ac:dyDescent="0.35">
@@ -39294,7 +39295,7 @@
       <c r="T901" s="54" t="s">
         <v>898</v>
       </c>
-      <c r="U901" s="216" t="s">
+      <c r="U901" s="220" t="s">
         <v>53</v>
       </c>
     </row>
@@ -39345,7 +39346,7 @@
       <c r="T902" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="U902" s="216"/>
+      <c r="U902" s="220"/>
     </row>
     <row r="903" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A903" s="37" t="s">
@@ -39394,7 +39395,7 @@
       <c r="T903" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="U903" s="216"/>
+      <c r="U903" s="220"/>
     </row>
     <row r="904" spans="1:21" ht="208" x14ac:dyDescent="0.35">
       <c r="A904" s="37" t="s">
@@ -39422,7 +39423,7 @@
         <v>1</v>
       </c>
       <c r="I904" s="37" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="J904" s="38" t="s">
         <v>2</v>
@@ -39438,13 +39439,13 @@
         <v>-1</v>
       </c>
       <c r="S904" s="24" t="s">
+        <v>1129</v>
+      </c>
+      <c r="T904" s="54" t="s">
         <v>1130</v>
       </c>
-      <c r="T904" s="54" t="s">
+      <c r="U904" s="54" t="s">
         <v>1131</v>
-      </c>
-      <c r="U904" s="54" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="905" spans="1:21" x14ac:dyDescent="0.35">
@@ -39494,7 +39495,7 @@
       <c r="T905" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="U905" s="220" t="s">
+      <c r="U905" s="223" t="s">
         <v>774</v>
       </c>
     </row>
@@ -39545,7 +39546,7 @@
       <c r="T906" s="54" t="s">
         <v>304</v>
       </c>
-      <c r="U906" s="220"/>
+      <c r="U906" s="223"/>
     </row>
     <row r="907" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A907" s="37" t="s">
@@ -39594,7 +39595,7 @@
       <c r="T907" s="54" t="s">
         <v>766</v>
       </c>
-      <c r="U907" s="220"/>
+      <c r="U907" s="223"/>
     </row>
     <row r="908" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A908" s="37" t="s">
@@ -39643,7 +39644,7 @@
       <c r="T908" s="54" t="s">
         <v>767</v>
       </c>
-      <c r="U908" s="220"/>
+      <c r="U908" s="223"/>
     </row>
     <row r="909" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A909" s="37" t="s">
@@ -39692,7 +39693,7 @@
       <c r="T909" s="54" t="s">
         <v>768</v>
       </c>
-      <c r="U909" s="220"/>
+      <c r="U909" s="223"/>
     </row>
     <row r="910" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A910" s="37" t="s">
@@ -39741,7 +39742,7 @@
       <c r="T910" s="54" t="s">
         <v>769</v>
       </c>
-      <c r="U910" s="220"/>
+      <c r="U910" s="223"/>
     </row>
     <row r="911" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A911" s="37" t="s">
@@ -39788,7 +39789,7 @@
       <c r="T911" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="U911" s="220"/>
+      <c r="U911" s="223"/>
     </row>
     <row r="912" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A912" s="37"/>
@@ -39810,7 +39811,7 @@
       <c r="R912" s="25"/>
       <c r="S912" s="42"/>
       <c r="T912" s="54"/>
-      <c r="U912" s="220"/>
+      <c r="U912" s="223"/>
     </row>
     <row r="913" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A913" s="37"/>
@@ -39832,7 +39833,7 @@
       <c r="R913" s="25"/>
       <c r="S913" s="42"/>
       <c r="T913" s="54"/>
-      <c r="U913" s="220"/>
+      <c r="U913" s="223"/>
     </row>
     <row r="914" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A914" s="37"/>
@@ -39854,7 +39855,7 @@
       <c r="R914" s="25"/>
       <c r="S914" s="42"/>
       <c r="T914" s="54"/>
-      <c r="U914" s="220"/>
+      <c r="U914" s="223"/>
     </row>
     <row r="915" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A915" s="37"/>
@@ -39876,7 +39877,7 @@
       <c r="R915" s="25"/>
       <c r="S915" s="42"/>
       <c r="T915" s="54"/>
-      <c r="U915" s="220"/>
+      <c r="U915" s="223"/>
     </row>
     <row r="916" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A916" s="37"/>
@@ -39898,7 +39899,7 @@
       <c r="R916" s="25"/>
       <c r="S916" s="42"/>
       <c r="T916" s="54"/>
-      <c r="U916" s="220"/>
+      <c r="U916" s="223"/>
     </row>
     <row r="917" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A917" s="37"/>
@@ -39920,7 +39921,7 @@
       <c r="R917" s="25"/>
       <c r="S917" s="42"/>
       <c r="T917" s="54"/>
-      <c r="U917" s="220"/>
+      <c r="U917" s="223"/>
     </row>
     <row r="918" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A918" s="37"/>
@@ -39942,7 +39943,7 @@
       <c r="R918" s="25"/>
       <c r="S918" s="42"/>
       <c r="T918" s="54"/>
-      <c r="U918" s="220"/>
+      <c r="U918" s="223"/>
     </row>
     <row r="919" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A919" s="37"/>
@@ -39964,7 +39965,7 @@
       <c r="R919" s="25"/>
       <c r="S919" s="42"/>
       <c r="T919" s="54"/>
-      <c r="U919" s="220"/>
+      <c r="U919" s="223"/>
     </row>
     <row r="920" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A920" s="37"/>
@@ -39986,7 +39987,7 @@
       <c r="R920" s="25"/>
       <c r="S920" s="42"/>
       <c r="T920" s="54"/>
-      <c r="U920" s="220"/>
+      <c r="U920" s="223"/>
     </row>
     <row r="921" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A921" s="37"/>
@@ -40008,7 +40009,7 @@
       <c r="R921" s="25"/>
       <c r="S921" s="42"/>
       <c r="T921" s="54"/>
-      <c r="U921" s="220"/>
+      <c r="U921" s="223"/>
     </row>
     <row r="922" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A922" s="37"/>
@@ -40030,7 +40031,7 @@
       <c r="R922" s="25"/>
       <c r="S922" s="42"/>
       <c r="T922" s="54"/>
-      <c r="U922" s="220"/>
+      <c r="U922" s="223"/>
     </row>
     <row r="923" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A923" s="37"/>
@@ -40052,7 +40053,7 @@
       <c r="R923" s="25"/>
       <c r="S923" s="42"/>
       <c r="T923" s="54"/>
-      <c r="U923" s="220"/>
+      <c r="U923" s="223"/>
     </row>
     <row r="924" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A924" s="37"/>
@@ -40074,7 +40075,7 @@
       <c r="R924" s="25"/>
       <c r="S924" s="42"/>
       <c r="T924" s="54"/>
-      <c r="U924" s="220"/>
+      <c r="U924" s="223"/>
     </row>
     <row r="925" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A925" s="37" t="s">
@@ -40123,7 +40124,7 @@
       <c r="T925" s="54" t="s">
         <v>297</v>
       </c>
-      <c r="U925" s="216" t="s">
+      <c r="U925" s="220" t="s">
         <v>500</v>
       </c>
     </row>
@@ -40174,7 +40175,7 @@
       <c r="T926" s="54" t="s">
         <v>298</v>
       </c>
-      <c r="U926" s="216"/>
+      <c r="U926" s="220"/>
     </row>
     <row r="927" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A927" s="37" t="s">
@@ -40223,7 +40224,7 @@
       <c r="T927" s="54" t="s">
         <v>299</v>
       </c>
-      <c r="U927" s="216"/>
+      <c r="U927" s="220"/>
     </row>
     <row r="928" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A928" s="37" t="s">
@@ -40272,7 +40273,7 @@
       <c r="T928" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="U928" s="216"/>
+      <c r="U928" s="220"/>
     </row>
     <row r="929" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A929" s="37" t="s">
@@ -40321,7 +40322,7 @@
       <c r="T929" s="54" t="s">
         <v>291</v>
       </c>
-      <c r="U929" s="216"/>
+      <c r="U929" s="220"/>
     </row>
     <row r="930" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A930" s="37" t="s">
@@ -40370,7 +40371,7 @@
       <c r="T930" s="54" t="s">
         <v>292</v>
       </c>
-      <c r="U930" s="216"/>
+      <c r="U930" s="220"/>
     </row>
     <row r="931" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A931" s="37"/>
@@ -40393,7 +40394,7 @@
       <c r="R931" s="25"/>
       <c r="S931" s="24"/>
       <c r="T931" s="54"/>
-      <c r="U931" s="216"/>
+      <c r="U931" s="220"/>
     </row>
     <row r="932" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A932" s="37"/>
@@ -40416,7 +40417,7 @@
       <c r="R932" s="25"/>
       <c r="S932" s="24"/>
       <c r="T932" s="54"/>
-      <c r="U932" s="216"/>
+      <c r="U932" s="220"/>
     </row>
     <row r="933" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A933" s="37"/>
@@ -40439,7 +40440,7 @@
       <c r="R933" s="25"/>
       <c r="S933" s="24"/>
       <c r="T933" s="54"/>
-      <c r="U933" s="216"/>
+      <c r="U933" s="220"/>
     </row>
     <row r="934" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A934" s="37"/>
@@ -40462,7 +40463,7 @@
       <c r="R934" s="25"/>
       <c r="S934" s="24"/>
       <c r="T934" s="54"/>
-      <c r="U934" s="216"/>
+      <c r="U934" s="220"/>
     </row>
     <row r="935" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A935" s="37" t="s">
@@ -40509,7 +40510,7 @@
       <c r="T935" s="187" t="s">
         <v>956</v>
       </c>
-      <c r="U935" s="217" t="s">
+      <c r="U935" s="215" t="s">
         <v>964</v>
       </c>
     </row>
@@ -40558,7 +40559,7 @@
       <c r="T936" s="187" t="s">
         <v>957</v>
       </c>
-      <c r="U936" s="217"/>
+      <c r="U936" s="215"/>
     </row>
     <row r="937" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A937" s="37" t="s">
@@ -40605,7 +40606,7 @@
       <c r="T937" s="187" t="s">
         <v>958</v>
       </c>
-      <c r="U937" s="217"/>
+      <c r="U937" s="215"/>
     </row>
     <row r="938" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A938" s="37" t="s">
@@ -40652,7 +40653,7 @@
       <c r="T938" s="187" t="s">
         <v>959</v>
       </c>
-      <c r="U938" s="217"/>
+      <c r="U938" s="215"/>
     </row>
     <row r="939" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A939" s="37"/>
@@ -40675,7 +40676,7 @@
       <c r="R939" s="25"/>
       <c r="S939" s="24"/>
       <c r="T939" s="186"/>
-      <c r="U939" s="217"/>
+      <c r="U939" s="215"/>
     </row>
     <row r="940" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A940" s="37"/>
@@ -40698,7 +40699,7 @@
       <c r="R940" s="25"/>
       <c r="S940" s="24"/>
       <c r="T940" s="186"/>
-      <c r="U940" s="217"/>
+      <c r="U940" s="215"/>
     </row>
     <row r="941" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A941" s="37"/>
@@ -40721,7 +40722,7 @@
       <c r="R941" s="25"/>
       <c r="S941" s="24"/>
       <c r="T941" s="186"/>
-      <c r="U941" s="217"/>
+      <c r="U941" s="215"/>
     </row>
     <row r="942" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A942" s="37"/>
@@ -40744,7 +40745,7 @@
       <c r="R942" s="25"/>
       <c r="S942" s="24"/>
       <c r="T942" s="186"/>
-      <c r="U942" s="217"/>
+      <c r="U942" s="215"/>
     </row>
     <row r="943" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A943" s="37"/>
@@ -40767,7 +40768,7 @@
       <c r="R943" s="25"/>
       <c r="S943" s="24"/>
       <c r="T943" s="186"/>
-      <c r="U943" s="217"/>
+      <c r="U943" s="215"/>
     </row>
     <row r="944" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A944" s="37"/>
@@ -40790,7 +40791,7 @@
       <c r="R944" s="25"/>
       <c r="S944" s="24"/>
       <c r="T944" s="186"/>
-      <c r="U944" s="217"/>
+      <c r="U944" s="215"/>
     </row>
     <row r="945" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A945" s="37"/>
@@ -40813,7 +40814,7 @@
       <c r="R945" s="25"/>
       <c r="S945" s="24"/>
       <c r="T945" s="189"/>
-      <c r="U945" s="217"/>
+      <c r="U945" s="215"/>
     </row>
     <row r="946" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A946" s="37"/>
@@ -40836,7 +40837,7 @@
       <c r="R946" s="25"/>
       <c r="S946" s="24"/>
       <c r="T946" s="189"/>
-      <c r="U946" s="217"/>
+      <c r="U946" s="215"/>
     </row>
     <row r="947" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A947" s="37"/>
@@ -40859,7 +40860,7 @@
       <c r="R947" s="25"/>
       <c r="S947" s="24"/>
       <c r="T947" s="189"/>
-      <c r="U947" s="217"/>
+      <c r="U947" s="215"/>
     </row>
     <row r="948" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A948" s="37"/>
@@ -40882,7 +40883,7 @@
       <c r="R948" s="25"/>
       <c r="S948" s="24"/>
       <c r="T948" s="189"/>
-      <c r="U948" s="217"/>
+      <c r="U948" s="215"/>
     </row>
     <row r="949" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A949" s="37"/>
@@ -40905,7 +40906,7 @@
       <c r="R949" s="25"/>
       <c r="S949" s="24"/>
       <c r="T949" s="189"/>
-      <c r="U949" s="217"/>
+      <c r="U949" s="215"/>
     </row>
     <row r="950" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A950" s="37"/>
@@ -40928,7 +40929,7 @@
       <c r="R950" s="25"/>
       <c r="S950" s="24"/>
       <c r="T950" s="189"/>
-      <c r="U950" s="217"/>
+      <c r="U950" s="215"/>
     </row>
     <row r="951" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A951" s="37"/>
@@ -40951,7 +40952,7 @@
       <c r="R951" s="25"/>
       <c r="S951" s="24"/>
       <c r="T951" s="189"/>
-      <c r="U951" s="217"/>
+      <c r="U951" s="215"/>
     </row>
     <row r="952" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A952" s="37"/>
@@ -40974,7 +40975,7 @@
       <c r="R952" s="25"/>
       <c r="S952" s="24"/>
       <c r="T952" s="189"/>
-      <c r="U952" s="217"/>
+      <c r="U952" s="215"/>
     </row>
     <row r="953" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A953" s="37"/>
@@ -40997,7 +40998,7 @@
       <c r="R953" s="25"/>
       <c r="S953" s="24"/>
       <c r="T953" s="189"/>
-      <c r="U953" s="217"/>
+      <c r="U953" s="215"/>
     </row>
     <row r="954" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A954" s="37"/>
@@ -41020,7 +41021,7 @@
       <c r="R954" s="25"/>
       <c r="S954" s="24"/>
       <c r="T954" s="189"/>
-      <c r="U954" s="217"/>
+      <c r="U954" s="215"/>
     </row>
     <row r="955" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A955" s="37"/>
@@ -41043,7 +41044,7 @@
       <c r="R955" s="25"/>
       <c r="S955" s="24"/>
       <c r="T955" s="189"/>
-      <c r="U955" s="217"/>
+      <c r="U955" s="215"/>
     </row>
     <row r="956" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A956" s="37"/>
@@ -41066,7 +41067,7 @@
       <c r="R956" s="25"/>
       <c r="S956" s="24"/>
       <c r="T956" s="189"/>
-      <c r="U956" s="217"/>
+      <c r="U956" s="215"/>
     </row>
     <row r="957" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A957" s="37" t="s">
@@ -41105,7 +41106,7 @@
       <c r="T957" s="54" t="s">
         <v>702</v>
       </c>
-      <c r="U957" s="217" t="s">
+      <c r="U957" s="215" t="s">
         <v>704</v>
       </c>
     </row>
@@ -41130,7 +41131,7 @@
       <c r="R958" s="25"/>
       <c r="S958" s="24"/>
       <c r="T958" s="54"/>
-      <c r="U958" s="217"/>
+      <c r="U958" s="215"/>
     </row>
     <row r="959" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A959" s="37"/>
@@ -41153,7 +41154,7 @@
       <c r="R959" s="25"/>
       <c r="S959" s="24"/>
       <c r="T959" s="54"/>
-      <c r="U959" s="217"/>
+      <c r="U959" s="215"/>
     </row>
     <row r="960" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A960" s="37"/>
@@ -41176,7 +41177,7 @@
       <c r="R960" s="25"/>
       <c r="S960" s="24"/>
       <c r="T960" s="54"/>
-      <c r="U960" s="217"/>
+      <c r="U960" s="215"/>
     </row>
     <row r="961" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A961" s="37"/>
@@ -41199,7 +41200,7 @@
       <c r="R961" s="25"/>
       <c r="S961" s="24"/>
       <c r="T961" s="54"/>
-      <c r="U961" s="217"/>
+      <c r="U961" s="215"/>
     </row>
     <row r="962" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A962" s="37" t="s">
@@ -41238,7 +41239,7 @@
       <c r="T962" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="U962" s="216" t="s">
+      <c r="U962" s="220" t="s">
         <v>917</v>
       </c>
     </row>
@@ -41279,7 +41280,7 @@
       <c r="T963" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="U963" s="216"/>
+      <c r="U963" s="220"/>
     </row>
     <row r="964" spans="1:21" ht="26" x14ac:dyDescent="0.35">
       <c r="A964" s="37" t="s">
@@ -41363,7 +41364,7 @@
       <c r="T965" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="U965" s="216" t="s">
+      <c r="U965" s="220" t="s">
         <v>169</v>
       </c>
     </row>
@@ -41408,7 +41409,7 @@
       <c r="T966" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="U966" s="216"/>
+      <c r="U966" s="220"/>
     </row>
     <row r="967" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A967" s="37" t="s">
@@ -41451,7 +41452,7 @@
       <c r="T967" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="U967" s="216"/>
+      <c r="U967" s="220"/>
     </row>
     <row r="968" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A968" s="37" t="s">
@@ -41494,7 +41495,7 @@
       <c r="T968" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="U968" s="216"/>
+      <c r="U968" s="220"/>
     </row>
     <row r="969" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A969" s="37" t="s">
@@ -41537,7 +41538,7 @@
       <c r="T969" s="54" t="s">
         <v>203</v>
       </c>
-      <c r="U969" s="216"/>
+      <c r="U969" s="220"/>
     </row>
     <row r="970" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A970" s="37" t="s">
@@ -41580,7 +41581,7 @@
       <c r="T970" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="U970" s="216"/>
+      <c r="U970" s="220"/>
     </row>
     <row r="971" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A971" s="37" t="s">
@@ -41623,7 +41624,7 @@
       <c r="T971" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="U971" s="216"/>
+      <c r="U971" s="220"/>
     </row>
     <row r="972" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A972" s="37" t="s">
@@ -41666,7 +41667,7 @@
       <c r="T972" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="U972" s="216"/>
+      <c r="U972" s="220"/>
     </row>
     <row r="973" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A973" s="37" t="s">
@@ -41709,7 +41710,7 @@
       <c r="T973" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="U973" s="216"/>
+      <c r="U973" s="220"/>
     </row>
     <row r="974" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A974" s="37" t="s">
@@ -41752,7 +41753,7 @@
       <c r="T974" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="U974" s="216"/>
+      <c r="U974" s="220"/>
     </row>
     <row r="975" spans="1:21" ht="26" x14ac:dyDescent="0.35">
       <c r="A975" s="37" t="s">
@@ -41836,7 +41837,7 @@
       <c r="T976" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="U976" s="216" t="s">
+      <c r="U976" s="220" t="s">
         <v>169</v>
       </c>
     </row>
@@ -41881,7 +41882,7 @@
       <c r="T977" s="54" t="s">
         <v>187</v>
       </c>
-      <c r="U977" s="216"/>
+      <c r="U977" s="220"/>
     </row>
     <row r="978" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A978" s="37" t="s">
@@ -41924,7 +41925,7 @@
       <c r="T978" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="U978" s="216"/>
+      <c r="U978" s="220"/>
     </row>
     <row r="979" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A979" s="37" t="s">
@@ -41967,7 +41968,7 @@
       <c r="T979" s="54" t="s">
         <v>189</v>
       </c>
-      <c r="U979" s="216"/>
+      <c r="U979" s="220"/>
     </row>
     <row r="980" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A980" s="37" t="s">
@@ -42010,7 +42011,7 @@
       <c r="T980" s="54" t="s">
         <v>190</v>
       </c>
-      <c r="U980" s="216"/>
+      <c r="U980" s="220"/>
     </row>
     <row r="981" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A981" s="37" t="s">
@@ -42053,7 +42054,7 @@
       <c r="T981" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="U981" s="216"/>
+      <c r="U981" s="220"/>
     </row>
     <row r="982" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A982" s="37" t="s">
@@ -42096,7 +42097,7 @@
       <c r="T982" s="54" t="s">
         <v>192</v>
       </c>
-      <c r="U982" s="216"/>
+      <c r="U982" s="220"/>
     </row>
     <row r="983" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A983" s="37" t="s">
@@ -42139,7 +42140,7 @@
       <c r="T983" s="54" t="s">
         <v>193</v>
       </c>
-      <c r="U983" s="216"/>
+      <c r="U983" s="220"/>
     </row>
     <row r="984" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A984" s="37" t="s">
@@ -42182,7 +42183,7 @@
       <c r="T984" s="54" t="s">
         <v>194</v>
       </c>
-      <c r="U984" s="216"/>
+      <c r="U984" s="220"/>
     </row>
     <row r="985" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A985" s="37" t="s">
@@ -42225,7 +42226,7 @@
       <c r="T985" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="U985" s="216"/>
+      <c r="U985" s="220"/>
     </row>
     <row r="986" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A986" s="37" t="s">
@@ -42272,7 +42273,7 @@
       <c r="T986" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="U986" s="217" t="s">
+      <c r="U986" s="215" t="s">
         <v>891</v>
       </c>
     </row>
@@ -42321,7 +42322,7 @@
       <c r="T987" s="54" t="s">
         <v>888</v>
       </c>
-      <c r="U987" s="217"/>
+      <c r="U987" s="215"/>
     </row>
     <row r="988" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A988" s="37" t="s">
@@ -42368,7 +42369,7 @@
       <c r="T988" s="54" t="s">
         <v>889</v>
       </c>
-      <c r="U988" s="217"/>
+      <c r="U988" s="215"/>
     </row>
     <row r="989" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A989" s="37"/>
@@ -42391,7 +42392,7 @@
       <c r="R989" s="62"/>
       <c r="S989" s="24"/>
       <c r="T989" s="54"/>
-      <c r="U989" s="217"/>
+      <c r="U989" s="215"/>
     </row>
     <row r="990" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A990" s="37"/>
@@ -42414,7 +42415,7 @@
       <c r="R990" s="62"/>
       <c r="S990" s="24"/>
       <c r="T990" s="54"/>
-      <c r="U990" s="217"/>
+      <c r="U990" s="215"/>
     </row>
     <row r="991" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A991" s="37"/>
@@ -42437,7 +42438,7 @@
       <c r="R991" s="62"/>
       <c r="S991" s="24"/>
       <c r="T991" s="54"/>
-      <c r="U991" s="217"/>
+      <c r="U991" s="215"/>
     </row>
     <row r="992" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A992" s="37"/>
@@ -42460,7 +42461,7 @@
       <c r="R992" s="62"/>
       <c r="S992" s="24"/>
       <c r="T992" s="54"/>
-      <c r="U992" s="217"/>
+      <c r="U992" s="215"/>
     </row>
     <row r="993" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A993" s="37"/>
@@ -42483,7 +42484,7 @@
       <c r="R993" s="62"/>
       <c r="S993" s="24"/>
       <c r="T993" s="54"/>
-      <c r="U993" s="217"/>
+      <c r="U993" s="215"/>
     </row>
     <row r="994" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A994" s="37"/>
@@ -42506,7 +42507,7 @@
       <c r="R994" s="62"/>
       <c r="S994" s="24"/>
       <c r="T994" s="54"/>
-      <c r="U994" s="217"/>
+      <c r="U994" s="215"/>
     </row>
     <row r="995" spans="1:21" ht="78" x14ac:dyDescent="0.35">
       <c r="A995" s="37" t="s">
@@ -42602,7 +42603,7 @@
       <c r="T996" s="54" t="s">
         <v>806</v>
       </c>
-      <c r="U996" s="217" t="s">
+      <c r="U996" s="215" t="s">
         <v>852</v>
       </c>
     </row>
@@ -42651,7 +42652,7 @@
       <c r="T997" s="54" t="s">
         <v>807</v>
       </c>
-      <c r="U997" s="217"/>
+      <c r="U997" s="215"/>
     </row>
     <row r="998" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A998" s="37"/>
@@ -42674,7 +42675,7 @@
       <c r="R998" s="86"/>
       <c r="S998" s="24"/>
       <c r="T998" s="54"/>
-      <c r="U998" s="217"/>
+      <c r="U998" s="215"/>
     </row>
     <row r="999" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A999" s="37"/>
@@ -42697,7 +42698,7 @@
       <c r="R999" s="86"/>
       <c r="S999" s="24"/>
       <c r="T999" s="54"/>
-      <c r="U999" s="217"/>
+      <c r="U999" s="215"/>
     </row>
     <row r="1000" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1000" s="37"/>
@@ -42720,7 +42721,7 @@
       <c r="R1000" s="86"/>
       <c r="S1000" s="24"/>
       <c r="T1000" s="54"/>
-      <c r="U1000" s="217"/>
+      <c r="U1000" s="215"/>
     </row>
     <row r="1001" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1001" s="37"/>
@@ -42743,7 +42744,7 @@
       <c r="R1001" s="86"/>
       <c r="S1001" s="24"/>
       <c r="T1001" s="209"/>
-      <c r="U1001" s="217"/>
+      <c r="U1001" s="215"/>
     </row>
     <row r="1002" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1002" s="37"/>
@@ -42766,7 +42767,7 @@
       <c r="R1002" s="86"/>
       <c r="S1002" s="24"/>
       <c r="T1002" s="54"/>
-      <c r="U1002" s="217"/>
+      <c r="U1002" s="215"/>
     </row>
     <row r="1003" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1003" s="37"/>
@@ -42789,7 +42790,7 @@
       <c r="R1003" s="86"/>
       <c r="S1003" s="24"/>
       <c r="T1003" s="54"/>
-      <c r="U1003" s="217"/>
+      <c r="U1003" s="215"/>
     </row>
     <row r="1004" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1004" s="37"/>
@@ -42812,7 +42813,7 @@
       <c r="R1004" s="86"/>
       <c r="S1004" s="24"/>
       <c r="T1004" s="54"/>
-      <c r="U1004" s="217"/>
+      <c r="U1004" s="215"/>
     </row>
     <row r="1005" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1005" s="37"/>
@@ -42835,7 +42836,7 @@
       <c r="R1005" s="86"/>
       <c r="S1005" s="24"/>
       <c r="T1005" s="54"/>
-      <c r="U1005" s="217"/>
+      <c r="U1005" s="215"/>
     </row>
     <row r="1006" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1006" s="37" t="s">
@@ -42986,7 +42987,7 @@
       <c r="T1008" s="198" t="s">
         <v>1108</v>
       </c>
-      <c r="U1008" s="215" t="s">
+      <c r="U1008" s="221" t="s">
         <v>1120</v>
       </c>
     </row>
@@ -43041,7 +43042,7 @@
       <c r="T1009" s="198" t="s">
         <v>1109</v>
       </c>
-      <c r="U1009" s="215"/>
+      <c r="U1009" s="221"/>
     </row>
     <row r="1010" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1010" s="37" t="s">
@@ -43094,7 +43095,7 @@
       <c r="T1010" s="198" t="s">
         <v>1110</v>
       </c>
-      <c r="U1010" s="215"/>
+      <c r="U1010" s="221"/>
     </row>
     <row r="1011" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1011" s="37" t="s">
@@ -43147,7 +43148,7 @@
       <c r="T1011" s="198" t="s">
         <v>1108</v>
       </c>
-      <c r="U1011" s="215"/>
+      <c r="U1011" s="221"/>
     </row>
     <row r="1012" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1012" s="37" t="s">
@@ -43200,7 +43201,7 @@
       <c r="T1012" s="198" t="s">
         <v>1109</v>
       </c>
-      <c r="U1012" s="215"/>
+      <c r="U1012" s="221"/>
     </row>
     <row r="1013" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1013" s="37" t="s">
@@ -43253,7 +43254,7 @@
       <c r="T1013" s="198" t="s">
         <v>1110</v>
       </c>
-      <c r="U1013" s="215"/>
+      <c r="U1013" s="221"/>
     </row>
     <row r="1014" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1014" s="37" t="s">
@@ -43306,7 +43307,7 @@
       <c r="T1014" s="198" t="s">
         <v>1108</v>
       </c>
-      <c r="U1014" s="215"/>
+      <c r="U1014" s="221"/>
     </row>
     <row r="1015" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1015" s="37" t="s">
@@ -43359,7 +43360,7 @@
       <c r="T1015" s="198" t="s">
         <v>1109</v>
       </c>
-      <c r="U1015" s="215"/>
+      <c r="U1015" s="221"/>
     </row>
     <row r="1016" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1016" s="37" t="s">
@@ -43412,7 +43413,7 @@
       <c r="T1016" s="198" t="s">
         <v>1110</v>
       </c>
-      <c r="U1016" s="215"/>
+      <c r="U1016" s="221"/>
     </row>
     <row r="1017" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1017" s="37" t="s">
@@ -43465,7 +43466,7 @@
       <c r="T1017" s="198" t="s">
         <v>1108</v>
       </c>
-      <c r="U1017" s="215"/>
+      <c r="U1017" s="221"/>
     </row>
     <row r="1018" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1018" s="37" t="s">
@@ -43518,7 +43519,7 @@
       <c r="T1018" s="198" t="s">
         <v>1109</v>
       </c>
-      <c r="U1018" s="215"/>
+      <c r="U1018" s="221"/>
     </row>
     <row r="1019" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1019" s="37" t="s">
@@ -43571,7 +43572,7 @@
       <c r="T1019" s="198" t="s">
         <v>1110</v>
       </c>
-      <c r="U1019" s="215"/>
+      <c r="U1019" s="221"/>
     </row>
     <row r="1020" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1020" s="37" t="s">
@@ -43624,7 +43625,7 @@
       <c r="T1020" s="198" t="s">
         <v>1111</v>
       </c>
-      <c r="U1020" s="215"/>
+      <c r="U1020" s="221"/>
     </row>
     <row r="1021" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1021" s="37" t="s">
@@ -43677,7 +43678,7 @@
       <c r="T1021" s="198" t="s">
         <v>1112</v>
       </c>
-      <c r="U1021" s="215"/>
+      <c r="U1021" s="221"/>
     </row>
     <row r="1022" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1022" s="37" t="s">
@@ -43730,7 +43731,7 @@
       <c r="T1022" s="198" t="s">
         <v>1113</v>
       </c>
-      <c r="U1022" s="215"/>
+      <c r="U1022" s="221"/>
     </row>
     <row r="1023" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1023" s="37" t="s">
@@ -43783,7 +43784,7 @@
       <c r="T1023" s="198" t="s">
         <v>1111</v>
       </c>
-      <c r="U1023" s="215"/>
+      <c r="U1023" s="221"/>
     </row>
     <row r="1024" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1024" s="37" t="s">
@@ -43836,7 +43837,7 @@
       <c r="T1024" s="198" t="s">
         <v>1112</v>
       </c>
-      <c r="U1024" s="215"/>
+      <c r="U1024" s="221"/>
     </row>
     <row r="1025" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1025" s="37" t="s">
@@ -43889,7 +43890,7 @@
       <c r="T1025" s="198" t="s">
         <v>1113</v>
       </c>
-      <c r="U1025" s="215"/>
+      <c r="U1025" s="221"/>
     </row>
     <row r="1026" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1026" s="37" t="s">
@@ -43942,7 +43943,7 @@
       <c r="T1026" s="198" t="s">
         <v>1111</v>
       </c>
-      <c r="U1026" s="215"/>
+      <c r="U1026" s="221"/>
     </row>
     <row r="1027" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1027" s="37" t="s">
@@ -43995,7 +43996,7 @@
       <c r="T1027" s="198" t="s">
         <v>1112</v>
       </c>
-      <c r="U1027" s="215"/>
+      <c r="U1027" s="221"/>
     </row>
     <row r="1028" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1028" s="37" t="s">
@@ -44048,7 +44049,7 @@
       <c r="T1028" s="198" t="s">
         <v>1113</v>
       </c>
-      <c r="U1028" s="215"/>
+      <c r="U1028" s="221"/>
     </row>
     <row r="1029" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1029" s="37" t="s">
@@ -44101,7 +44102,7 @@
       <c r="T1029" s="198" t="s">
         <v>1111</v>
       </c>
-      <c r="U1029" s="215"/>
+      <c r="U1029" s="221"/>
     </row>
     <row r="1030" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1030" s="37" t="s">
@@ -44154,7 +44155,7 @@
       <c r="T1030" s="198" t="s">
         <v>1112</v>
       </c>
-      <c r="U1030" s="215"/>
+      <c r="U1030" s="221"/>
     </row>
     <row r="1031" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1031" s="37" t="s">
@@ -44207,7 +44208,7 @@
       <c r="T1031" s="198" t="s">
         <v>1113</v>
       </c>
-      <c r="U1031" s="215"/>
+      <c r="U1031" s="221"/>
     </row>
     <row r="1032" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1032" s="37" t="s">
@@ -44253,10 +44254,10 @@
       <c r="Q1032" s="53"/>
       <c r="R1032" s="86"/>
       <c r="S1032" s="24"/>
-      <c r="T1032" s="216" t="s">
+      <c r="T1032" s="220" t="s">
         <v>332</v>
       </c>
-      <c r="U1032" s="220" t="s">
+      <c r="U1032" s="223" t="s">
         <v>854</v>
       </c>
     </row>
@@ -44304,8 +44305,8 @@
       <c r="Q1033" s="53"/>
       <c r="R1033" s="86"/>
       <c r="S1033" s="24"/>
-      <c r="T1033" s="216"/>
-      <c r="U1033" s="220"/>
+      <c r="T1033" s="220"/>
+      <c r="U1033" s="223"/>
     </row>
     <row r="1034" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1034" s="37" t="s">
@@ -44351,8 +44352,8 @@
       <c r="Q1034" s="53"/>
       <c r="R1034" s="86"/>
       <c r="S1034" s="24"/>
-      <c r="T1034" s="216"/>
-      <c r="U1034" s="220"/>
+      <c r="T1034" s="220"/>
+      <c r="U1034" s="223"/>
     </row>
     <row r="1035" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1035" s="37" t="s">
@@ -44398,8 +44399,8 @@
       <c r="Q1035" s="53"/>
       <c r="R1035" s="86"/>
       <c r="S1035" s="24"/>
-      <c r="T1035" s="216"/>
-      <c r="U1035" s="220"/>
+      <c r="T1035" s="220"/>
+      <c r="U1035" s="223"/>
     </row>
     <row r="1036" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1036" s="37" t="s">
@@ -44445,8 +44446,8 @@
       <c r="Q1036" s="53"/>
       <c r="R1036" s="86"/>
       <c r="S1036" s="24"/>
-      <c r="T1036" s="216"/>
-      <c r="U1036" s="220"/>
+      <c r="T1036" s="220"/>
+      <c r="U1036" s="223"/>
     </row>
     <row r="1037" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1037" s="37" t="s">
@@ -44492,8 +44493,8 @@
       <c r="Q1037" s="53"/>
       <c r="R1037" s="86"/>
       <c r="S1037" s="24"/>
-      <c r="T1037" s="216"/>
-      <c r="U1037" s="220"/>
+      <c r="T1037" s="220"/>
+      <c r="U1037" s="223"/>
     </row>
     <row r="1038" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1038" s="37" t="s">
@@ -44539,8 +44540,8 @@
       <c r="Q1038" s="53"/>
       <c r="R1038" s="86"/>
       <c r="S1038" s="24"/>
-      <c r="T1038" s="216"/>
-      <c r="U1038" s="220"/>
+      <c r="T1038" s="220"/>
+      <c r="U1038" s="223"/>
     </row>
     <row r="1039" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1039" s="37" t="s">
@@ -44586,8 +44587,8 @@
       <c r="Q1039" s="53"/>
       <c r="R1039" s="86"/>
       <c r="S1039" s="24"/>
-      <c r="T1039" s="216"/>
-      <c r="U1039" s="220"/>
+      <c r="T1039" s="220"/>
+      <c r="U1039" s="223"/>
     </row>
     <row r="1040" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1040" s="37" t="s">
@@ -44633,8 +44634,8 @@
       <c r="Q1040" s="53"/>
       <c r="R1040" s="86"/>
       <c r="S1040" s="24"/>
-      <c r="T1040" s="216"/>
-      <c r="U1040" s="220"/>
+      <c r="T1040" s="220"/>
+      <c r="U1040" s="223"/>
     </row>
     <row r="1041" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1041" s="37" t="s">
@@ -44680,8 +44681,8 @@
       <c r="Q1041" s="53"/>
       <c r="R1041" s="86"/>
       <c r="S1041" s="24"/>
-      <c r="T1041" s="216"/>
-      <c r="U1041" s="220"/>
+      <c r="T1041" s="220"/>
+      <c r="U1041" s="223"/>
     </row>
     <row r="1042" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1042" s="37" t="s">
@@ -44727,8 +44728,8 @@
       <c r="Q1042" s="53"/>
       <c r="R1042" s="86"/>
       <c r="S1042" s="24"/>
-      <c r="T1042" s="216"/>
-      <c r="U1042" s="220"/>
+      <c r="T1042" s="220"/>
+      <c r="U1042" s="223"/>
     </row>
     <row r="1043" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1043" s="37" t="s">
@@ -44774,8 +44775,8 @@
       <c r="Q1043" s="53"/>
       <c r="R1043" s="86"/>
       <c r="S1043" s="24"/>
-      <c r="T1043" s="216"/>
-      <c r="U1043" s="220"/>
+      <c r="T1043" s="220"/>
+      <c r="U1043" s="223"/>
     </row>
     <row r="1044" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1044" s="37" t="s">
@@ -44821,8 +44822,8 @@
       <c r="Q1044" s="53"/>
       <c r="R1044" s="86"/>
       <c r="S1044" s="24"/>
-      <c r="T1044" s="216"/>
-      <c r="U1044" s="220"/>
+      <c r="T1044" s="220"/>
+      <c r="U1044" s="223"/>
     </row>
     <row r="1045" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1045" s="37" t="s">
@@ -44868,8 +44869,8 @@
       <c r="Q1045" s="53"/>
       <c r="R1045" s="86"/>
       <c r="S1045" s="24"/>
-      <c r="T1045" s="216"/>
-      <c r="U1045" s="220"/>
+      <c r="T1045" s="220"/>
+      <c r="U1045" s="223"/>
     </row>
     <row r="1046" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1046" s="37" t="s">
@@ -44915,8 +44916,8 @@
       <c r="Q1046" s="53"/>
       <c r="R1046" s="86"/>
       <c r="S1046" s="24"/>
-      <c r="T1046" s="216"/>
-      <c r="U1046" s="220"/>
+      <c r="T1046" s="220"/>
+      <c r="U1046" s="223"/>
     </row>
     <row r="1047" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1047" s="37" t="s">
@@ -44962,8 +44963,8 @@
       <c r="Q1047" s="53"/>
       <c r="R1047" s="86"/>
       <c r="S1047" s="24"/>
-      <c r="T1047" s="216"/>
-      <c r="U1047" s="220"/>
+      <c r="T1047" s="220"/>
+      <c r="U1047" s="223"/>
     </row>
     <row r="1048" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1048" s="37" t="s">
@@ -45009,8 +45010,8 @@
       <c r="Q1048" s="53"/>
       <c r="R1048" s="86"/>
       <c r="S1048" s="24"/>
-      <c r="T1048" s="216"/>
-      <c r="U1048" s="220"/>
+      <c r="T1048" s="220"/>
+      <c r="U1048" s="223"/>
     </row>
     <row r="1049" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1049" s="37" t="s">
@@ -45056,8 +45057,8 @@
       <c r="Q1049" s="53"/>
       <c r="R1049" s="86"/>
       <c r="S1049" s="24"/>
-      <c r="T1049" s="216"/>
-      <c r="U1049" s="220"/>
+      <c r="T1049" s="220"/>
+      <c r="U1049" s="223"/>
     </row>
     <row r="1050" spans="1:21" ht="130" x14ac:dyDescent="0.35">
       <c r="A1050" s="37" t="s">
@@ -45155,7 +45156,7 @@
       <c r="T1051" s="54" t="s">
         <v>334</v>
       </c>
-      <c r="U1051" s="217" t="s">
+      <c r="U1051" s="215" t="s">
         <v>914</v>
       </c>
     </row>
@@ -45206,7 +45207,7 @@
       <c r="T1052" s="54" t="s">
         <v>335</v>
       </c>
-      <c r="U1052" s="217"/>
+      <c r="U1052" s="215"/>
     </row>
     <row r="1053" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1053" s="37" t="s">
@@ -45255,7 +45256,7 @@
       <c r="T1053" s="54" t="s">
         <v>336</v>
       </c>
-      <c r="U1053" s="217"/>
+      <c r="U1053" s="215"/>
     </row>
     <row r="1054" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1054" s="37" t="s">
@@ -45304,7 +45305,7 @@
       <c r="T1054" s="54" t="s">
         <v>337</v>
       </c>
-      <c r="U1054" s="217"/>
+      <c r="U1054" s="215"/>
     </row>
     <row r="1055" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1055" s="37" t="s">
@@ -45353,7 +45354,7 @@
       <c r="T1055" s="54" t="s">
         <v>338</v>
       </c>
-      <c r="U1055" s="217"/>
+      <c r="U1055" s="215"/>
     </row>
     <row r="1056" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1056" s="37"/>
@@ -45376,7 +45377,7 @@
       <c r="R1056" s="25"/>
       <c r="S1056" s="24"/>
       <c r="T1056" s="171"/>
-      <c r="U1056" s="217"/>
+      <c r="U1056" s="215"/>
     </row>
     <row r="1057" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1057" s="37" t="s">
@@ -45423,7 +45424,7 @@
       <c r="T1057" s="186" t="s">
         <v>962</v>
       </c>
-      <c r="U1057" s="216" t="s">
+      <c r="U1057" s="220" t="s">
         <v>311</v>
       </c>
     </row>
@@ -45472,7 +45473,7 @@
       <c r="T1058" s="186" t="s">
         <v>963</v>
       </c>
-      <c r="U1058" s="216"/>
+      <c r="U1058" s="220"/>
     </row>
     <row r="1059" spans="1:21" ht="26" x14ac:dyDescent="0.35">
       <c r="A1059" s="37" t="s">
@@ -45500,7 +45501,7 @@
         <v>1</v>
       </c>
       <c r="I1059" s="58" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J1059" s="38" t="s">
         <v>2</v>
@@ -45519,10 +45520,10 @@
         <v>9</v>
       </c>
       <c r="T1059" s="214" t="s">
+        <v>1207</v>
+      </c>
+      <c r="U1059" s="214" t="s">
         <v>1208</v>
-      </c>
-      <c r="U1059" s="214" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="1060" spans="1:21" ht="26" x14ac:dyDescent="0.35">
@@ -45818,7 +45819,7 @@
         <v>935</v>
       </c>
       <c r="U1065" s="175" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="1066" spans="1:21" ht="52" x14ac:dyDescent="0.35">
@@ -46415,7 +46416,7 @@
       <c r="T1077" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="U1077" s="217" t="s">
+      <c r="U1077" s="215" t="s">
         <v>894</v>
       </c>
     </row>
@@ -46464,7 +46465,7 @@
       <c r="T1078" s="54" t="s">
         <v>892</v>
       </c>
-      <c r="U1078" s="217"/>
+      <c r="U1078" s="215"/>
     </row>
     <row r="1079" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1079" s="37" t="s">
@@ -46511,7 +46512,7 @@
       <c r="T1079" s="54" t="s">
         <v>893</v>
       </c>
-      <c r="U1079" s="217"/>
+      <c r="U1079" s="215"/>
     </row>
     <row r="1080" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1080" s="37"/>
@@ -46534,7 +46535,7 @@
       <c r="R1080" s="62"/>
       <c r="S1080" s="24"/>
       <c r="T1080" s="54"/>
-      <c r="U1080" s="217"/>
+      <c r="U1080" s="215"/>
     </row>
     <row r="1081" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1081" s="37"/>
@@ -46557,7 +46558,7 @@
       <c r="R1081" s="62"/>
       <c r="S1081" s="24"/>
       <c r="T1081" s="54"/>
-      <c r="U1081" s="217"/>
+      <c r="U1081" s="215"/>
     </row>
     <row r="1082" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1082" s="37"/>
@@ -46580,7 +46581,7 @@
       <c r="R1082" s="62"/>
       <c r="S1082" s="24"/>
       <c r="T1082" s="54"/>
-      <c r="U1082" s="217"/>
+      <c r="U1082" s="215"/>
     </row>
     <row r="1083" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1083" s="37"/>
@@ -46603,7 +46604,7 @@
       <c r="R1083" s="62"/>
       <c r="S1083" s="24"/>
       <c r="T1083" s="54"/>
-      <c r="U1083" s="217"/>
+      <c r="U1083" s="215"/>
     </row>
     <row r="1084" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1084" s="37"/>
@@ -46626,7 +46627,7 @@
       <c r="R1084" s="62"/>
       <c r="S1084" s="24"/>
       <c r="T1084" s="54"/>
-      <c r="U1084" s="217"/>
+      <c r="U1084" s="215"/>
     </row>
     <row r="1085" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1085" s="37"/>
@@ -46649,7 +46650,7 @@
       <c r="R1085" s="62"/>
       <c r="S1085" s="24"/>
       <c r="T1085" s="54"/>
-      <c r="U1085" s="217"/>
+      <c r="U1085" s="215"/>
     </row>
     <row r="1086" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1086" s="37"/>
@@ -46672,7 +46673,7 @@
       <c r="R1086" s="62"/>
       <c r="S1086" s="24"/>
       <c r="T1086" s="54"/>
-      <c r="U1086" s="217"/>
+      <c r="U1086" s="215"/>
     </row>
     <row r="1087" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1087" s="37"/>
@@ -46695,7 +46696,7 @@
       <c r="R1087" s="62"/>
       <c r="S1087" s="24"/>
       <c r="T1087" s="54"/>
-      <c r="U1087" s="217"/>
+      <c r="U1087" s="215"/>
     </row>
     <row r="1088" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1088" s="37"/>
@@ -46718,7 +46719,7 @@
       <c r="R1088" s="62"/>
       <c r="S1088" s="24"/>
       <c r="T1088" s="54"/>
-      <c r="U1088" s="217"/>
+      <c r="U1088" s="215"/>
     </row>
     <row r="1089" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1089" s="37"/>
@@ -46741,7 +46742,7 @@
       <c r="R1089" s="62"/>
       <c r="S1089" s="24"/>
       <c r="T1089" s="54"/>
-      <c r="U1089" s="217"/>
+      <c r="U1089" s="215"/>
     </row>
     <row r="1090" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1090" s="37"/>
@@ -46764,7 +46765,7 @@
       <c r="R1090" s="62"/>
       <c r="S1090" s="24"/>
       <c r="T1090" s="54"/>
-      <c r="U1090" s="217"/>
+      <c r="U1090" s="215"/>
     </row>
     <row r="1091" spans="1:21" ht="78" x14ac:dyDescent="0.35">
       <c r="A1091" s="37" t="s">
@@ -46860,7 +46861,7 @@
       <c r="T1092" s="54" t="s">
         <v>809</v>
       </c>
-      <c r="U1092" s="217" t="s">
+      <c r="U1092" s="215" t="s">
         <v>853</v>
       </c>
     </row>
@@ -46909,7 +46910,7 @@
       <c r="T1093" s="54" t="s">
         <v>810</v>
       </c>
-      <c r="U1093" s="217"/>
+      <c r="U1093" s="215"/>
     </row>
     <row r="1094" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1094" s="37"/>
@@ -46932,7 +46933,7 @@
       <c r="R1094" s="86"/>
       <c r="S1094" s="24"/>
       <c r="T1094" s="54"/>
-      <c r="U1094" s="217"/>
+      <c r="U1094" s="215"/>
     </row>
     <row r="1095" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1095" s="37"/>
@@ -46955,7 +46956,7 @@
       <c r="R1095" s="86"/>
       <c r="S1095" s="24"/>
       <c r="T1095" s="54"/>
-      <c r="U1095" s="217"/>
+      <c r="U1095" s="215"/>
     </row>
     <row r="1096" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1096" s="37"/>
@@ -46978,7 +46979,7 @@
       <c r="R1096" s="86"/>
       <c r="S1096" s="24"/>
       <c r="T1096" s="207"/>
-      <c r="U1096" s="217"/>
+      <c r="U1096" s="215"/>
     </row>
     <row r="1097" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1097" s="37"/>
@@ -47001,7 +47002,7 @@
       <c r="R1097" s="86"/>
       <c r="S1097" s="24"/>
       <c r="T1097" s="54"/>
-      <c r="U1097" s="217"/>
+      <c r="U1097" s="215"/>
     </row>
     <row r="1098" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1098" s="37"/>
@@ -47024,7 +47025,7 @@
       <c r="R1098" s="86"/>
       <c r="S1098" s="24"/>
       <c r="T1098" s="54"/>
-      <c r="U1098" s="217"/>
+      <c r="U1098" s="215"/>
     </row>
     <row r="1099" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1099" s="37"/>
@@ -47047,7 +47048,7 @@
       <c r="R1099" s="86"/>
       <c r="S1099" s="24"/>
       <c r="T1099" s="54"/>
-      <c r="U1099" s="217"/>
+      <c r="U1099" s="215"/>
     </row>
     <row r="1100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1100" s="37"/>
@@ -47070,7 +47071,7 @@
       <c r="R1100" s="86"/>
       <c r="S1100" s="24"/>
       <c r="T1100" s="54"/>
-      <c r="U1100" s="217"/>
+      <c r="U1100" s="215"/>
     </row>
     <row r="1101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1101" s="37"/>
@@ -47093,7 +47094,7 @@
       <c r="R1101" s="86"/>
       <c r="S1101" s="24"/>
       <c r="T1101" s="54"/>
-      <c r="U1101" s="217"/>
+      <c r="U1101" s="215"/>
     </row>
     <row r="1102" spans="1:21" ht="65" x14ac:dyDescent="0.35">
       <c r="A1102" s="37" t="s">
@@ -47195,7 +47196,7 @@
       <c r="T1103" s="198" t="s">
         <v>1114</v>
       </c>
-      <c r="U1103" s="215" t="s">
+      <c r="U1103" s="221" t="s">
         <v>1120</v>
       </c>
     </row>
@@ -47250,7 +47251,7 @@
       <c r="T1104" s="198" t="s">
         <v>1115</v>
       </c>
-      <c r="U1104" s="215"/>
+      <c r="U1104" s="221"/>
     </row>
     <row r="1105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1105" s="37" t="s">
@@ -47303,7 +47304,7 @@
       <c r="T1105" s="198" t="s">
         <v>1116</v>
       </c>
-      <c r="U1105" s="215"/>
+      <c r="U1105" s="221"/>
     </row>
     <row r="1106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1106" s="37" t="s">
@@ -47356,7 +47357,7 @@
       <c r="T1106" s="198" t="s">
         <v>1114</v>
       </c>
-      <c r="U1106" s="215"/>
+      <c r="U1106" s="221"/>
     </row>
     <row r="1107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1107" s="37" t="s">
@@ -47409,7 +47410,7 @@
       <c r="T1107" s="198" t="s">
         <v>1115</v>
       </c>
-      <c r="U1107" s="215"/>
+      <c r="U1107" s="221"/>
     </row>
     <row r="1108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1108" s="37" t="s">
@@ -47462,7 +47463,7 @@
       <c r="T1108" s="198" t="s">
         <v>1116</v>
       </c>
-      <c r="U1108" s="215"/>
+      <c r="U1108" s="221"/>
     </row>
     <row r="1109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1109" s="37" t="s">
@@ -47515,7 +47516,7 @@
       <c r="T1109" s="198" t="s">
         <v>1114</v>
       </c>
-      <c r="U1109" s="215"/>
+      <c r="U1109" s="221"/>
     </row>
     <row r="1110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1110" s="37" t="s">
@@ -47568,7 +47569,7 @@
       <c r="T1110" s="198" t="s">
         <v>1115</v>
       </c>
-      <c r="U1110" s="215"/>
+      <c r="U1110" s="221"/>
     </row>
     <row r="1111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1111" s="37" t="s">
@@ -47621,7 +47622,7 @@
       <c r="T1111" s="198" t="s">
         <v>1116</v>
       </c>
-      <c r="U1111" s="215"/>
+      <c r="U1111" s="221"/>
     </row>
     <row r="1112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1112" s="37" t="s">
@@ -47674,7 +47675,7 @@
       <c r="T1112" s="198" t="s">
         <v>1114</v>
       </c>
-      <c r="U1112" s="215"/>
+      <c r="U1112" s="221"/>
     </row>
     <row r="1113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1113" s="37" t="s">
@@ -47727,7 +47728,7 @@
       <c r="T1113" s="198" t="s">
         <v>1115</v>
       </c>
-      <c r="U1113" s="215"/>
+      <c r="U1113" s="221"/>
     </row>
     <row r="1114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1114" s="37" t="s">
@@ -47780,7 +47781,7 @@
       <c r="T1114" s="198" t="s">
         <v>1116</v>
       </c>
-      <c r="U1114" s="215"/>
+      <c r="U1114" s="221"/>
     </row>
     <row r="1115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1115" s="37" t="s">
@@ -47833,7 +47834,7 @@
       <c r="T1115" s="198" t="s">
         <v>1117</v>
       </c>
-      <c r="U1115" s="215"/>
+      <c r="U1115" s="221"/>
     </row>
     <row r="1116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1116" s="37" t="s">
@@ -47886,7 +47887,7 @@
       <c r="T1116" s="198" t="s">
         <v>1118</v>
       </c>
-      <c r="U1116" s="215"/>
+      <c r="U1116" s="221"/>
     </row>
     <row r="1117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1117" s="37" t="s">
@@ -47939,7 +47940,7 @@
       <c r="T1117" s="198" t="s">
         <v>1119</v>
       </c>
-      <c r="U1117" s="215"/>
+      <c r="U1117" s="221"/>
     </row>
     <row r="1118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1118" s="37" t="s">
@@ -47992,7 +47993,7 @@
       <c r="T1118" s="198" t="s">
         <v>1117</v>
       </c>
-      <c r="U1118" s="215"/>
+      <c r="U1118" s="221"/>
     </row>
     <row r="1119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1119" s="37" t="s">
@@ -48045,7 +48046,7 @@
       <c r="T1119" s="198" t="s">
         <v>1118</v>
       </c>
-      <c r="U1119" s="215"/>
+      <c r="U1119" s="221"/>
     </row>
     <row r="1120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1120" s="37" t="s">
@@ -48098,7 +48099,7 @@
       <c r="T1120" s="198" t="s">
         <v>1119</v>
       </c>
-      <c r="U1120" s="215"/>
+      <c r="U1120" s="221"/>
     </row>
     <row r="1121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1121" s="37" t="s">
@@ -48151,7 +48152,7 @@
       <c r="T1121" s="198" t="s">
         <v>1117</v>
       </c>
-      <c r="U1121" s="215"/>
+      <c r="U1121" s="221"/>
     </row>
     <row r="1122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1122" s="37" t="s">
@@ -48204,7 +48205,7 @@
       <c r="T1122" s="198" t="s">
         <v>1118</v>
       </c>
-      <c r="U1122" s="215"/>
+      <c r="U1122" s="221"/>
     </row>
     <row r="1123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1123" s="37" t="s">
@@ -48257,7 +48258,7 @@
       <c r="T1123" s="198" t="s">
         <v>1119</v>
       </c>
-      <c r="U1123" s="215"/>
+      <c r="U1123" s="221"/>
     </row>
     <row r="1124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1124" s="37" t="s">
@@ -48310,7 +48311,7 @@
       <c r="T1124" s="198" t="s">
         <v>1117</v>
       </c>
-      <c r="U1124" s="215"/>
+      <c r="U1124" s="221"/>
     </row>
     <row r="1125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1125" s="37" t="s">
@@ -48363,7 +48364,7 @@
       <c r="T1125" s="198" t="s">
         <v>1118</v>
       </c>
-      <c r="U1125" s="215"/>
+      <c r="U1125" s="221"/>
     </row>
     <row r="1126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1126" s="37" t="s">
@@ -48416,7 +48417,7 @@
       <c r="T1126" s="198" t="s">
         <v>1119</v>
       </c>
-      <c r="U1126" s="215"/>
+      <c r="U1126" s="221"/>
     </row>
     <row r="1127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1127" s="37" t="s">
@@ -48461,7 +48462,7 @@
       <c r="T1127" s="54" t="s">
         <v>904</v>
       </c>
-      <c r="U1127" s="217" t="s">
+      <c r="U1127" s="215" t="s">
         <v>903</v>
       </c>
     </row>
@@ -48508,7 +48509,7 @@
       <c r="T1128" s="54" t="s">
         <v>905</v>
       </c>
-      <c r="U1128" s="217"/>
+      <c r="U1128" s="215"/>
     </row>
     <row r="1129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1129" s="37"/>
@@ -48531,7 +48532,7 @@
       <c r="R1129" s="25"/>
       <c r="S1129" s="24"/>
       <c r="T1129" s="169"/>
-      <c r="U1129" s="217"/>
+      <c r="U1129" s="215"/>
     </row>
     <row r="1130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1130" s="37"/>
@@ -48554,7 +48555,7 @@
       <c r="R1130" s="25"/>
       <c r="S1130" s="24"/>
       <c r="T1130" s="169"/>
-      <c r="U1130" s="217"/>
+      <c r="U1130" s="215"/>
     </row>
     <row r="1131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1131" s="37"/>
@@ -48577,7 +48578,7 @@
       <c r="R1131" s="25"/>
       <c r="S1131" s="24"/>
       <c r="T1131" s="169"/>
-      <c r="U1131" s="217"/>
+      <c r="U1131" s="215"/>
     </row>
     <row r="1132" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1132" s="37"/>
@@ -48600,7 +48601,7 @@
       <c r="R1132" s="25"/>
       <c r="S1132" s="24"/>
       <c r="T1132" s="54"/>
-      <c r="U1132" s="217"/>
+      <c r="U1132" s="215"/>
     </row>
     <row r="1133" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1133" s="37" t="s">
@@ -48651,7 +48652,7 @@
       <c r="T1133" s="54" t="s">
         <v>416</v>
       </c>
-      <c r="U1133" s="216" t="s">
+      <c r="U1133" s="220" t="s">
         <v>417</v>
       </c>
     </row>
@@ -48702,7 +48703,7 @@
       </c>
       <c r="S1134" s="24"/>
       <c r="T1134" s="54"/>
-      <c r="U1134" s="216"/>
+      <c r="U1134" s="220"/>
     </row>
     <row r="1135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1135" s="37" t="s">
@@ -48751,7 +48752,7 @@
       </c>
       <c r="S1135" s="24"/>
       <c r="T1135" s="54"/>
-      <c r="U1135" s="216"/>
+      <c r="U1135" s="220"/>
     </row>
     <row r="1136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1136" s="37" t="s">
@@ -48798,7 +48799,7 @@
       <c r="R1136" s="25"/>
       <c r="S1136" s="24"/>
       <c r="T1136" s="54"/>
-      <c r="U1136" s="216"/>
+      <c r="U1136" s="220"/>
     </row>
     <row r="1137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1137" s="37"/>
@@ -48821,7 +48822,7 @@
       <c r="R1137" s="25"/>
       <c r="S1137" s="24"/>
       <c r="T1137" s="54"/>
-      <c r="U1137" s="216"/>
+      <c r="U1137" s="220"/>
     </row>
     <row r="1138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1138" s="37"/>
@@ -48844,7 +48845,7 @@
       <c r="R1138" s="25"/>
       <c r="S1138" s="24"/>
       <c r="T1138" s="54"/>
-      <c r="U1138" s="216"/>
+      <c r="U1138" s="220"/>
     </row>
     <row r="1139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1139" s="37"/>
@@ -48867,7 +48868,7 @@
       <c r="R1139" s="25"/>
       <c r="S1139" s="24"/>
       <c r="T1139" s="54"/>
-      <c r="U1139" s="216"/>
+      <c r="U1139" s="220"/>
     </row>
     <row r="1140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1140" s="37"/>
@@ -48890,7 +48891,7 @@
       <c r="R1140" s="25"/>
       <c r="S1140" s="24"/>
       <c r="T1140" s="54"/>
-      <c r="U1140" s="216"/>
+      <c r="U1140" s="220"/>
     </row>
     <row r="1141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1141" s="37"/>
@@ -48913,7 +48914,7 @@
       <c r="R1141" s="25"/>
       <c r="S1141" s="24"/>
       <c r="T1141" s="54"/>
-      <c r="U1141" s="216"/>
+      <c r="U1141" s="220"/>
     </row>
     <row r="1142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1142" s="37"/>
@@ -48936,7 +48937,7 @@
       <c r="R1142" s="25"/>
       <c r="S1142" s="24"/>
       <c r="T1142" s="54"/>
-      <c r="U1142" s="216"/>
+      <c r="U1142" s="220"/>
     </row>
     <row r="1143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1143" s="37"/>
@@ -48959,7 +48960,7 @@
       <c r="R1143" s="25"/>
       <c r="S1143" s="24"/>
       <c r="T1143" s="54"/>
-      <c r="U1143" s="216"/>
+      <c r="U1143" s="220"/>
     </row>
     <row r="1144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1144" s="37" t="s">
@@ -49057,7 +49058,7 @@
       <c r="T1145" s="54" t="s">
         <v>236</v>
       </c>
-      <c r="U1145" s="216" t="s">
+      <c r="U1145" s="220" t="s">
         <v>237</v>
       </c>
     </row>
@@ -49108,7 +49109,7 @@
       <c r="T1146" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="U1146" s="216"/>
+      <c r="U1146" s="220"/>
     </row>
     <row r="1147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1147" s="37" t="s">
@@ -49157,7 +49158,7 @@
       <c r="T1147" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="U1147" s="216"/>
+      <c r="U1147" s="220"/>
     </row>
     <row r="1148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1148" s="37" t="s">
@@ -49206,7 +49207,7 @@
       <c r="T1148" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="U1148" s="217" t="s">
+      <c r="U1148" s="215" t="s">
         <v>915</v>
       </c>
     </row>
@@ -49257,7 +49258,7 @@
       <c r="T1149" s="54" t="s">
         <v>229</v>
       </c>
-      <c r="U1149" s="217"/>
+      <c r="U1149" s="215"/>
     </row>
     <row r="1150" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1150" s="37" t="s">
@@ -49306,7 +49307,7 @@
       <c r="T1150" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="U1150" s="217"/>
+      <c r="U1150" s="215"/>
     </row>
     <row r="1151" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1151" s="37" t="s">
@@ -49355,7 +49356,7 @@
       <c r="T1151" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="U1151" s="217"/>
+      <c r="U1151" s="215"/>
     </row>
     <row r="1152" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1152" s="37" t="s">
@@ -49404,7 +49405,7 @@
       <c r="T1152" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="U1152" s="217"/>
+      <c r="U1152" s="215"/>
     </row>
     <row r="1153" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1153" s="37"/>
@@ -49427,7 +49428,7 @@
       <c r="R1153" s="25"/>
       <c r="S1153" s="24"/>
       <c r="T1153" s="171"/>
-      <c r="U1153" s="217"/>
+      <c r="U1153" s="215"/>
     </row>
     <row r="1154" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1154" s="37" t="s">
@@ -49474,7 +49475,7 @@
       <c r="T1154" s="186" t="s">
         <v>960</v>
       </c>
-      <c r="U1154" s="216" t="s">
+      <c r="U1154" s="220" t="s">
         <v>311</v>
       </c>
     </row>
@@ -49523,7 +49524,7 @@
       <c r="T1155" s="186" t="s">
         <v>961</v>
       </c>
-      <c r="U1155" s="216"/>
+      <c r="U1155" s="220"/>
     </row>
     <row r="1156" spans="1:21" ht="26" x14ac:dyDescent="0.35">
       <c r="A1156" s="37" t="s">
@@ -49551,7 +49552,7 @@
         <v>1</v>
       </c>
       <c r="I1156" s="58" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J1156" s="38" t="s">
         <v>2</v>
@@ -49570,10 +49571,10 @@
         <v>9</v>
       </c>
       <c r="T1156" s="214" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="U1156" s="214" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="1157" spans="1:21" ht="26" x14ac:dyDescent="0.35">
@@ -51075,6 +51076,67 @@
   </sheetData>
   <autoFilter ref="A3:U1197" xr:uid="{F169886C-A9B5-4F04-8A7C-168F082390ED}"/>
   <mergeCells count="77">
+    <mergeCell ref="U773:U787"/>
+    <mergeCell ref="U965:U974"/>
+    <mergeCell ref="U996:U1005"/>
+    <mergeCell ref="U227:U228"/>
+    <mergeCell ref="U234:U239"/>
+    <mergeCell ref="U957:U961"/>
+    <mergeCell ref="U714:U719"/>
+    <mergeCell ref="U687:U690"/>
+    <mergeCell ref="U726:U728"/>
+    <mergeCell ref="U692:U697"/>
+    <mergeCell ref="U857:U879"/>
+    <mergeCell ref="U890:U899"/>
+    <mergeCell ref="U845:U856"/>
+    <mergeCell ref="U134:U136"/>
+    <mergeCell ref="U156:U196"/>
+    <mergeCell ref="U208:U219"/>
+    <mergeCell ref="U584:U592"/>
+    <mergeCell ref="U358:U376"/>
+    <mergeCell ref="U429:U431"/>
+    <mergeCell ref="U443:U445"/>
+    <mergeCell ref="U143:U145"/>
+    <mergeCell ref="U251:U303"/>
+    <mergeCell ref="U377:U398"/>
+    <mergeCell ref="U521:U548"/>
+    <mergeCell ref="U322:U350"/>
+    <mergeCell ref="U558:U564"/>
+    <mergeCell ref="U399:U409"/>
+    <mergeCell ref="U460:U489"/>
+    <mergeCell ref="U410:U420"/>
+    <mergeCell ref="U1154:U1155"/>
+    <mergeCell ref="U1057:U1058"/>
+    <mergeCell ref="U901:U903"/>
+    <mergeCell ref="U925:U934"/>
+    <mergeCell ref="U1145:U1147"/>
+    <mergeCell ref="U976:U985"/>
+    <mergeCell ref="U962:U963"/>
+    <mergeCell ref="U1148:U1153"/>
+    <mergeCell ref="U1133:U1143"/>
+    <mergeCell ref="U1092:U1101"/>
+    <mergeCell ref="U1127:U1132"/>
+    <mergeCell ref="U935:U956"/>
+    <mergeCell ref="U986:U994"/>
+    <mergeCell ref="U1077:U1090"/>
+    <mergeCell ref="U1051:U1056"/>
+    <mergeCell ref="U1103:U1126"/>
+    <mergeCell ref="T1032:T1049"/>
+    <mergeCell ref="U551:U557"/>
+    <mergeCell ref="U610:U624"/>
+    <mergeCell ref="U633:U635"/>
+    <mergeCell ref="U636:U638"/>
+    <mergeCell ref="U1032:U1049"/>
+    <mergeCell ref="U880:U884"/>
+    <mergeCell ref="U788:U811"/>
+    <mergeCell ref="U812:U821"/>
+    <mergeCell ref="U830:U844"/>
+    <mergeCell ref="U885:U889"/>
+    <mergeCell ref="U822:U829"/>
+    <mergeCell ref="U905:U924"/>
+    <mergeCell ref="U738:U772"/>
+    <mergeCell ref="U1008:U1031"/>
+    <mergeCell ref="U731:U736"/>
     <mergeCell ref="U132:U133"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="U13:U16"/>
@@ -51091,67 +51153,6 @@
     <mergeCell ref="U46:U47"/>
     <mergeCell ref="U220:U224"/>
     <mergeCell ref="U141:U142"/>
-    <mergeCell ref="T1032:T1049"/>
-    <mergeCell ref="U551:U557"/>
-    <mergeCell ref="U610:U624"/>
-    <mergeCell ref="U633:U635"/>
-    <mergeCell ref="U636:U638"/>
-    <mergeCell ref="U1032:U1049"/>
-    <mergeCell ref="U880:U884"/>
-    <mergeCell ref="U788:U811"/>
-    <mergeCell ref="U812:U821"/>
-    <mergeCell ref="U830:U844"/>
-    <mergeCell ref="U885:U889"/>
-    <mergeCell ref="U822:U829"/>
-    <mergeCell ref="U905:U924"/>
-    <mergeCell ref="U738:U772"/>
-    <mergeCell ref="U1008:U1031"/>
-    <mergeCell ref="U731:U736"/>
-    <mergeCell ref="U1154:U1155"/>
-    <mergeCell ref="U1057:U1058"/>
-    <mergeCell ref="U901:U903"/>
-    <mergeCell ref="U925:U934"/>
-    <mergeCell ref="U1145:U1147"/>
-    <mergeCell ref="U976:U985"/>
-    <mergeCell ref="U962:U963"/>
-    <mergeCell ref="U1148:U1153"/>
-    <mergeCell ref="U1133:U1143"/>
-    <mergeCell ref="U1092:U1101"/>
-    <mergeCell ref="U1127:U1132"/>
-    <mergeCell ref="U935:U956"/>
-    <mergeCell ref="U986:U994"/>
-    <mergeCell ref="U1077:U1090"/>
-    <mergeCell ref="U1051:U1056"/>
-    <mergeCell ref="U1103:U1126"/>
-    <mergeCell ref="U134:U136"/>
-    <mergeCell ref="U156:U196"/>
-    <mergeCell ref="U208:U219"/>
-    <mergeCell ref="U584:U592"/>
-    <mergeCell ref="U358:U376"/>
-    <mergeCell ref="U429:U431"/>
-    <mergeCell ref="U443:U445"/>
-    <mergeCell ref="U143:U145"/>
-    <mergeCell ref="U251:U303"/>
-    <mergeCell ref="U377:U398"/>
-    <mergeCell ref="U521:U548"/>
-    <mergeCell ref="U322:U350"/>
-    <mergeCell ref="U558:U564"/>
-    <mergeCell ref="U399:U409"/>
-    <mergeCell ref="U460:U489"/>
-    <mergeCell ref="U410:U420"/>
-    <mergeCell ref="U773:U787"/>
-    <mergeCell ref="U965:U974"/>
-    <mergeCell ref="U996:U1005"/>
-    <mergeCell ref="U227:U228"/>
-    <mergeCell ref="U234:U239"/>
-    <mergeCell ref="U957:U961"/>
-    <mergeCell ref="U714:U719"/>
-    <mergeCell ref="U687:U690"/>
-    <mergeCell ref="U726:U728"/>
-    <mergeCell ref="U692:U697"/>
-    <mergeCell ref="U857:U879"/>
-    <mergeCell ref="U890:U899"/>
-    <mergeCell ref="U845:U856"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R438" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -51207,12 +51208,12 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="390" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A7" s="164">
         <v>3</v>
       </c>
       <c r="B7" s="166" t="s">
-        <v>1129</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="208" x14ac:dyDescent="0.35">
@@ -51225,7 +51226,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="166" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
   </sheetData>
